--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="F14" t="n">
-        <v>6.24</v>
+        <v>5.37</v>
       </c>
       <c r="G14" t="n">
-        <v>332.2</v>
+        <v>334.3</v>
       </c>
       <c r="H14" t="n">
-        <v>99.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-26.07</v>
+        <v>-13.83</v>
       </c>
       <c r="K14" t="n">
-        <v>86.92</v>
+        <v>116.09</v>
       </c>
       <c r="L14" t="n">
-        <v>90.75</v>
+        <v>116.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:04:33</t>
+          <t>05:04:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="F15" t="n">
-        <v>5.63</v>
+        <v>6.54</v>
       </c>
       <c r="G15" t="n">
-        <v>327.4</v>
+        <v>319.6</v>
       </c>
       <c r="H15" t="n">
-        <v>97.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.17</v>
+        <v>92.19</v>
       </c>
       <c r="K15" t="n">
-        <v>-132.46</v>
+        <v>52.63</v>
       </c>
       <c r="L15" t="n">
-        <v>132.93</v>
+        <v>106.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:06:20</t>
+          <t>05:06:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="F16" t="n">
-        <v>5.93</v>
+        <v>5.99</v>
       </c>
       <c r="G16" t="n">
-        <v>342</v>
+        <v>342.4</v>
       </c>
       <c r="H16" t="n">
-        <v>92.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>117.99</v>
+        <v>34.78</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>22.72</v>
       </c>
       <c r="L16" t="n">
-        <v>118.01</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:10:52</t>
+          <t>05:09:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="F17" t="n">
-        <v>6.99</v>
+        <v>6.24</v>
       </c>
       <c r="G17" t="n">
-        <v>329.5</v>
+        <v>336.2</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-96.54000000000001</v>
+        <v>55.34</v>
       </c>
       <c r="K17" t="n">
-        <v>22.46</v>
+        <v>-4.29</v>
       </c>
       <c r="L17" t="n">
-        <v>99.11</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:12:36</t>
+          <t>05:11:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="F18" t="n">
-        <v>6.27</v>
+        <v>6.92</v>
       </c>
       <c r="G18" t="n">
-        <v>331.8</v>
+        <v>344.5</v>
       </c>
       <c r="H18" t="n">
-        <v>98</v>
+        <v>91.8</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>-39.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-54.05</v>
+        <v>-28.25</v>
       </c>
       <c r="L18" t="n">
-        <v>55.16</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:13:44</t>
+          <t>05:13:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="F19" t="n">
-        <v>5.77</v>
+        <v>7.01</v>
       </c>
       <c r="G19" t="n">
-        <v>346.9</v>
+        <v>330.2</v>
       </c>
       <c r="H19" t="n">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>136.61</v>
+        <v>42.22</v>
       </c>
       <c r="K19" t="n">
-        <v>135.1</v>
+        <v>174.49</v>
       </c>
       <c r="L19" t="n">
-        <v>192.13</v>
+        <v>179.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:18:29</t>
+          <t>05:18:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.93</v>
+        <v>1.7</v>
       </c>
       <c r="F20" t="n">
-        <v>6.23</v>
+        <v>5.99</v>
       </c>
       <c r="G20" t="n">
-        <v>324.2</v>
+        <v>339.3</v>
       </c>
       <c r="H20" t="n">
-        <v>97</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>31.48</v>
+        <v>-151.04</v>
       </c>
       <c r="K20" t="n">
-        <v>-247.12</v>
+        <v>192.96</v>
       </c>
       <c r="L20" t="n">
-        <v>249.11</v>
+        <v>245.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:20:42</t>
+          <t>05:20:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="F21" t="n">
-        <v>5.99</v>
+        <v>5.86</v>
       </c>
       <c r="G21" t="n">
-        <v>343.1</v>
+        <v>327.7</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-72.92</v>
+        <v>-92.15000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-114.5</v>
+        <v>-194.15</v>
       </c>
       <c r="L21" t="n">
-        <v>135.75</v>
+        <v>214.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:21:51</t>
+          <t>05:21:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="F22" t="n">
-        <v>6.35</v>
+        <v>6.01</v>
       </c>
       <c r="G22" t="n">
-        <v>332.3</v>
+        <v>333.4</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>29.41</v>
+        <v>-56.85</v>
       </c>
       <c r="K22" t="n">
-        <v>117.72</v>
+        <v>214.32</v>
       </c>
       <c r="L22" t="n">
-        <v>121.34</v>
+        <v>221.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:26:52</t>
+          <t>05:25:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="F23" t="n">
-        <v>6.11</v>
+        <v>6.72</v>
       </c>
       <c r="G23" t="n">
-        <v>343.7</v>
+        <v>326.8</v>
       </c>
       <c r="H23" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-108.69</v>
+        <v>89.75</v>
       </c>
       <c r="K23" t="n">
-        <v>58.94</v>
+        <v>111.89</v>
       </c>
       <c r="L23" t="n">
-        <v>123.64</v>
+        <v>143.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:28:03</t>
+          <t>05:26:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="F24" t="n">
-        <v>6.45</v>
+        <v>6.14</v>
       </c>
       <c r="G24" t="n">
-        <v>338.6</v>
+        <v>336.8</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-62.59</v>
+        <v>-93.73</v>
       </c>
       <c r="K24" t="n">
-        <v>29.73</v>
+        <v>20.2</v>
       </c>
       <c r="L24" t="n">
-        <v>69.29000000000001</v>
+        <v>95.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:29:05</t>
+          <t>05:28:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="F25" t="n">
-        <v>5.92</v>
+        <v>6.35</v>
       </c>
       <c r="G25" t="n">
-        <v>327.3</v>
+        <v>330.2</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-138.8</v>
+        <v>-26.52</v>
       </c>
       <c r="K25" t="n">
-        <v>101.4</v>
+        <v>-162.7</v>
       </c>
       <c r="L25" t="n">
-        <v>171.89</v>
+        <v>164.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:33:41</t>
+          <t>05:34:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="F26" t="n">
-        <v>6.58</v>
+        <v>5.51</v>
       </c>
       <c r="G26" t="n">
-        <v>343.6</v>
+        <v>340</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-245.22</v>
+        <v>-132.18</v>
       </c>
       <c r="K26" t="n">
-        <v>14.22</v>
+        <v>-387.06</v>
       </c>
       <c r="L26" t="n">
-        <v>245.63</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:35:57</t>
+          <t>05:35:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="F27" t="n">
-        <v>6.79</v>
+        <v>6.31</v>
       </c>
       <c r="G27" t="n">
-        <v>322.7</v>
+        <v>333.8</v>
       </c>
       <c r="H27" t="n">
-        <v>93.7</v>
+        <v>92</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>303.51</v>
+        <v>-129.39</v>
       </c>
       <c r="K27" t="n">
-        <v>181.64</v>
+        <v>339.01</v>
       </c>
       <c r="L27" t="n">
-        <v>353.7</v>
+        <v>362.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:38:01</t>
+          <t>05:38:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="F28" t="n">
-        <v>6.58</v>
+        <v>6.28</v>
       </c>
       <c r="G28" t="n">
-        <v>2.8</v>
+        <v>336.5</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-94.45</v>
+        <v>168.68</v>
       </c>
       <c r="K28" t="n">
-        <v>-191.4</v>
+        <v>-62.64</v>
       </c>
       <c r="L28" t="n">
-        <v>213.44</v>
+        <v>179.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:51:14</t>
+          <t>05:48:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="F29" t="n">
-        <v>6.83</v>
+        <v>6.29</v>
       </c>
       <c r="G29" t="n">
-        <v>320.9</v>
+        <v>345.7</v>
       </c>
       <c r="H29" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>58.84</v>
+        <v>-28.66</v>
       </c>
       <c r="K29" t="n">
-        <v>-149.81</v>
+        <v>1.36</v>
       </c>
       <c r="L29" t="n">
-        <v>160.95</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:52:58</t>
+          <t>05:50:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="F30" t="n">
-        <v>5.97</v>
+        <v>6.3</v>
       </c>
       <c r="G30" t="n">
-        <v>326.5</v>
+        <v>334.4</v>
       </c>
       <c r="H30" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-77.31</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-90.13</v>
+        <v>5.22</v>
       </c>
       <c r="L30" t="n">
-        <v>118.75</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:55:45</t>
+          <t>05:50:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.78</v>
+        <v>1.69</v>
       </c>
       <c r="F31" t="n">
-        <v>5.69</v>
+        <v>6.73</v>
       </c>
       <c r="G31" t="n">
-        <v>341.5</v>
+        <v>319.1</v>
       </c>
       <c r="H31" t="n">
-        <v>93.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="I31" t="n">
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-50.43</v>
+        <v>81.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-62.51</v>
+        <v>-13.54</v>
       </c>
       <c r="L31" t="n">
-        <v>80.31</v>
+        <v>82.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:01:13</t>
+          <t>05:55:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="F32" t="n">
-        <v>6.56</v>
+        <v>6.11</v>
       </c>
       <c r="G32" t="n">
-        <v>335.8</v>
+        <v>323.6</v>
       </c>
       <c r="H32" t="n">
-        <v>92.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>150.32</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>57.82</v>
+        <v>-153.88</v>
       </c>
       <c r="L32" t="n">
-        <v>161.06</v>
+        <v>154.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:03:23</t>
+          <t>05:57:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="F33" t="n">
-        <v>6.28</v>
+        <v>6.25</v>
       </c>
       <c r="G33" t="n">
-        <v>329.6</v>
+        <v>331.9</v>
       </c>
       <c r="H33" t="n">
-        <v>91.5</v>
+        <v>95.7</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>35.97</v>
+        <v>-4.34</v>
       </c>
       <c r="K33" t="n">
-        <v>-12.47</v>
+        <v>95.02</v>
       </c>
       <c r="L33" t="n">
-        <v>38.07</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:05:38</t>
+          <t>05:57:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="F34" t="n">
-        <v>6.22</v>
+        <v>6.26</v>
       </c>
       <c r="G34" t="n">
-        <v>322.5</v>
+        <v>338.1</v>
       </c>
       <c r="H34" t="n">
-        <v>98</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-55.45</v>
+        <v>7.4</v>
       </c>
       <c r="K34" t="n">
-        <v>152.32</v>
+        <v>-103.12</v>
       </c>
       <c r="L34" t="n">
-        <v>162.1</v>
+        <v>103.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:09:31</t>
+          <t>06:03:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="F35" t="n">
-        <v>5.85</v>
+        <v>6.49</v>
       </c>
       <c r="G35" t="n">
-        <v>330.3</v>
+        <v>324.7</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-91.92</v>
+        <v>90.44</v>
       </c>
       <c r="K35" t="n">
-        <v>-44.45</v>
+        <v>-122.01</v>
       </c>
       <c r="L35" t="n">
-        <v>102.1</v>
+        <v>151.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:10:59</t>
+          <t>06:04:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="F36" t="n">
-        <v>6.24</v>
+        <v>6.06</v>
       </c>
       <c r="G36" t="n">
-        <v>325.1</v>
+        <v>335.6</v>
       </c>
       <c r="H36" t="n">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-190.02</v>
+        <v>244.39</v>
       </c>
       <c r="K36" t="n">
-        <v>53.9</v>
+        <v>-183.25</v>
       </c>
       <c r="L36" t="n">
-        <v>197.52</v>
+        <v>305.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:12:43</t>
+          <t>06:07:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>6.56</v>
+        <v>6.86</v>
       </c>
       <c r="G37" t="n">
-        <v>322</v>
+        <v>320.2</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>87.84</v>
+        <v>-26.42</v>
       </c>
       <c r="K37" t="n">
-        <v>-70.16</v>
+        <v>126.1</v>
       </c>
       <c r="L37" t="n">
-        <v>112.42</v>
+        <v>128.84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:16:00</t>
+          <t>06:10:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="F38" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>320.3</v>
+        <v>328.8</v>
       </c>
       <c r="H38" t="n">
-        <v>97.3</v>
+        <v>91.2</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>112.38</v>
+        <v>-233.15</v>
       </c>
       <c r="K38" t="n">
-        <v>-197.33</v>
+        <v>141.15</v>
       </c>
       <c r="L38" t="n">
-        <v>227.09</v>
+        <v>272.55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:17:53</t>
+          <t>06:12:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="F39" t="n">
-        <v>6.81</v>
+        <v>6.08</v>
       </c>
       <c r="G39" t="n">
-        <v>323.3</v>
+        <v>324.8</v>
       </c>
       <c r="H39" t="n">
-        <v>96.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-254.44</v>
+        <v>-24.15</v>
       </c>
       <c r="K39" t="n">
-        <v>-315.56</v>
+        <v>-144.72</v>
       </c>
       <c r="L39" t="n">
-        <v>405.36</v>
+        <v>146.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:20:14</t>
+          <t>06:14:10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="F40" t="n">
-        <v>6.51</v>
+        <v>6.78</v>
       </c>
       <c r="G40" t="n">
-        <v>337.3</v>
+        <v>331.7</v>
       </c>
       <c r="H40" t="n">
-        <v>92.2</v>
+        <v>98</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>390.08</v>
+        <v>108.27</v>
       </c>
       <c r="K40" t="n">
-        <v>193.02</v>
+        <v>210.22</v>
       </c>
       <c r="L40" t="n">
-        <v>435.22</v>
+        <v>236.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:25:55</t>
+          <t>06:19:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="F41" t="n">
-        <v>6.48</v>
+        <v>6.22</v>
       </c>
       <c r="G41" t="n">
-        <v>331.4</v>
+        <v>336.3</v>
       </c>
       <c r="H41" t="n">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-45.28</v>
+        <v>-104.65</v>
       </c>
       <c r="K41" t="n">
-        <v>-86.29000000000001</v>
+        <v>197.15</v>
       </c>
       <c r="L41" t="n">
-        <v>97.45</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:27:42</t>
+          <t>06:20:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="F42" t="n">
-        <v>5.83</v>
+        <v>6.21</v>
       </c>
       <c r="G42" t="n">
-        <v>332.2</v>
+        <v>344.4</v>
       </c>
       <c r="H42" t="n">
-        <v>98.2</v>
+        <v>87.2</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>46.69</v>
+        <v>340.14</v>
       </c>
       <c r="K42" t="n">
-        <v>-91.59999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="L42" t="n">
-        <v>102.82</v>
+        <v>351.76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:28:28</t>
+          <t>06:22:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="F43" t="n">
-        <v>6.37</v>
+        <v>6.87</v>
       </c>
       <c r="G43" t="n">
-        <v>341.1</v>
+        <v>332.3</v>
       </c>
       <c r="H43" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>400.38</v>
+        <v>-92.98</v>
       </c>
       <c r="K43" t="n">
-        <v>-69.56</v>
+        <v>424.33</v>
       </c>
       <c r="L43" t="n">
-        <v>406.38</v>
+        <v>434.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:39:04</t>
+          <t>06:33:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="F44" t="n">
-        <v>6.41</v>
+        <v>5.67</v>
       </c>
       <c r="G44" t="n">
-        <v>332.1</v>
+        <v>346.4</v>
       </c>
       <c r="H44" t="n">
-        <v>93.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>9.630000000000001</v>
+        <v>-32.28</v>
       </c>
       <c r="K44" t="n">
-        <v>2.36</v>
+        <v>-25.08</v>
       </c>
       <c r="L44" t="n">
-        <v>9.92</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:40:03</t>
+          <t>06:34:51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="F45" t="n">
-        <v>6.49</v>
+        <v>6.03</v>
       </c>
       <c r="G45" t="n">
-        <v>335.9</v>
+        <v>336.5</v>
       </c>
       <c r="H45" t="n">
-        <v>95.2</v>
+        <v>92.2</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>98.06</v>
+        <v>-36.01</v>
       </c>
       <c r="K45" t="n">
-        <v>-21.27</v>
+        <v>23.49</v>
       </c>
       <c r="L45" t="n">
-        <v>100.34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:42:32</t>
+          <t>06:36:55</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="F46" t="n">
-        <v>6.21</v>
+        <v>6.18</v>
       </c>
       <c r="G46" t="n">
-        <v>333.8</v>
+        <v>339.3</v>
       </c>
       <c r="H46" t="n">
-        <v>98.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>66.3</v>
+        <v>5.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-77.27</v>
+        <v>36.78</v>
       </c>
       <c r="L46" t="n">
-        <v>101.81</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:46:44</t>
+          <t>06:41:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.99</v>
+        <v>1.54</v>
       </c>
       <c r="F47" t="n">
-        <v>6.13</v>
+        <v>6.58</v>
       </c>
       <c r="G47" t="n">
-        <v>343.1</v>
+        <v>324.5</v>
       </c>
       <c r="H47" t="n">
         <v>95.8</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.87</v>
+        <v>-119.7</v>
       </c>
       <c r="K47" t="n">
-        <v>-27.62</v>
+        <v>-23.96</v>
       </c>
       <c r="L47" t="n">
-        <v>27.89</v>
+        <v>122.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:49:05</t>
+          <t>06:43:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="F48" t="n">
-        <v>6.53</v>
+        <v>6.14</v>
       </c>
       <c r="G48" t="n">
-        <v>325.8</v>
+        <v>327.4</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-148.61</v>
+        <v>-58.02</v>
       </c>
       <c r="K48" t="n">
-        <v>65.63</v>
+        <v>128.92</v>
       </c>
       <c r="L48" t="n">
-        <v>162.46</v>
+        <v>141.38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:50:43</t>
+          <t>06:45:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="F49" t="n">
-        <v>5.98</v>
+        <v>6.06</v>
       </c>
       <c r="G49" t="n">
-        <v>338</v>
+        <v>340.3</v>
       </c>
       <c r="H49" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-241.5</v>
+        <v>-130.47</v>
       </c>
       <c r="K49" t="n">
-        <v>204.34</v>
+        <v>5.56</v>
       </c>
       <c r="L49" t="n">
-        <v>316.35</v>
+        <v>130.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:55:09</t>
+          <t>06:50:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="F50" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="G50" t="n">
-        <v>315.8</v>
+        <v>328.5</v>
       </c>
       <c r="H50" t="n">
-        <v>96</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I50" t="n">
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>35.48</v>
+        <v>243.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-105.66</v>
+        <v>18.23</v>
       </c>
       <c r="L50" t="n">
-        <v>111.46</v>
+        <v>244.48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:56:15</t>
+          <t>06:52:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="F51" t="n">
-        <v>6.81</v>
+        <v>6.74</v>
       </c>
       <c r="G51" t="n">
-        <v>343.7</v>
+        <v>324</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-225.11</v>
+        <v>11.83</v>
       </c>
       <c r="K51" t="n">
-        <v>225.87</v>
+        <v>138.03</v>
       </c>
       <c r="L51" t="n">
-        <v>318.89</v>
+        <v>138.54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:57:37</t>
+          <t>06:54:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="F52" t="n">
-        <v>5.57</v>
+        <v>6.53</v>
       </c>
       <c r="G52" t="n">
-        <v>325.9</v>
+        <v>331.7</v>
       </c>
       <c r="H52" t="n">
-        <v>91.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-152.48</v>
+        <v>28.73</v>
       </c>
       <c r="K52" t="n">
-        <v>-232.41</v>
+        <v>114.81</v>
       </c>
       <c r="L52" t="n">
-        <v>277.96</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:02:06</t>
+          <t>06:59:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="F53" t="n">
-        <v>5.34</v>
+        <v>5.58</v>
       </c>
       <c r="G53" t="n">
-        <v>324.5</v>
+        <v>337.8</v>
       </c>
       <c r="H53" t="n">
-        <v>91.5</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>44.35</v>
+        <v>-93.40000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-175.58</v>
+        <v>242.56</v>
       </c>
       <c r="L53" t="n">
-        <v>181.09</v>
+        <v>259.92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:03:57</t>
+          <t>07:01:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="F54" t="n">
-        <v>6.29</v>
+        <v>6.2</v>
       </c>
       <c r="G54" t="n">
-        <v>332.5</v>
+        <v>335.6</v>
       </c>
       <c r="H54" t="n">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-225.91</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>105.39</v>
+        <v>174.82</v>
       </c>
       <c r="L54" t="n">
-        <v>249.28</v>
+        <v>188.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:05:36</t>
+          <t>07:02:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.77</v>
+        <v>1.43</v>
       </c>
       <c r="F55" t="n">
-        <v>5.58</v>
+        <v>6.15</v>
       </c>
       <c r="G55" t="n">
-        <v>338</v>
+        <v>338.3</v>
       </c>
       <c r="H55" t="n">
-        <v>95.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-466.49</v>
+        <v>171.74</v>
       </c>
       <c r="K55" t="n">
-        <v>0.48</v>
+        <v>-329.63</v>
       </c>
       <c r="L55" t="n">
-        <v>466.49</v>
+        <v>371.68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:10:14</t>
+          <t>07:07:21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="F56" t="n">
-        <v>6.37</v>
+        <v>6.79</v>
       </c>
       <c r="G56" t="n">
         <v>333.3</v>
       </c>
       <c r="H56" t="n">
-        <v>95.7</v>
+        <v>93</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-109.82</v>
+        <v>-50.66</v>
       </c>
       <c r="K56" t="n">
-        <v>-217.74</v>
+        <v>272.39</v>
       </c>
       <c r="L56" t="n">
-        <v>243.87</v>
+        <v>277.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:11:50</t>
+          <t>07:09:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.83</v>
+        <v>2.94</v>
       </c>
       <c r="F57" t="n">
-        <v>6.5</v>
+        <v>5.88</v>
       </c>
       <c r="G57" t="n">
-        <v>325.2</v>
+        <v>330.3</v>
       </c>
       <c r="H57" t="n">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>372.07</v>
+        <v>270.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-128.99</v>
+        <v>-149.92</v>
       </c>
       <c r="L57" t="n">
-        <v>393.79</v>
+        <v>309.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:13:21</t>
+          <t>07:11:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="F58" t="n">
-        <v>5.63</v>
+        <v>6.23</v>
       </c>
       <c r="G58" t="n">
-        <v>331.5</v>
+        <v>330.2</v>
       </c>
       <c r="H58" t="n">
-        <v>99.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>222.75</v>
+        <v>319.51</v>
       </c>
       <c r="K58" t="n">
-        <v>-238.03</v>
+        <v>-334.17</v>
       </c>
       <c r="L58" t="n">
-        <v>326</v>
+        <v>462.34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:26:44</t>
+          <t>07:20:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="F59" t="n">
-        <v>6.71</v>
+        <v>6.44</v>
       </c>
       <c r="G59" t="n">
-        <v>329.2</v>
+        <v>333.9</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>18.9</v>
+        <v>40.39</v>
       </c>
       <c r="K59" t="n">
-        <v>90.23</v>
+        <v>-70.52</v>
       </c>
       <c r="L59" t="n">
-        <v>92.19</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:28:23</t>
+          <t>07:21:51</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="F60" t="n">
-        <v>6.99</v>
+        <v>6.25</v>
       </c>
       <c r="G60" t="n">
-        <v>331.6</v>
+        <v>318.6</v>
       </c>
       <c r="H60" t="n">
-        <v>96.8</v>
+        <v>97.3</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-50.38</v>
+        <v>-95.03</v>
       </c>
       <c r="K60" t="n">
-        <v>-11.6</v>
+        <v>-28.68</v>
       </c>
       <c r="L60" t="n">
-        <v>51.69</v>
+        <v>99.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:30:41</t>
+          <t>07:23:04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="F61" t="n">
-        <v>6.26</v>
+        <v>6.28</v>
       </c>
       <c r="G61" t="n">
-        <v>338.4</v>
+        <v>333.4</v>
       </c>
       <c r="H61" t="n">
-        <v>92.2</v>
+        <v>90</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>26.41</v>
+        <v>-26.5</v>
       </c>
       <c r="K61" t="n">
-        <v>62.68</v>
+        <v>-52.8</v>
       </c>
       <c r="L61" t="n">
-        <v>68.02</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:34:54</t>
+          <t>07:26:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="F62" t="n">
-        <v>7.1</v>
+        <v>6.22</v>
       </c>
       <c r="G62" t="n">
-        <v>320</v>
+        <v>331.8</v>
       </c>
       <c r="H62" t="n">
-        <v>99.5</v>
+        <v>96.7</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>52.04</v>
+        <v>-29.66</v>
       </c>
       <c r="K62" t="n">
-        <v>-35.73</v>
+        <v>207.28</v>
       </c>
       <c r="L62" t="n">
-        <v>63.12</v>
+        <v>209.39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:37:11</t>
+          <t>07:28:33</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="F63" t="n">
-        <v>6.09</v>
+        <v>6.64</v>
       </c>
       <c r="G63" t="n">
-        <v>333.7</v>
+        <v>319.6</v>
       </c>
       <c r="H63" t="n">
-        <v>92.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>68.54000000000001</v>
+        <v>79.62</v>
       </c>
       <c r="K63" t="n">
-        <v>63.03</v>
+        <v>-17.31</v>
       </c>
       <c r="L63" t="n">
-        <v>93.11</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:37:52</t>
+          <t>07:29:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="F64" t="n">
-        <v>6.46</v>
+        <v>6.47</v>
       </c>
       <c r="G64" t="n">
-        <v>335.1</v>
+        <v>338.4</v>
       </c>
       <c r="H64" t="n">
-        <v>96.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>18.78</v>
+        <v>50.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-133.32</v>
+        <v>103.38</v>
       </c>
       <c r="L64" t="n">
-        <v>134.63</v>
+        <v>115.13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:42:04</t>
+          <t>07:34:39</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="F65" t="n">
-        <v>6.34</v>
+        <v>6.35</v>
       </c>
       <c r="G65" t="n">
-        <v>328.8</v>
+        <v>332.6</v>
       </c>
       <c r="H65" t="n">
-        <v>96.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>204.32</v>
+        <v>-22.45</v>
       </c>
       <c r="K65" t="n">
-        <v>-17.05</v>
+        <v>52.8</v>
       </c>
       <c r="L65" t="n">
-        <v>205.03</v>
+        <v>57.37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:43:23</t>
+          <t>07:37:13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="F66" t="n">
-        <v>7.12</v>
+        <v>6.57</v>
       </c>
       <c r="G66" t="n">
-        <v>332.8</v>
+        <v>336.8</v>
       </c>
       <c r="H66" t="n">
-        <v>89.3</v>
+        <v>96.7</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-31.97</v>
+        <v>-171.27</v>
       </c>
       <c r="K66" t="n">
-        <v>146.3</v>
+        <v>226.56</v>
       </c>
       <c r="L66" t="n">
-        <v>149.75</v>
+        <v>284.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:44:34</t>
+          <t>07:39:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>6.85</v>
       </c>
       <c r="G67" t="n">
-        <v>332.3</v>
+        <v>343</v>
       </c>
       <c r="H67" t="n">
-        <v>96.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-63.35</v>
+        <v>-19.62</v>
       </c>
       <c r="K67" t="n">
-        <v>-265.48</v>
+        <v>107.49</v>
       </c>
       <c r="L67" t="n">
-        <v>272.94</v>
+        <v>109.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:49:48</t>
+          <t>07:43:51</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="F68" t="n">
-        <v>6.05</v>
+        <v>6.4</v>
       </c>
       <c r="G68" t="n">
-        <v>328</v>
+        <v>327.1</v>
       </c>
       <c r="H68" t="n">
-        <v>95.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-26.35</v>
+        <v>116.79</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.28</v>
+        <v>-115.75</v>
       </c>
       <c r="L68" t="n">
-        <v>26.35</v>
+        <v>164.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:51:31</t>
+          <t>07:44:57</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="F69" t="n">
-        <v>6.92</v>
+        <v>6.71</v>
       </c>
       <c r="G69" t="n">
-        <v>327.1</v>
+        <v>322</v>
       </c>
       <c r="H69" t="n">
-        <v>96.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-47.82</v>
+        <v>-130.77</v>
       </c>
       <c r="K69" t="n">
-        <v>164.05</v>
+        <v>230.63</v>
       </c>
       <c r="L69" t="n">
-        <v>170.88</v>
+        <v>265.12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:53:37</t>
+          <t>07:46:06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="F70" t="n">
-        <v>6.34</v>
+        <v>6.64</v>
       </c>
       <c r="G70" t="n">
-        <v>332.2</v>
+        <v>337.3</v>
       </c>
       <c r="H70" t="n">
-        <v>97.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>316.6</v>
+        <v>98.2</v>
       </c>
       <c r="K70" t="n">
-        <v>105.24</v>
+        <v>26.02</v>
       </c>
       <c r="L70" t="n">
-        <v>333.63</v>
+        <v>101.59</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:57:49</t>
+          <t>07:52:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="F71" t="n">
-        <v>5.99</v>
+        <v>6.32</v>
       </c>
       <c r="G71" t="n">
-        <v>342.5</v>
+        <v>325.1</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>647.46</v>
+        <v>-312.59</v>
       </c>
       <c r="K71" t="n">
-        <v>71.76000000000001</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>651.42</v>
+        <v>319.61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:58:58</t>
+          <t>07:54:54</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="F72" t="n">
-        <v>5.89</v>
+        <v>6.15</v>
       </c>
       <c r="G72" t="n">
-        <v>341.5</v>
+        <v>318.1</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-136.18</v>
+        <v>-269</v>
       </c>
       <c r="K72" t="n">
-        <v>305.35</v>
+        <v>206.51</v>
       </c>
       <c r="L72" t="n">
-        <v>334.34</v>
+        <v>339.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:01:03</t>
+          <t>07:56:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="F73" t="n">
-        <v>6.35</v>
+        <v>5.79</v>
       </c>
       <c r="G73" t="n">
-        <v>323.4</v>
+        <v>331.5</v>
       </c>
       <c r="H73" t="n">
-        <v>91.8</v>
+        <v>93.5</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-362.82</v>
+        <v>-249.44</v>
       </c>
       <c r="K73" t="n">
-        <v>137.13</v>
+        <v>254.32</v>
       </c>
       <c r="L73" t="n">
-        <v>387.87</v>
+        <v>356.23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:09:43</t>
+          <t>08:04:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="F74" t="n">
-        <v>5.58</v>
+        <v>6.45</v>
       </c>
       <c r="G74" t="n">
-        <v>334</v>
+        <v>325.2</v>
       </c>
       <c r="H74" t="n">
-        <v>89.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-132.24</v>
+        <v>119.72</v>
       </c>
       <c r="K74" t="n">
-        <v>29.38</v>
+        <v>3.81</v>
       </c>
       <c r="L74" t="n">
-        <v>135.47</v>
+        <v>119.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:11:27</t>
+          <t>08:07:33</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.77</v>
+        <v>2.33</v>
       </c>
       <c r="F75" t="n">
-        <v>6.01</v>
+        <v>5.36</v>
       </c>
       <c r="G75" t="n">
-        <v>335.4</v>
+        <v>334</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-64.02</v>
+        <v>42.71</v>
       </c>
       <c r="K75" t="n">
-        <v>2.88</v>
+        <v>-120.64</v>
       </c>
       <c r="L75" t="n">
-        <v>64.08</v>
+        <v>127.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:12:18</t>
+          <t>08:08:51</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="F76" t="n">
-        <v>6.52</v>
+        <v>6.11</v>
       </c>
       <c r="G76" t="n">
-        <v>330.8</v>
+        <v>322.8</v>
       </c>
       <c r="H76" t="n">
-        <v>95.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I76" t="n">
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>54.47</v>
+        <v>-17.3</v>
       </c>
       <c r="K76" t="n">
-        <v>-35.89</v>
+        <v>17.89</v>
       </c>
       <c r="L76" t="n">
-        <v>65.23999999999999</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:16:07</t>
+          <t>08:12:28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="F77" t="n">
-        <v>6.16</v>
+        <v>6.33</v>
       </c>
       <c r="G77" t="n">
-        <v>319.9</v>
+        <v>322.3</v>
       </c>
       <c r="H77" t="n">
         <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-41.54</v>
+        <v>110.35</v>
       </c>
       <c r="K77" t="n">
-        <v>-41.74</v>
+        <v>-39.68</v>
       </c>
       <c r="L77" t="n">
-        <v>58.89</v>
+        <v>117.27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:18:22</t>
+          <t>08:13:41</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="F78" t="n">
-        <v>6.32</v>
+        <v>7.04</v>
       </c>
       <c r="G78" t="n">
-        <v>302.4</v>
+        <v>335.5</v>
       </c>
       <c r="H78" t="n">
-        <v>96.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-12.49</v>
+        <v>61.7</v>
       </c>
       <c r="K78" t="n">
-        <v>80.09999999999999</v>
+        <v>77.22</v>
       </c>
       <c r="L78" t="n">
-        <v>81.06999999999999</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:19:47</t>
+          <t>08:14:46</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="F79" t="n">
-        <v>6.86</v>
+        <v>6.2</v>
       </c>
       <c r="G79" t="n">
-        <v>329.1</v>
+        <v>347.9</v>
       </c>
       <c r="H79" t="n">
-        <v>91.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>109.5</v>
+        <v>102.71</v>
       </c>
       <c r="K79" t="n">
-        <v>-67.17</v>
+        <v>-82.95999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>128.46</v>
+        <v>132.03</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:24:52</t>
+          <t>08:19:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>6.52</v>
       </c>
       <c r="G80" t="n">
-        <v>332.6</v>
+        <v>318.1</v>
       </c>
       <c r="H80" t="n">
-        <v>99.2</v>
+        <v>96.8</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-285.86</v>
+        <v>199.01</v>
       </c>
       <c r="K80" t="n">
-        <v>77.16</v>
+        <v>-75.39</v>
       </c>
       <c r="L80" t="n">
-        <v>296.09</v>
+        <v>212.81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:26:32</t>
+          <t>08:21:21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="F81" t="n">
-        <v>6.26</v>
+        <v>5.96</v>
       </c>
       <c r="G81" t="n">
-        <v>328.4</v>
+        <v>333.7</v>
       </c>
       <c r="H81" t="n">
-        <v>94.8</v>
+        <v>95.8</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-167.01</v>
+        <v>-50.31</v>
       </c>
       <c r="K81" t="n">
-        <v>11.14</v>
+        <v>-39.78</v>
       </c>
       <c r="L81" t="n">
-        <v>167.38</v>
+        <v>64.14</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:28:15</t>
+          <t>08:22:46</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="F82" t="n">
-        <v>6.15</v>
+        <v>6.06</v>
       </c>
       <c r="G82" t="n">
-        <v>336.1</v>
+        <v>331.9</v>
       </c>
       <c r="H82" t="n">
-        <v>99.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>86.09999999999999</v>
+        <v>-40.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-361.38</v>
+        <v>-0.44</v>
       </c>
       <c r="L82" t="n">
-        <v>371.5</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:32:16</t>
+          <t>08:27:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.56</v>
+        <v>3.19</v>
       </c>
       <c r="F83" t="n">
-        <v>6.9</v>
+        <v>6.19</v>
       </c>
       <c r="G83" t="n">
-        <v>331.2</v>
+        <v>324.8</v>
       </c>
       <c r="H83" t="n">
-        <v>99.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-752.48</v>
+        <v>406.89</v>
       </c>
       <c r="K83" t="n">
-        <v>-87.91</v>
+        <v>30</v>
       </c>
       <c r="L83" t="n">
-        <v>757.6</v>
+        <v>407.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:33:54</t>
+          <t>08:28:58</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="F84" t="n">
-        <v>6.86</v>
+        <v>5.93</v>
       </c>
       <c r="G84" t="n">
-        <v>336.2</v>
+        <v>329.2</v>
       </c>
       <c r="H84" t="n">
-        <v>97.2</v>
+        <v>91.7</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-251.58</v>
+        <v>-554.1900000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>-115.2</v>
+        <v>-220</v>
       </c>
       <c r="L84" t="n">
-        <v>276.7</v>
+        <v>596.27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:36:32</t>
+          <t>08:30:25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="F85" t="n">
         <v>6.12</v>
       </c>
       <c r="G85" t="n">
-        <v>329.3</v>
+        <v>336</v>
       </c>
       <c r="H85" t="n">
-        <v>95.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-65.58</v>
+        <v>253.76</v>
       </c>
       <c r="K85" t="n">
-        <v>275.85</v>
+        <v>32.35</v>
       </c>
       <c r="L85" t="n">
-        <v>283.54</v>
+        <v>255.81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:40:47</t>
+          <t>08:34:28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="F86" t="n">
-        <v>6.78</v>
+        <v>6.83</v>
       </c>
       <c r="G86" t="n">
-        <v>330.7</v>
+        <v>329.3</v>
       </c>
       <c r="H86" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>170.91</v>
+        <v>-344.23</v>
       </c>
       <c r="K86" t="n">
-        <v>-151.76</v>
+        <v>-120.21</v>
       </c>
       <c r="L86" t="n">
-        <v>228.56</v>
+        <v>364.61</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:42:10</t>
+          <t>08:36:11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>6.52</v>
       </c>
       <c r="G87" t="n">
-        <v>331.3</v>
+        <v>331</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>427.08</v>
+        <v>329.27</v>
       </c>
       <c r="K87" t="n">
-        <v>40.17</v>
+        <v>-72</v>
       </c>
       <c r="L87" t="n">
-        <v>428.96</v>
+        <v>337.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:44:00</t>
+          <t>08:36:53</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.71</v>
+        <v>2.11</v>
       </c>
       <c r="F88" t="n">
-        <v>6.68</v>
+        <v>5.45</v>
       </c>
       <c r="G88" t="n">
-        <v>328</v>
+        <v>329.8</v>
       </c>
       <c r="H88" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>119.33</v>
+        <v>43.07</v>
       </c>
       <c r="K88" t="n">
-        <v>-379.35</v>
+        <v>-274.01</v>
       </c>
       <c r="L88" t="n">
-        <v>397.67</v>
+        <v>277.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.83</v>
+        <v>-9.49</v>
       </c>
       <c r="K14" t="n">
-        <v>116.09</v>
+        <v>79.69</v>
       </c>
       <c r="L14" t="n">
-        <v>116.91</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>92.19</v>
+        <v>74.08</v>
       </c>
       <c r="K15" t="n">
-        <v>52.63</v>
+        <v>42.29</v>
       </c>
       <c r="L15" t="n">
-        <v>106.15</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>34.78</v>
+        <v>42.37</v>
       </c>
       <c r="K16" t="n">
-        <v>22.72</v>
+        <v>27.68</v>
       </c>
       <c r="L16" t="n">
-        <v>41.54</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>55.34</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.29</v>
+        <v>-5.08</v>
       </c>
       <c r="L17" t="n">
-        <v>55.51</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-39.8</v>
+        <v>-48.82</v>
       </c>
       <c r="K18" t="n">
-        <v>-28.25</v>
+        <v>-34.64</v>
       </c>
       <c r="L18" t="n">
-        <v>48.81</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>42.22</v>
+        <v>30.02</v>
       </c>
       <c r="K19" t="n">
-        <v>174.49</v>
+        <v>124.05</v>
       </c>
       <c r="L19" t="n">
-        <v>179.52</v>
+        <v>127.63</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-151.04</v>
+        <v>-133.62</v>
       </c>
       <c r="K20" t="n">
-        <v>192.96</v>
+        <v>170.71</v>
       </c>
       <c r="L20" t="n">
-        <v>245.05</v>
+        <v>216.79</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-92.15000000000001</v>
+        <v>-85.42</v>
       </c>
       <c r="K21" t="n">
-        <v>-194.15</v>
+        <v>-179.98</v>
       </c>
       <c r="L21" t="n">
-        <v>214.91</v>
+        <v>199.23</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-56.85</v>
+        <v>-49.14</v>
       </c>
       <c r="K22" t="n">
-        <v>214.32</v>
+        <v>185.26</v>
       </c>
       <c r="L22" t="n">
-        <v>221.73</v>
+        <v>191.66</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>89.75</v>
+        <v>107.93</v>
       </c>
       <c r="K23" t="n">
-        <v>111.89</v>
+        <v>134.55</v>
       </c>
       <c r="L23" t="n">
-        <v>143.44</v>
+        <v>172.49</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-93.73</v>
+        <v>-158.74</v>
       </c>
       <c r="K24" t="n">
-        <v>20.2</v>
+        <v>34.21</v>
       </c>
       <c r="L24" t="n">
-        <v>95.88</v>
+        <v>162.38</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-26.52</v>
+        <v>-37.63</v>
       </c>
       <c r="K25" t="n">
-        <v>-162.7</v>
+        <v>-230.87</v>
       </c>
       <c r="L25" t="n">
-        <v>164.85</v>
+        <v>233.92</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-132.18</v>
+        <v>-158.11</v>
       </c>
       <c r="K26" t="n">
-        <v>-387.06</v>
+        <v>-462.99</v>
       </c>
       <c r="L26" t="n">
-        <v>409</v>
+        <v>489.24</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-129.39</v>
+        <v>-140.59</v>
       </c>
       <c r="K27" t="n">
-        <v>339.01</v>
+        <v>368.34</v>
       </c>
       <c r="L27" t="n">
-        <v>362.86</v>
+        <v>394.26</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>168.68</v>
+        <v>259.12</v>
       </c>
       <c r="K28" t="n">
-        <v>-62.64</v>
+        <v>-96.23</v>
       </c>
       <c r="L28" t="n">
-        <v>179.93</v>
+        <v>276.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-28.66</v>
+        <v>-39.03</v>
       </c>
       <c r="K29" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="L29" t="n">
-        <v>28.69</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>92.93000000000001</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>5.22</v>
+        <v>4.78</v>
       </c>
       <c r="L30" t="n">
-        <v>93.08</v>
+        <v>85.28</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>81.3</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-13.54</v>
+        <v>-13.17</v>
       </c>
       <c r="L31" t="n">
-        <v>82.42</v>
+        <v>80.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>9.890000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-153.88</v>
+        <v>-134.43</v>
       </c>
       <c r="L32" t="n">
-        <v>154.2</v>
+        <v>134.71</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.34</v>
+        <v>-4.35</v>
       </c>
       <c r="K33" t="n">
-        <v>95.02</v>
+        <v>95.22</v>
       </c>
       <c r="L33" t="n">
-        <v>95.12</v>
+        <v>95.31999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-103.12</v>
+        <v>-100.26</v>
       </c>
       <c r="L34" t="n">
-        <v>103.38</v>
+        <v>100.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>90.44</v>
+        <v>93.98</v>
       </c>
       <c r="K35" t="n">
-        <v>-122.01</v>
+        <v>-126.78</v>
       </c>
       <c r="L35" t="n">
-        <v>151.87</v>
+        <v>157.82</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>244.39</v>
+        <v>184.86</v>
       </c>
       <c r="K36" t="n">
-        <v>-183.25</v>
+        <v>-138.62</v>
       </c>
       <c r="L36" t="n">
-        <v>305.46</v>
+        <v>231.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-26.42</v>
+        <v>-26.15</v>
       </c>
       <c r="K37" t="n">
-        <v>126.1</v>
+        <v>124.83</v>
       </c>
       <c r="L37" t="n">
-        <v>128.84</v>
+        <v>127.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-233.15</v>
+        <v>-234.95</v>
       </c>
       <c r="K38" t="n">
-        <v>141.15</v>
+        <v>142.24</v>
       </c>
       <c r="L38" t="n">
-        <v>272.55</v>
+        <v>274.65</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-24.15</v>
+        <v>-31.4</v>
       </c>
       <c r="K39" t="n">
-        <v>-144.72</v>
+        <v>-188.22</v>
       </c>
       <c r="L39" t="n">
-        <v>146.72</v>
+        <v>190.82</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>108.27</v>
+        <v>119.89</v>
       </c>
       <c r="K40" t="n">
-        <v>210.22</v>
+        <v>232.77</v>
       </c>
       <c r="L40" t="n">
-        <v>236.46</v>
+        <v>261.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-104.65</v>
+        <v>-134.36</v>
       </c>
       <c r="K41" t="n">
-        <v>197.15</v>
+        <v>253.12</v>
       </c>
       <c r="L41" t="n">
-        <v>223.2</v>
+        <v>286.57</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>340.14</v>
+        <v>374.54</v>
       </c>
       <c r="K42" t="n">
-        <v>89.66</v>
+        <v>98.73</v>
       </c>
       <c r="L42" t="n">
-        <v>351.76</v>
+        <v>387.33</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-92.98</v>
+        <v>-98.88</v>
       </c>
       <c r="K43" t="n">
-        <v>424.33</v>
+        <v>451.26</v>
       </c>
       <c r="L43" t="n">
-        <v>434.4</v>
+        <v>461.96</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-32.28</v>
+        <v>-36.59</v>
       </c>
       <c r="K44" t="n">
-        <v>-25.08</v>
+        <v>-28.43</v>
       </c>
       <c r="L44" t="n">
-        <v>40.88</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.01</v>
+        <v>-45.44</v>
       </c>
       <c r="K45" t="n">
-        <v>23.49</v>
+        <v>29.65</v>
       </c>
       <c r="L45" t="n">
-        <v>43</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>5.44</v>
+        <v>6.71</v>
       </c>
       <c r="K46" t="n">
-        <v>36.78</v>
+        <v>45.36</v>
       </c>
       <c r="L46" t="n">
-        <v>37.18</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-119.7</v>
+        <v>-102.76</v>
       </c>
       <c r="K47" t="n">
-        <v>-23.96</v>
+        <v>-20.57</v>
       </c>
       <c r="L47" t="n">
-        <v>122.07</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.02</v>
+        <v>-50.22</v>
       </c>
       <c r="K48" t="n">
-        <v>128.92</v>
+        <v>111.58</v>
       </c>
       <c r="L48" t="n">
-        <v>141.38</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-130.47</v>
+        <v>-108.43</v>
       </c>
       <c r="K49" t="n">
-        <v>5.56</v>
+        <v>4.62</v>
       </c>
       <c r="L49" t="n">
-        <v>130.59</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>243.8</v>
+        <v>228.27</v>
       </c>
       <c r="K50" t="n">
-        <v>18.23</v>
+        <v>17.07</v>
       </c>
       <c r="L50" t="n">
-        <v>244.48</v>
+        <v>228.91</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>11.83</v>
+        <v>11.18</v>
       </c>
       <c r="K51" t="n">
-        <v>138.03</v>
+        <v>130.39</v>
       </c>
       <c r="L51" t="n">
-        <v>138.54</v>
+        <v>130.87</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>28.73</v>
+        <v>31.25</v>
       </c>
       <c r="K52" t="n">
-        <v>114.81</v>
+        <v>124.85</v>
       </c>
       <c r="L52" t="n">
-        <v>118.35</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-93.40000000000001</v>
+        <v>-85.56</v>
       </c>
       <c r="K53" t="n">
-        <v>242.56</v>
+        <v>222.2</v>
       </c>
       <c r="L53" t="n">
-        <v>259.92</v>
+        <v>238.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>71.79000000000001</v>
+        <v>85.06</v>
       </c>
       <c r="K54" t="n">
-        <v>174.82</v>
+        <v>207.15</v>
       </c>
       <c r="L54" t="n">
-        <v>188.98</v>
+        <v>223.93</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>171.74</v>
+        <v>188.55</v>
       </c>
       <c r="K55" t="n">
-        <v>-329.63</v>
+        <v>-361.88</v>
       </c>
       <c r="L55" t="n">
-        <v>371.68</v>
+        <v>408.05</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-50.66</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>272.39</v>
+        <v>360.06</v>
       </c>
       <c r="L56" t="n">
-        <v>277.06</v>
+        <v>366.24</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>270.65</v>
+        <v>409.11</v>
       </c>
       <c r="K57" t="n">
-        <v>-149.92</v>
+        <v>-226.62</v>
       </c>
       <c r="L57" t="n">
-        <v>309.4</v>
+        <v>467.68</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>319.51</v>
+        <v>364.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-334.17</v>
+        <v>-381.59</v>
       </c>
       <c r="L58" t="n">
-        <v>462.34</v>
+        <v>527.9400000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>40.39</v>
+        <v>31.61</v>
       </c>
       <c r="K59" t="n">
-        <v>-70.52</v>
+        <v>-55.19</v>
       </c>
       <c r="L59" t="n">
-        <v>81.27</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-95.03</v>
+        <v>-77.53</v>
       </c>
       <c r="K60" t="n">
-        <v>-28.68</v>
+        <v>-23.4</v>
       </c>
       <c r="L60" t="n">
-        <v>99.27</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-26.5</v>
+        <v>-28.15</v>
       </c>
       <c r="K61" t="n">
-        <v>-52.8</v>
+        <v>-56.1</v>
       </c>
       <c r="L61" t="n">
-        <v>59.08</v>
+        <v>62.77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-29.66</v>
+        <v>-21.96</v>
       </c>
       <c r="K62" t="n">
-        <v>207.28</v>
+        <v>153.42</v>
       </c>
       <c r="L62" t="n">
-        <v>209.39</v>
+        <v>154.99</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>79.62</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-17.31</v>
+        <v>-16.64</v>
       </c>
       <c r="L63" t="n">
-        <v>81.48</v>
+        <v>78.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>50.69</v>
+        <v>41.21</v>
       </c>
       <c r="K64" t="n">
-        <v>103.38</v>
+        <v>84.05</v>
       </c>
       <c r="L64" t="n">
-        <v>115.13</v>
+        <v>93.61</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-22.45</v>
+        <v>-38.61</v>
       </c>
       <c r="K65" t="n">
-        <v>52.8</v>
+        <v>90.83</v>
       </c>
       <c r="L65" t="n">
-        <v>57.37</v>
+        <v>98.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-171.27</v>
+        <v>-139.89</v>
       </c>
       <c r="K66" t="n">
-        <v>226.56</v>
+        <v>185.05</v>
       </c>
       <c r="L66" t="n">
-        <v>284.01</v>
+        <v>231.98</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-19.62</v>
+        <v>-25.22</v>
       </c>
       <c r="K67" t="n">
-        <v>107.49</v>
+        <v>138.17</v>
       </c>
       <c r="L67" t="n">
-        <v>109.27</v>
+        <v>140.45</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>116.79</v>
+        <v>155.62</v>
       </c>
       <c r="K68" t="n">
-        <v>-115.75</v>
+        <v>-154.23</v>
       </c>
       <c r="L68" t="n">
-        <v>164.44</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-130.77</v>
+        <v>-121.68</v>
       </c>
       <c r="K69" t="n">
-        <v>230.63</v>
+        <v>214.6</v>
       </c>
       <c r="L69" t="n">
-        <v>265.12</v>
+        <v>246.69</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>98.2</v>
+        <v>141.28</v>
       </c>
       <c r="K70" t="n">
-        <v>26.02</v>
+        <v>37.44</v>
       </c>
       <c r="L70" t="n">
-        <v>101.59</v>
+        <v>146.15</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-312.59</v>
+        <v>-374.7</v>
       </c>
       <c r="K71" t="n">
-        <v>66.65000000000001</v>
+        <v>79.89</v>
       </c>
       <c r="L71" t="n">
-        <v>319.61</v>
+        <v>383.13</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-269</v>
+        <v>-344.12</v>
       </c>
       <c r="K72" t="n">
-        <v>206.51</v>
+        <v>264.17</v>
       </c>
       <c r="L72" t="n">
-        <v>339.13</v>
+        <v>433.82</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-249.44</v>
+        <v>-267.39</v>
       </c>
       <c r="K73" t="n">
-        <v>254.32</v>
+        <v>272.63</v>
       </c>
       <c r="L73" t="n">
-        <v>356.23</v>
+        <v>381.88</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>119.72</v>
+        <v>90.56</v>
       </c>
       <c r="K74" t="n">
-        <v>3.81</v>
+        <v>2.88</v>
       </c>
       <c r="L74" t="n">
-        <v>119.78</v>
+        <v>90.61</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>42.71</v>
+        <v>35.79</v>
       </c>
       <c r="K75" t="n">
-        <v>-120.64</v>
+        <v>-101.09</v>
       </c>
       <c r="L75" t="n">
-        <v>127.98</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.3</v>
+        <v>-31</v>
       </c>
       <c r="K76" t="n">
-        <v>17.89</v>
+        <v>32.07</v>
       </c>
       <c r="L76" t="n">
-        <v>24.88</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>110.35</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-39.68</v>
+        <v>-35.76</v>
       </c>
       <c r="L77" t="n">
-        <v>117.27</v>
+        <v>105.69</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>61.7</v>
+        <v>61.44</v>
       </c>
       <c r="K78" t="n">
-        <v>77.22</v>
+        <v>76.89</v>
       </c>
       <c r="L78" t="n">
-        <v>98.84</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>102.71</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-82.95999999999999</v>
+        <v>-72.08</v>
       </c>
       <c r="L79" t="n">
-        <v>132.03</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>199.01</v>
+        <v>169.59</v>
       </c>
       <c r="K80" t="n">
-        <v>-75.39</v>
+        <v>-64.25</v>
       </c>
       <c r="L80" t="n">
-        <v>212.81</v>
+        <v>181.35</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-50.31</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-39.78</v>
+        <v>-59.98</v>
       </c>
       <c r="L81" t="n">
-        <v>64.14</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-40.52</v>
+        <v>-86.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.44</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>40.52</v>
+        <v>86.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>406.89</v>
+        <v>467.03</v>
       </c>
       <c r="K83" t="n">
-        <v>30</v>
+        <v>34.43</v>
       </c>
       <c r="L83" t="n">
-        <v>407.99</v>
+        <v>468.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-554.1900000000001</v>
+        <v>-489.02</v>
       </c>
       <c r="K84" t="n">
-        <v>-220</v>
+        <v>-194.13</v>
       </c>
       <c r="L84" t="n">
-        <v>596.27</v>
+        <v>526.15</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>253.76</v>
+        <v>295.14</v>
       </c>
       <c r="K85" t="n">
-        <v>32.35</v>
+        <v>37.63</v>
       </c>
       <c r="L85" t="n">
-        <v>255.81</v>
+        <v>297.53</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-344.23</v>
+        <v>-411.14</v>
       </c>
       <c r="K86" t="n">
-        <v>-120.21</v>
+        <v>-143.58</v>
       </c>
       <c r="L86" t="n">
-        <v>364.61</v>
+        <v>435.49</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>329.27</v>
+        <v>378.14</v>
       </c>
       <c r="K87" t="n">
-        <v>-72</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>337.05</v>
+        <v>387.07</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>43.07</v>
+        <v>50.4</v>
       </c>
       <c r="K88" t="n">
-        <v>-274.01</v>
+        <v>-320.68</v>
       </c>
       <c r="L88" t="n">
-        <v>277.38</v>
+        <v>324.62</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.49</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>79.69</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>80.25</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>74.08</v>
+        <v>63.9</v>
       </c>
       <c r="K15" t="n">
-        <v>42.29</v>
+        <v>36.48</v>
       </c>
       <c r="L15" t="n">
-        <v>85.3</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>42.37</v>
+        <v>33.89</v>
       </c>
       <c r="K16" t="n">
-        <v>27.68</v>
+        <v>22.14</v>
       </c>
       <c r="L16" t="n">
-        <v>50.61</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>65.56999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.08</v>
+        <v>-4.13</v>
       </c>
       <c r="L17" t="n">
-        <v>65.76000000000001</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-48.82</v>
+        <v>-40.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-34.64</v>
+        <v>-28.97</v>
       </c>
       <c r="L18" t="n">
-        <v>59.86</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>30.02</v>
+        <v>26.71</v>
       </c>
       <c r="K19" t="n">
-        <v>124.05</v>
+        <v>110.37</v>
       </c>
       <c r="L19" t="n">
-        <v>127.63</v>
+        <v>113.56</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-133.62</v>
+        <v>-89.5</v>
       </c>
       <c r="K20" t="n">
-        <v>170.71</v>
+        <v>114.34</v>
       </c>
       <c r="L20" t="n">
-        <v>216.79</v>
+        <v>145.2</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-85.42</v>
+        <v>-56.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-179.98</v>
+        <v>-119.1</v>
       </c>
       <c r="L21" t="n">
-        <v>199.23</v>
+        <v>131.83</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-49.14</v>
+        <v>-35.48</v>
       </c>
       <c r="K22" t="n">
-        <v>185.26</v>
+        <v>133.77</v>
       </c>
       <c r="L22" t="n">
-        <v>191.66</v>
+        <v>138.39</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>107.93</v>
+        <v>68.62</v>
       </c>
       <c r="K23" t="n">
-        <v>134.55</v>
+        <v>85.55</v>
       </c>
       <c r="L23" t="n">
-        <v>172.49</v>
+        <v>109.67</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-158.74</v>
+        <v>-87.7</v>
       </c>
       <c r="K24" t="n">
-        <v>34.21</v>
+        <v>18.9</v>
       </c>
       <c r="L24" t="n">
-        <v>162.38</v>
+        <v>89.70999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-37.63</v>
+        <v>-19.62</v>
       </c>
       <c r="K25" t="n">
-        <v>-230.87</v>
+        <v>-120.41</v>
       </c>
       <c r="L25" t="n">
-        <v>233.92</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-158.11</v>
+        <v>-80.20999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-462.99</v>
+        <v>-234.87</v>
       </c>
       <c r="L26" t="n">
-        <v>489.24</v>
+        <v>248.19</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-140.59</v>
+        <v>-79.45</v>
       </c>
       <c r="K27" t="n">
-        <v>368.34</v>
+        <v>208.15</v>
       </c>
       <c r="L27" t="n">
-        <v>394.26</v>
+        <v>222.8</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>259.12</v>
+        <v>136.46</v>
       </c>
       <c r="K28" t="n">
-        <v>-96.23</v>
+        <v>-50.67</v>
       </c>
       <c r="L28" t="n">
-        <v>276.41</v>
+        <v>145.56</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-39.03</v>
+        <v>-33.75</v>
       </c>
       <c r="K29" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="L29" t="n">
-        <v>39.07</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>85.15000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="K30" t="n">
-        <v>4.78</v>
+        <v>3.71</v>
       </c>
       <c r="L30" t="n">
-        <v>85.28</v>
+        <v>66.09</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>79.06999999999999</v>
+        <v>57.61</v>
       </c>
       <c r="K31" t="n">
-        <v>-13.17</v>
+        <v>-9.6</v>
       </c>
       <c r="L31" t="n">
-        <v>80.16</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>8.640000000000001</v>
+        <v>6.35</v>
       </c>
       <c r="K32" t="n">
-        <v>-134.43</v>
+        <v>-98.73</v>
       </c>
       <c r="L32" t="n">
-        <v>134.71</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.35</v>
+        <v>-3.29</v>
       </c>
       <c r="K33" t="n">
-        <v>95.22</v>
+        <v>72.13</v>
       </c>
       <c r="L33" t="n">
-        <v>95.31999999999999</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="K34" t="n">
-        <v>-100.26</v>
+        <v>-76.55</v>
       </c>
       <c r="L34" t="n">
-        <v>100.52</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>93.98</v>
+        <v>63.29</v>
       </c>
       <c r="K35" t="n">
-        <v>-126.78</v>
+        <v>-85.38</v>
       </c>
       <c r="L35" t="n">
-        <v>157.82</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>184.86</v>
+        <v>137.62</v>
       </c>
       <c r="K36" t="n">
-        <v>-138.62</v>
+        <v>-103.2</v>
       </c>
       <c r="L36" t="n">
-        <v>231.06</v>
+        <v>172.02</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-26.15</v>
+        <v>-19.6</v>
       </c>
       <c r="K37" t="n">
-        <v>124.83</v>
+        <v>93.58</v>
       </c>
       <c r="L37" t="n">
-        <v>127.53</v>
+        <v>95.61</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-234.95</v>
+        <v>-138.5</v>
       </c>
       <c r="K38" t="n">
-        <v>142.24</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>274.65</v>
+        <v>161.9</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-31.4</v>
+        <v>-17.89</v>
       </c>
       <c r="K39" t="n">
-        <v>-188.22</v>
+        <v>-107.23</v>
       </c>
       <c r="L39" t="n">
-        <v>190.82</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>119.89</v>
+        <v>70.83</v>
       </c>
       <c r="K40" t="n">
-        <v>232.77</v>
+        <v>137.51</v>
       </c>
       <c r="L40" t="n">
-        <v>261.83</v>
+        <v>154.68</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-134.36</v>
+        <v>-77.52</v>
       </c>
       <c r="K41" t="n">
-        <v>253.12</v>
+        <v>146.04</v>
       </c>
       <c r="L41" t="n">
-        <v>286.57</v>
+        <v>165.34</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>374.54</v>
+        <v>211.72</v>
       </c>
       <c r="K42" t="n">
-        <v>98.73</v>
+        <v>55.81</v>
       </c>
       <c r="L42" t="n">
-        <v>387.33</v>
+        <v>218.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-98.88</v>
+        <v>-54.89</v>
       </c>
       <c r="K43" t="n">
-        <v>451.26</v>
+        <v>250.49</v>
       </c>
       <c r="L43" t="n">
-        <v>461.96</v>
+        <v>256.43</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.59</v>
+        <v>-31.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-28.43</v>
+        <v>-24.46</v>
       </c>
       <c r="L44" t="n">
-        <v>46.34</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-45.44</v>
+        <v>-34.15</v>
       </c>
       <c r="K45" t="n">
-        <v>29.65</v>
+        <v>22.28</v>
       </c>
       <c r="L45" t="n">
-        <v>54.26</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>6.71</v>
+        <v>5.34</v>
       </c>
       <c r="K46" t="n">
-        <v>45.36</v>
+        <v>36.1</v>
       </c>
       <c r="L46" t="n">
-        <v>45.85</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-102.76</v>
+        <v>-83.83</v>
       </c>
       <c r="K47" t="n">
-        <v>-20.57</v>
+        <v>-16.78</v>
       </c>
       <c r="L47" t="n">
-        <v>104.8</v>
+        <v>85.48999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-50.22</v>
+        <v>-37.88</v>
       </c>
       <c r="K48" t="n">
-        <v>111.58</v>
+        <v>84.17</v>
       </c>
       <c r="L48" t="n">
-        <v>122.36</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-108.43</v>
+        <v>-89.09</v>
       </c>
       <c r="K49" t="n">
-        <v>4.62</v>
+        <v>3.8</v>
       </c>
       <c r="L49" t="n">
-        <v>108.53</v>
+        <v>89.17</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>228.27</v>
+        <v>149.94</v>
       </c>
       <c r="K50" t="n">
-        <v>17.07</v>
+        <v>11.21</v>
       </c>
       <c r="L50" t="n">
-        <v>228.91</v>
+        <v>150.36</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>11.18</v>
+        <v>8.33</v>
       </c>
       <c r="K51" t="n">
-        <v>130.39</v>
+        <v>97.11</v>
       </c>
       <c r="L51" t="n">
-        <v>130.87</v>
+        <v>97.45999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>31.25</v>
+        <v>21.89</v>
       </c>
       <c r="K52" t="n">
-        <v>124.85</v>
+        <v>87.48</v>
       </c>
       <c r="L52" t="n">
-        <v>128.7</v>
+        <v>90.18000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-85.56</v>
+        <v>-56.8</v>
       </c>
       <c r="K53" t="n">
-        <v>222.2</v>
+        <v>147.5</v>
       </c>
       <c r="L53" t="n">
-        <v>238.1</v>
+        <v>158.06</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>85.06</v>
+        <v>47.32</v>
       </c>
       <c r="K54" t="n">
-        <v>207.15</v>
+        <v>115.23</v>
       </c>
       <c r="L54" t="n">
-        <v>223.93</v>
+        <v>124.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>188.55</v>
+        <v>98.37</v>
       </c>
       <c r="K55" t="n">
-        <v>-361.88</v>
+        <v>-188.79</v>
       </c>
       <c r="L55" t="n">
-        <v>408.05</v>
+        <v>212.88</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-66.95999999999999</v>
+        <v>-34.17</v>
       </c>
       <c r="K56" t="n">
-        <v>360.06</v>
+        <v>183.74</v>
       </c>
       <c r="L56" t="n">
-        <v>366.24</v>
+        <v>186.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>409.11</v>
+        <v>201.75</v>
       </c>
       <c r="K57" t="n">
-        <v>-226.62</v>
+        <v>-111.75</v>
       </c>
       <c r="L57" t="n">
-        <v>467.68</v>
+        <v>230.63</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>364.84</v>
+        <v>179.34</v>
       </c>
       <c r="K58" t="n">
-        <v>-381.59</v>
+        <v>-187.57</v>
       </c>
       <c r="L58" t="n">
-        <v>527.9400000000001</v>
+        <v>259.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>31.61</v>
+        <v>29.53</v>
       </c>
       <c r="K59" t="n">
-        <v>-55.19</v>
+        <v>-51.57</v>
       </c>
       <c r="L59" t="n">
-        <v>63.6</v>
+        <v>59.43</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-77.53</v>
+        <v>-66.23</v>
       </c>
       <c r="K60" t="n">
-        <v>-23.4</v>
+        <v>-19.99</v>
       </c>
       <c r="L60" t="n">
-        <v>80.98999999999999</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.15</v>
+        <v>-21.78</v>
       </c>
       <c r="K61" t="n">
-        <v>-56.1</v>
+        <v>-43.41</v>
       </c>
       <c r="L61" t="n">
-        <v>62.77</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-21.96</v>
+        <v>-17.73</v>
       </c>
       <c r="K62" t="n">
-        <v>153.42</v>
+        <v>123.88</v>
       </c>
       <c r="L62" t="n">
-        <v>154.99</v>
+        <v>125.14</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>76.56999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.64</v>
+        <v>-13.93</v>
       </c>
       <c r="L63" t="n">
-        <v>78.36</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>41.21</v>
+        <v>35.75</v>
       </c>
       <c r="K64" t="n">
-        <v>84.05</v>
+        <v>72.91</v>
       </c>
       <c r="L64" t="n">
-        <v>93.61</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-38.61</v>
+        <v>-25.63</v>
       </c>
       <c r="K65" t="n">
-        <v>90.83</v>
+        <v>60.29</v>
       </c>
       <c r="L65" t="n">
-        <v>98.69</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-139.89</v>
+        <v>-96.45</v>
       </c>
       <c r="K66" t="n">
-        <v>185.05</v>
+        <v>127.59</v>
       </c>
       <c r="L66" t="n">
-        <v>231.98</v>
+        <v>159.94</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-25.22</v>
+        <v>-15.54</v>
       </c>
       <c r="K67" t="n">
-        <v>138.17</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>140.45</v>
+        <v>86.58</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>155.62</v>
+        <v>84</v>
       </c>
       <c r="K68" t="n">
-        <v>-154.23</v>
+        <v>-83.25</v>
       </c>
       <c r="L68" t="n">
-        <v>219.1</v>
+        <v>118.27</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-121.68</v>
+        <v>-81.06</v>
       </c>
       <c r="K69" t="n">
-        <v>214.6</v>
+        <v>142.96</v>
       </c>
       <c r="L69" t="n">
-        <v>246.69</v>
+        <v>164.34</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>141.28</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>37.44</v>
+        <v>22.88</v>
       </c>
       <c r="L70" t="n">
-        <v>146.15</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-374.7</v>
+        <v>-196.95</v>
       </c>
       <c r="K71" t="n">
-        <v>79.89</v>
+        <v>41.99</v>
       </c>
       <c r="L71" t="n">
-        <v>383.13</v>
+        <v>201.37</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-344.12</v>
+        <v>-165.62</v>
       </c>
       <c r="K72" t="n">
-        <v>264.17</v>
+        <v>127.14</v>
       </c>
       <c r="L72" t="n">
-        <v>433.82</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-267.39</v>
+        <v>-153.57</v>
       </c>
       <c r="K73" t="n">
-        <v>272.63</v>
+        <v>156.58</v>
       </c>
       <c r="L73" t="n">
-        <v>381.88</v>
+        <v>219.31</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>90.56</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="L74" t="n">
-        <v>90.61</v>
+        <v>73.75</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>35.79</v>
+        <v>29.48</v>
       </c>
       <c r="K75" t="n">
-        <v>-101.09</v>
+        <v>-83.27</v>
       </c>
       <c r="L75" t="n">
-        <v>107.24</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-31</v>
+        <v>-25.22</v>
       </c>
       <c r="K76" t="n">
-        <v>32.07</v>
+        <v>26.08</v>
       </c>
       <c r="L76" t="n">
-        <v>44.6</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>99.45999999999999</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-35.76</v>
+        <v>-28.2</v>
       </c>
       <c r="L77" t="n">
-        <v>105.69</v>
+        <v>83.34</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>61.44</v>
+        <v>48.81</v>
       </c>
       <c r="K78" t="n">
-        <v>76.89</v>
+        <v>61.08</v>
       </c>
       <c r="L78" t="n">
-        <v>98.42</v>
+        <v>78.18000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>89.23999999999999</v>
+        <v>69.89</v>
       </c>
       <c r="K79" t="n">
-        <v>-72.08</v>
+        <v>-56.45</v>
       </c>
       <c r="L79" t="n">
-        <v>114.71</v>
+        <v>89.84</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>169.59</v>
+        <v>122.72</v>
       </c>
       <c r="K80" t="n">
-        <v>-64.25</v>
+        <v>-46.49</v>
       </c>
       <c r="L80" t="n">
-        <v>181.35</v>
+        <v>131.23</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-75.84999999999999</v>
+        <v>-58.1</v>
       </c>
       <c r="K81" t="n">
-        <v>-59.98</v>
+        <v>-45.94</v>
       </c>
       <c r="L81" t="n">
-        <v>96.7</v>
+        <v>74.06</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-86.52</v>
+        <v>-60.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="L82" t="n">
-        <v>86.53</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>467.03</v>
+        <v>265.03</v>
       </c>
       <c r="K83" t="n">
-        <v>34.43</v>
+        <v>19.54</v>
       </c>
       <c r="L83" t="n">
-        <v>468.3</v>
+        <v>265.75</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-489.02</v>
+        <v>-317.52</v>
       </c>
       <c r="K84" t="n">
-        <v>-194.13</v>
+        <v>-126.05</v>
       </c>
       <c r="L84" t="n">
-        <v>526.15</v>
+        <v>341.63</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>295.14</v>
+        <v>166.65</v>
       </c>
       <c r="K85" t="n">
-        <v>37.63</v>
+        <v>21.25</v>
       </c>
       <c r="L85" t="n">
-        <v>297.53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-411.14</v>
+        <v>-229.95</v>
       </c>
       <c r="K86" t="n">
-        <v>-143.58</v>
+        <v>-80.3</v>
       </c>
       <c r="L86" t="n">
-        <v>435.49</v>
+        <v>243.57</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>378.14</v>
+        <v>205.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-82.68000000000001</v>
+        <v>-44.98</v>
       </c>
       <c r="L87" t="n">
-        <v>387.07</v>
+        <v>210.58</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>50.4</v>
+        <v>30.14</v>
       </c>
       <c r="K88" t="n">
-        <v>-320.68</v>
+        <v>-191.76</v>
       </c>
       <c r="L88" t="n">
-        <v>324.62</v>
+        <v>194.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>72.31999999999999</v>
+        <v>74.53</v>
       </c>
       <c r="L14" t="n">
-        <v>72.83</v>
+        <v>75.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>63.9</v>
+        <v>64.72</v>
       </c>
       <c r="K15" t="n">
-        <v>36.48</v>
+        <v>36.95</v>
       </c>
       <c r="L15" t="n">
-        <v>73.58</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>33.89</v>
+        <v>34.92</v>
       </c>
       <c r="K16" t="n">
-        <v>22.14</v>
+        <v>22.81</v>
       </c>
       <c r="L16" t="n">
-        <v>40.48</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>53.3</v>
+        <v>56.76</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.13</v>
+        <v>-4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>53.46</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-40.83</v>
+        <v>-43.15</v>
       </c>
       <c r="K18" t="n">
-        <v>-28.97</v>
+        <v>-30.62</v>
       </c>
       <c r="L18" t="n">
-        <v>50.07</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>26.71</v>
+        <v>28.49</v>
       </c>
       <c r="K19" t="n">
-        <v>110.37</v>
+        <v>117.72</v>
       </c>
       <c r="L19" t="n">
-        <v>113.56</v>
+        <v>121.12</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-89.5</v>
+        <v>-100.93</v>
       </c>
       <c r="K20" t="n">
-        <v>114.34</v>
+        <v>128.94</v>
       </c>
       <c r="L20" t="n">
-        <v>145.2</v>
+        <v>163.75</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-56.53</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-119.1</v>
+        <v>-136.39</v>
       </c>
       <c r="L21" t="n">
-        <v>131.83</v>
+        <v>150.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-35.48</v>
+        <v>-39.78</v>
       </c>
       <c r="K22" t="n">
-        <v>133.77</v>
+        <v>149.98</v>
       </c>
       <c r="L22" t="n">
-        <v>138.39</v>
+        <v>155.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>68.62</v>
+        <v>79.92</v>
       </c>
       <c r="K23" t="n">
-        <v>85.55</v>
+        <v>99.63</v>
       </c>
       <c r="L23" t="n">
-        <v>109.67</v>
+        <v>127.72</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-87.7</v>
+        <v>-103.33</v>
       </c>
       <c r="K24" t="n">
-        <v>18.9</v>
+        <v>22.27</v>
       </c>
       <c r="L24" t="n">
-        <v>89.70999999999999</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-19.62</v>
+        <v>-23.36</v>
       </c>
       <c r="K25" t="n">
-        <v>-120.41</v>
+        <v>-143.33</v>
       </c>
       <c r="L25" t="n">
-        <v>122</v>
+        <v>145.22</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-80.20999999999999</v>
+        <v>-96.3</v>
       </c>
       <c r="K26" t="n">
-        <v>-234.87</v>
+        <v>-282</v>
       </c>
       <c r="L26" t="n">
-        <v>248.19</v>
+        <v>297.99</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-79.45</v>
+        <v>-92.98</v>
       </c>
       <c r="K27" t="n">
-        <v>208.15</v>
+        <v>243.61</v>
       </c>
       <c r="L27" t="n">
-        <v>222.8</v>
+        <v>260.75</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>136.46</v>
+        <v>161.57</v>
       </c>
       <c r="K28" t="n">
-        <v>-50.67</v>
+        <v>-60</v>
       </c>
       <c r="L28" t="n">
-        <v>145.56</v>
+        <v>172.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.75</v>
+        <v>-34.18</v>
       </c>
       <c r="K29" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="L29" t="n">
-        <v>33.79</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>65.98</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="L30" t="n">
-        <v>66.09</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>57.61</v>
+        <v>61.12</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.6</v>
+        <v>-10.18</v>
       </c>
       <c r="L31" t="n">
-        <v>58.4</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>6.35</v>
+        <v>6.91</v>
       </c>
       <c r="K32" t="n">
-        <v>-98.73</v>
+        <v>-107.41</v>
       </c>
       <c r="L32" t="n">
-        <v>98.93000000000001</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.29</v>
+        <v>-3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>72.13</v>
+        <v>77.7</v>
       </c>
       <c r="L33" t="n">
-        <v>72.2</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="K34" t="n">
-        <v>-76.55</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>76.75</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>63.29</v>
+        <v>72.14</v>
       </c>
       <c r="K35" t="n">
-        <v>-85.38</v>
+        <v>-97.31999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>106.28</v>
+        <v>121.14</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>137.62</v>
+        <v>154.48</v>
       </c>
       <c r="K36" t="n">
-        <v>-103.2</v>
+        <v>-115.84</v>
       </c>
       <c r="L36" t="n">
-        <v>172.02</v>
+        <v>193.09</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-19.6</v>
+        <v>-21.87</v>
       </c>
       <c r="K37" t="n">
-        <v>93.58</v>
+        <v>104.4</v>
       </c>
       <c r="L37" t="n">
-        <v>95.61</v>
+        <v>106.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-138.5</v>
+        <v>-161.08</v>
       </c>
       <c r="K38" t="n">
-        <v>83.84999999999999</v>
+        <v>97.52</v>
       </c>
       <c r="L38" t="n">
-        <v>161.9</v>
+        <v>188.3</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-17.89</v>
+        <v>-21.01</v>
       </c>
       <c r="K39" t="n">
-        <v>-107.23</v>
+        <v>-125.92</v>
       </c>
       <c r="L39" t="n">
-        <v>108.71</v>
+        <v>127.66</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>70.83</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>137.51</v>
+        <v>161.44</v>
       </c>
       <c r="L40" t="n">
-        <v>154.68</v>
+        <v>181.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-77.52</v>
+        <v>-91.44</v>
       </c>
       <c r="K41" t="n">
-        <v>146.04</v>
+        <v>172.26</v>
       </c>
       <c r="L41" t="n">
-        <v>165.34</v>
+        <v>195.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>211.72</v>
+        <v>246.25</v>
       </c>
       <c r="K42" t="n">
-        <v>55.81</v>
+        <v>64.92</v>
       </c>
       <c r="L42" t="n">
-        <v>218.95</v>
+        <v>254.67</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-54.89</v>
+        <v>-65.28</v>
       </c>
       <c r="K43" t="n">
-        <v>250.49</v>
+        <v>297.89</v>
       </c>
       <c r="L43" t="n">
-        <v>256.43</v>
+        <v>304.96</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-31.48</v>
+        <v>-32.23</v>
       </c>
       <c r="K44" t="n">
-        <v>-24.46</v>
+        <v>-25.05</v>
       </c>
       <c r="L44" t="n">
-        <v>39.86</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.15</v>
+        <v>-35.61</v>
       </c>
       <c r="K45" t="n">
-        <v>22.28</v>
+        <v>23.23</v>
       </c>
       <c r="L45" t="n">
-        <v>40.78</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>5.34</v>
+        <v>5.63</v>
       </c>
       <c r="K46" t="n">
-        <v>36.1</v>
+        <v>38.04</v>
       </c>
       <c r="L46" t="n">
-        <v>36.5</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-83.83</v>
+        <v>-89.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-16.78</v>
+        <v>-17.87</v>
       </c>
       <c r="L47" t="n">
-        <v>85.48999999999999</v>
+        <v>91.05</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-37.88</v>
+        <v>-40.76</v>
       </c>
       <c r="K48" t="n">
-        <v>84.17</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>92.3</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-89.09</v>
+        <v>-95.59999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>3.8</v>
+        <v>4.08</v>
       </c>
       <c r="L49" t="n">
-        <v>89.17</v>
+        <v>95.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>149.94</v>
+        <v>172.68</v>
       </c>
       <c r="K50" t="n">
-        <v>11.21</v>
+        <v>12.91</v>
       </c>
       <c r="L50" t="n">
-        <v>150.36</v>
+        <v>173.17</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>8.33</v>
+        <v>9.33</v>
       </c>
       <c r="K51" t="n">
-        <v>97.11</v>
+        <v>108.83</v>
       </c>
       <c r="L51" t="n">
-        <v>97.45999999999999</v>
+        <v>109.23</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>21.89</v>
+        <v>24.67</v>
       </c>
       <c r="K52" t="n">
-        <v>87.48</v>
+        <v>98.56</v>
       </c>
       <c r="L52" t="n">
-        <v>90.18000000000001</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-56.8</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>147.5</v>
+        <v>171.38</v>
       </c>
       <c r="L53" t="n">
-        <v>158.06</v>
+        <v>183.65</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>47.32</v>
+        <v>55.73</v>
       </c>
       <c r="K54" t="n">
-        <v>115.23</v>
+        <v>135.72</v>
       </c>
       <c r="L54" t="n">
-        <v>124.57</v>
+        <v>146.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>98.37</v>
+        <v>117.58</v>
       </c>
       <c r="K55" t="n">
-        <v>-188.79</v>
+        <v>-225.66</v>
       </c>
       <c r="L55" t="n">
-        <v>212.88</v>
+        <v>254.45</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-34.17</v>
+        <v>-40.7</v>
       </c>
       <c r="K56" t="n">
-        <v>183.74</v>
+        <v>218.84</v>
       </c>
       <c r="L56" t="n">
-        <v>186.89</v>
+        <v>222.59</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>201.75</v>
+        <v>240.12</v>
       </c>
       <c r="K57" t="n">
-        <v>-111.75</v>
+        <v>-133.01</v>
       </c>
       <c r="L57" t="n">
-        <v>230.63</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>179.34</v>
+        <v>214.2</v>
       </c>
       <c r="K58" t="n">
-        <v>-187.57</v>
+        <v>-224.04</v>
       </c>
       <c r="L58" t="n">
-        <v>259.51</v>
+        <v>309.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>29.53</v>
+        <v>30.8</v>
       </c>
       <c r="K59" t="n">
-        <v>-51.57</v>
+        <v>-53.79</v>
       </c>
       <c r="L59" t="n">
-        <v>59.43</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-66.23</v>
+        <v>-70.53</v>
       </c>
       <c r="K60" t="n">
-        <v>-19.99</v>
+        <v>-21.29</v>
       </c>
       <c r="L60" t="n">
-        <v>69.18000000000001</v>
+        <v>73.67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.78</v>
+        <v>-22.59</v>
       </c>
       <c r="K61" t="n">
-        <v>-43.41</v>
+        <v>-45.02</v>
       </c>
       <c r="L61" t="n">
-        <v>48.57</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.73</v>
+        <v>-18.95</v>
       </c>
       <c r="K62" t="n">
-        <v>123.88</v>
+        <v>132.39</v>
       </c>
       <c r="L62" t="n">
-        <v>125.14</v>
+        <v>133.74</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>64.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K63" t="n">
-        <v>-13.93</v>
+        <v>-14.85</v>
       </c>
       <c r="L63" t="n">
-        <v>65.59999999999999</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>35.75</v>
+        <v>37.95</v>
       </c>
       <c r="K64" t="n">
-        <v>72.91</v>
+        <v>77.39</v>
       </c>
       <c r="L64" t="n">
-        <v>81.2</v>
+        <v>86.19</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-25.63</v>
+        <v>-29.25</v>
       </c>
       <c r="K65" t="n">
-        <v>60.29</v>
+        <v>68.81</v>
       </c>
       <c r="L65" t="n">
-        <v>65.51000000000001</v>
+        <v>74.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-96.45</v>
+        <v>-108.92</v>
       </c>
       <c r="K66" t="n">
-        <v>127.59</v>
+        <v>144.08</v>
       </c>
       <c r="L66" t="n">
-        <v>159.94</v>
+        <v>180.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-15.54</v>
+        <v>-17.84</v>
       </c>
       <c r="K67" t="n">
-        <v>85.18000000000001</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>86.58</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>84</v>
+        <v>100.25</v>
       </c>
       <c r="K68" t="n">
-        <v>-83.25</v>
+        <v>-99.36</v>
       </c>
       <c r="L68" t="n">
-        <v>118.27</v>
+        <v>141.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-81.06</v>
+        <v>-93.81999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>142.96</v>
+        <v>165.47</v>
       </c>
       <c r="L69" t="n">
-        <v>164.34</v>
+        <v>190.21</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>86.31999999999999</v>
+        <v>100.07</v>
       </c>
       <c r="K70" t="n">
-        <v>22.88</v>
+        <v>26.52</v>
       </c>
       <c r="L70" t="n">
-        <v>89.3</v>
+        <v>103.52</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-196.95</v>
+        <v>-234.9</v>
       </c>
       <c r="K71" t="n">
-        <v>41.99</v>
+        <v>50.08</v>
       </c>
       <c r="L71" t="n">
-        <v>201.37</v>
+        <v>240.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-165.62</v>
+        <v>-197.89</v>
       </c>
       <c r="K72" t="n">
-        <v>127.14</v>
+        <v>151.91</v>
       </c>
       <c r="L72" t="n">
-        <v>208.8</v>
+        <v>249.47</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-153.57</v>
+        <v>-179.66</v>
       </c>
       <c r="K73" t="n">
-        <v>156.58</v>
+        <v>183.18</v>
       </c>
       <c r="L73" t="n">
-        <v>219.31</v>
+        <v>256.57</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>73.70999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="L74" t="n">
-        <v>73.75</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>29.48</v>
+        <v>31.21</v>
       </c>
       <c r="K75" t="n">
-        <v>-83.27</v>
+        <v>-88.16</v>
       </c>
       <c r="L75" t="n">
-        <v>88.33</v>
+        <v>93.52</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.22</v>
+        <v>-26.88</v>
       </c>
       <c r="K76" t="n">
-        <v>26.08</v>
+        <v>27.8</v>
       </c>
       <c r="L76" t="n">
-        <v>36.28</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>78.43000000000001</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-28.2</v>
+        <v>-30.5</v>
       </c>
       <c r="L77" t="n">
-        <v>83.34</v>
+        <v>90.14</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>48.81</v>
+        <v>52.89</v>
       </c>
       <c r="K78" t="n">
-        <v>61.08</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>78.18000000000001</v>
+        <v>84.72</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>69.89</v>
+        <v>74.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-56.45</v>
+        <v>-60.38</v>
       </c>
       <c r="L79" t="n">
-        <v>89.84</v>
+        <v>96.09</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>122.72</v>
+        <v>137.9</v>
       </c>
       <c r="K80" t="n">
-        <v>-46.49</v>
+        <v>-52.24</v>
       </c>
       <c r="L80" t="n">
-        <v>131.23</v>
+        <v>147.46</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-58.1</v>
+        <v>-65.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-45.94</v>
+        <v>-51.56</v>
       </c>
       <c r="L81" t="n">
-        <v>74.06</v>
+        <v>83.12</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-60.2</v>
+        <v>-68.09</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.66</v>
+        <v>-0.74</v>
       </c>
       <c r="L82" t="n">
-        <v>60.2</v>
+        <v>68.09</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>265.03</v>
+        <v>306.91</v>
       </c>
       <c r="K83" t="n">
-        <v>19.54</v>
+        <v>22.63</v>
       </c>
       <c r="L83" t="n">
-        <v>265.75</v>
+        <v>307.75</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-317.52</v>
+        <v>-360.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-126.05</v>
+        <v>-143.15</v>
       </c>
       <c r="L84" t="n">
-        <v>341.63</v>
+        <v>387.99</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>166.65</v>
+        <v>198.28</v>
       </c>
       <c r="K85" t="n">
-        <v>21.25</v>
+        <v>25.28</v>
       </c>
       <c r="L85" t="n">
-        <v>168</v>
+        <v>199.88</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-229.95</v>
+        <v>-270.88</v>
       </c>
       <c r="K86" t="n">
-        <v>-80.3</v>
+        <v>-94.59999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>243.57</v>
+        <v>286.93</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>205.72</v>
+        <v>243</v>
       </c>
       <c r="K87" t="n">
-        <v>-44.98</v>
+        <v>-53.13</v>
       </c>
       <c r="L87" t="n">
-        <v>210.58</v>
+        <v>248.74</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>30.14</v>
+        <v>35.48</v>
       </c>
       <c r="K88" t="n">
-        <v>-191.76</v>
+        <v>-225.72</v>
       </c>
       <c r="L88" t="n">
-        <v>194.12</v>
+        <v>228.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.880000000000001</v>
+        <v>-6.56</v>
       </c>
       <c r="K14" t="n">
-        <v>74.53</v>
+        <v>55.05</v>
       </c>
       <c r="L14" t="n">
-        <v>75.06</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>64.72</v>
+        <v>48.54</v>
       </c>
       <c r="K15" t="n">
-        <v>36.95</v>
+        <v>27.71</v>
       </c>
       <c r="L15" t="n">
-        <v>74.52</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>34.92</v>
+        <v>26.19</v>
       </c>
       <c r="K16" t="n">
-        <v>22.81</v>
+        <v>17.11</v>
       </c>
       <c r="L16" t="n">
-        <v>41.71</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>56.76</v>
+        <v>42.57</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.4</v>
+        <v>-3.3</v>
       </c>
       <c r="L17" t="n">
-        <v>56.93</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-43.15</v>
+        <v>-32.36</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.62</v>
+        <v>-22.96</v>
       </c>
       <c r="L18" t="n">
-        <v>52.9</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>28.49</v>
+        <v>20.62</v>
       </c>
       <c r="K19" t="n">
-        <v>117.72</v>
+        <v>85.22</v>
       </c>
       <c r="L19" t="n">
-        <v>121.12</v>
+        <v>87.68000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-100.93</v>
+        <v>-75.7</v>
       </c>
       <c r="K20" t="n">
-        <v>128.94</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>163.75</v>
+        <v>122.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-64.73999999999999</v>
+        <v>-47.15</v>
       </c>
       <c r="K21" t="n">
-        <v>-136.39</v>
+        <v>-99.33</v>
       </c>
       <c r="L21" t="n">
-        <v>150.97</v>
+        <v>109.95</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-39.78</v>
+        <v>-29.84</v>
       </c>
       <c r="K22" t="n">
-        <v>149.98</v>
+        <v>112.49</v>
       </c>
       <c r="L22" t="n">
-        <v>155.17</v>
+        <v>116.38</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>79.92</v>
+        <v>59.94</v>
       </c>
       <c r="K23" t="n">
-        <v>99.63</v>
+        <v>74.72</v>
       </c>
       <c r="L23" t="n">
-        <v>127.72</v>
+        <v>95.79000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-103.33</v>
+        <v>-77.5</v>
       </c>
       <c r="K24" t="n">
-        <v>22.27</v>
+        <v>16.7</v>
       </c>
       <c r="L24" t="n">
-        <v>105.7</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-23.36</v>
+        <v>-17.52</v>
       </c>
       <c r="K25" t="n">
-        <v>-143.33</v>
+        <v>-107.5</v>
       </c>
       <c r="L25" t="n">
-        <v>145.22</v>
+        <v>108.91</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-96.3</v>
+        <v>-66.73</v>
       </c>
       <c r="K26" t="n">
-        <v>-282</v>
+        <v>-195.41</v>
       </c>
       <c r="L26" t="n">
-        <v>297.99</v>
+        <v>206.49</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-92.98</v>
+        <v>-69.73999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>243.61</v>
+        <v>182.71</v>
       </c>
       <c r="L27" t="n">
-        <v>260.75</v>
+        <v>195.56</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>161.57</v>
+        <v>121.18</v>
       </c>
       <c r="K28" t="n">
-        <v>-60</v>
+        <v>-45</v>
       </c>
       <c r="L28" t="n">
-        <v>172.35</v>
+        <v>129.26</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-34.18</v>
+        <v>-25.63</v>
       </c>
       <c r="K29" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="L29" t="n">
-        <v>34.22</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>69.06999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="K30" t="n">
-        <v>3.88</v>
+        <v>2.91</v>
       </c>
       <c r="L30" t="n">
-        <v>69.18000000000001</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>61.12</v>
+        <v>45.84</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.18</v>
+        <v>-7.64</v>
       </c>
       <c r="L31" t="n">
-        <v>61.96</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>6.91</v>
+        <v>5.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-107.41</v>
+        <v>-80.56</v>
       </c>
       <c r="L32" t="n">
-        <v>107.63</v>
+        <v>80.72</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.55</v>
+        <v>-2.66</v>
       </c>
       <c r="K33" t="n">
-        <v>77.7</v>
+        <v>58.27</v>
       </c>
       <c r="L33" t="n">
-        <v>77.78</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>5.88</v>
+        <v>4.41</v>
       </c>
       <c r="K34" t="n">
-        <v>-81.81999999999999</v>
+        <v>-61.37</v>
       </c>
       <c r="L34" t="n">
-        <v>82.03</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>72.14</v>
+        <v>54.1</v>
       </c>
       <c r="K35" t="n">
-        <v>-97.31999999999999</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>121.14</v>
+        <v>90.84999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>154.48</v>
+        <v>115.86</v>
       </c>
       <c r="K36" t="n">
-        <v>-115.84</v>
+        <v>-86.88</v>
       </c>
       <c r="L36" t="n">
-        <v>193.09</v>
+        <v>144.81</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-21.87</v>
+        <v>-16.4</v>
       </c>
       <c r="K37" t="n">
-        <v>104.4</v>
+        <v>78.3</v>
       </c>
       <c r="L37" t="n">
-        <v>106.66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-161.08</v>
+        <v>-120.81</v>
       </c>
       <c r="K38" t="n">
-        <v>97.52</v>
+        <v>73.14</v>
       </c>
       <c r="L38" t="n">
-        <v>188.3</v>
+        <v>141.23</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-21.01</v>
+        <v>-15.76</v>
       </c>
       <c r="K39" t="n">
-        <v>-125.92</v>
+        <v>-94.44</v>
       </c>
       <c r="L39" t="n">
-        <v>127.66</v>
+        <v>95.73999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>83.15000000000001</v>
+        <v>62.36</v>
       </c>
       <c r="K40" t="n">
-        <v>161.44</v>
+        <v>121.08</v>
       </c>
       <c r="L40" t="n">
-        <v>181.59</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-91.44</v>
+        <v>-66.94</v>
       </c>
       <c r="K41" t="n">
-        <v>172.26</v>
+        <v>126.11</v>
       </c>
       <c r="L41" t="n">
-        <v>195.03</v>
+        <v>142.77</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>246.25</v>
+        <v>184.69</v>
       </c>
       <c r="K42" t="n">
-        <v>64.92</v>
+        <v>48.69</v>
       </c>
       <c r="L42" t="n">
-        <v>254.67</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-65.28</v>
+        <v>-46.26</v>
       </c>
       <c r="K43" t="n">
-        <v>297.89</v>
+        <v>211.08</v>
       </c>
       <c r="L43" t="n">
-        <v>304.96</v>
+        <v>216.09</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-32.23</v>
+        <v>-24.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-25.05</v>
+        <v>-18.79</v>
       </c>
       <c r="L44" t="n">
-        <v>40.82</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.61</v>
+        <v>-26.71</v>
       </c>
       <c r="K45" t="n">
-        <v>23.23</v>
+        <v>17.42</v>
       </c>
       <c r="L45" t="n">
-        <v>42.52</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>5.63</v>
+        <v>4.22</v>
       </c>
       <c r="K46" t="n">
-        <v>38.04</v>
+        <v>28.53</v>
       </c>
       <c r="L46" t="n">
-        <v>38.46</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-89.28</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-17.87</v>
+        <v>-13.41</v>
       </c>
       <c r="L47" t="n">
-        <v>91.05</v>
+        <v>68.29000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-40.76</v>
+        <v>-30.57</v>
       </c>
       <c r="K48" t="n">
-        <v>90.56999999999999</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>99.31999999999999</v>
+        <v>74.48999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-95.59999999999999</v>
+        <v>-69.64</v>
       </c>
       <c r="K49" t="n">
-        <v>4.08</v>
+        <v>2.97</v>
       </c>
       <c r="L49" t="n">
-        <v>95.69</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>172.68</v>
+        <v>116.77</v>
       </c>
       <c r="K50" t="n">
-        <v>12.91</v>
+        <v>8.73</v>
       </c>
       <c r="L50" t="n">
-        <v>173.17</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>9.33</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>108.83</v>
+        <v>81.62</v>
       </c>
       <c r="L51" t="n">
-        <v>109.23</v>
+        <v>81.92</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>24.67</v>
+        <v>18.5</v>
       </c>
       <c r="K52" t="n">
-        <v>98.56</v>
+        <v>73.92</v>
       </c>
       <c r="L52" t="n">
-        <v>101.6</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-65.98999999999999</v>
+        <v>-48.14</v>
       </c>
       <c r="K53" t="n">
-        <v>171.38</v>
+        <v>125.03</v>
       </c>
       <c r="L53" t="n">
-        <v>183.65</v>
+        <v>133.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>55.73</v>
+        <v>41.58</v>
       </c>
       <c r="K54" t="n">
-        <v>135.72</v>
+        <v>101.27</v>
       </c>
       <c r="L54" t="n">
-        <v>146.72</v>
+        <v>109.47</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>117.58</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-225.66</v>
+        <v>-169.25</v>
       </c>
       <c r="L55" t="n">
-        <v>254.45</v>
+        <v>190.84</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-40.7</v>
+        <v>-29.51</v>
       </c>
       <c r="K56" t="n">
-        <v>218.84</v>
+        <v>158.69</v>
       </c>
       <c r="L56" t="n">
-        <v>222.59</v>
+        <v>161.41</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>240.12</v>
+        <v>143.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-133.01</v>
+        <v>-79.5</v>
       </c>
       <c r="L57" t="n">
-        <v>274.5</v>
+        <v>164.07</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>214.2</v>
+        <v>156.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-224.04</v>
+        <v>-164.01</v>
       </c>
       <c r="L58" t="n">
-        <v>309.96</v>
+        <v>226.91</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>30.8</v>
+        <v>21.81</v>
       </c>
       <c r="K59" t="n">
-        <v>-53.79</v>
+        <v>-38.08</v>
       </c>
       <c r="L59" t="n">
-        <v>61.98</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-70.53</v>
+        <v>-48.68</v>
       </c>
       <c r="K60" t="n">
-        <v>-21.29</v>
+        <v>-14.69</v>
       </c>
       <c r="L60" t="n">
-        <v>73.67</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.59</v>
+        <v>-16.94</v>
       </c>
       <c r="K61" t="n">
-        <v>-45.02</v>
+        <v>-33.76</v>
       </c>
       <c r="L61" t="n">
-        <v>50.37</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-18.95</v>
+        <v>-14.21</v>
       </c>
       <c r="K62" t="n">
-        <v>132.39</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>133.74</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>68.3</v>
+        <v>51.22</v>
       </c>
       <c r="K63" t="n">
-        <v>-14.85</v>
+        <v>-11.13</v>
       </c>
       <c r="L63" t="n">
-        <v>69.89</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>37.95</v>
+        <v>28.46</v>
       </c>
       <c r="K64" t="n">
-        <v>77.39</v>
+        <v>58.04</v>
       </c>
       <c r="L64" t="n">
-        <v>86.19</v>
+        <v>64.65000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-29.25</v>
+        <v>-21.23</v>
       </c>
       <c r="K65" t="n">
-        <v>68.81</v>
+        <v>49.93</v>
       </c>
       <c r="L65" t="n">
-        <v>74.77</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-108.92</v>
+        <v>-81.69</v>
       </c>
       <c r="K66" t="n">
-        <v>144.08</v>
+        <v>108.06</v>
       </c>
       <c r="L66" t="n">
-        <v>180.62</v>
+        <v>135.46</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-17.84</v>
+        <v>-13.18</v>
       </c>
       <c r="K67" t="n">
-        <v>97.73999999999999</v>
+        <v>72.22</v>
       </c>
       <c r="L67" t="n">
-        <v>99.34999999999999</v>
+        <v>73.42</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>100.25</v>
+        <v>73.5</v>
       </c>
       <c r="K68" t="n">
-        <v>-99.36</v>
+        <v>-72.84</v>
       </c>
       <c r="L68" t="n">
-        <v>141.15</v>
+        <v>103.48</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-93.81999999999999</v>
+        <v>-66.69</v>
       </c>
       <c r="K69" t="n">
-        <v>165.47</v>
+        <v>117.61</v>
       </c>
       <c r="L69" t="n">
-        <v>190.21</v>
+        <v>135.2</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>100.07</v>
+        <v>75.05</v>
       </c>
       <c r="K70" t="n">
-        <v>26.52</v>
+        <v>19.89</v>
       </c>
       <c r="L70" t="n">
-        <v>103.52</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-234.9</v>
+        <v>-176.18</v>
       </c>
       <c r="K71" t="n">
-        <v>50.08</v>
+        <v>37.56</v>
       </c>
       <c r="L71" t="n">
-        <v>240.18</v>
+        <v>180.14</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-197.89</v>
+        <v>-148.05</v>
       </c>
       <c r="K72" t="n">
-        <v>151.91</v>
+        <v>113.65</v>
       </c>
       <c r="L72" t="n">
-        <v>249.47</v>
+        <v>186.64</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-179.66</v>
+        <v>-132.15</v>
       </c>
       <c r="K73" t="n">
-        <v>183.18</v>
+        <v>134.74</v>
       </c>
       <c r="L73" t="n">
-        <v>256.57</v>
+        <v>188.73</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>77.23999999999999</v>
+        <v>57.06</v>
       </c>
       <c r="K74" t="n">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="L74" t="n">
-        <v>77.28</v>
+        <v>57.08</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>31.21</v>
+        <v>20.15</v>
       </c>
       <c r="K75" t="n">
-        <v>-88.16</v>
+        <v>-56.91</v>
       </c>
       <c r="L75" t="n">
-        <v>93.52</v>
+        <v>60.37</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.88</v>
+        <v>-10.37</v>
       </c>
       <c r="K76" t="n">
-        <v>27.8</v>
+        <v>10.73</v>
       </c>
       <c r="L76" t="n">
-        <v>38.67</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>84.81999999999999</v>
+        <v>62.38</v>
       </c>
       <c r="K77" t="n">
-        <v>-30.5</v>
+        <v>-22.43</v>
       </c>
       <c r="L77" t="n">
-        <v>90.14</v>
+        <v>66.29000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>52.89</v>
+        <v>36.92</v>
       </c>
       <c r="K78" t="n">
-        <v>66.18000000000001</v>
+        <v>46.21</v>
       </c>
       <c r="L78" t="n">
-        <v>84.72</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>74.75</v>
+        <v>56.07</v>
       </c>
       <c r="K79" t="n">
-        <v>-60.38</v>
+        <v>-45.29</v>
       </c>
       <c r="L79" t="n">
-        <v>96.09</v>
+        <v>72.06999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>137.9</v>
+        <v>101.9</v>
       </c>
       <c r="K80" t="n">
-        <v>-52.24</v>
+        <v>-38.6</v>
       </c>
       <c r="L80" t="n">
-        <v>147.46</v>
+        <v>108.97</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-65.2</v>
+        <v>-43.54</v>
       </c>
       <c r="K81" t="n">
-        <v>-51.56</v>
+        <v>-34.43</v>
       </c>
       <c r="L81" t="n">
-        <v>83.12</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-68.09</v>
+        <v>-23.06</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.74</v>
+        <v>-0.25</v>
       </c>
       <c r="L82" t="n">
-        <v>68.09</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>306.91</v>
+        <v>179.01</v>
       </c>
       <c r="K83" t="n">
-        <v>22.63</v>
+        <v>13.2</v>
       </c>
       <c r="L83" t="n">
-        <v>307.75</v>
+        <v>179.5</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-360.61</v>
+        <v>-221.06</v>
       </c>
       <c r="K84" t="n">
-        <v>-143.15</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>387.99</v>
+        <v>237.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>198.28</v>
+        <v>134.37</v>
       </c>
       <c r="K85" t="n">
-        <v>25.28</v>
+        <v>17.13</v>
       </c>
       <c r="L85" t="n">
-        <v>199.88</v>
+        <v>135.46</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-270.88</v>
+        <v>-175.88</v>
       </c>
       <c r="K86" t="n">
-        <v>-94.59999999999999</v>
+        <v>-61.42</v>
       </c>
       <c r="L86" t="n">
-        <v>286.93</v>
+        <v>186.29</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>243</v>
+        <v>182.25</v>
       </c>
       <c r="K87" t="n">
-        <v>-53.13</v>
+        <v>-39.85</v>
       </c>
       <c r="L87" t="n">
-        <v>248.74</v>
+        <v>186.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>35.48</v>
+        <v>25.03</v>
       </c>
       <c r="K88" t="n">
-        <v>-225.72</v>
+        <v>-159.23</v>
       </c>
       <c r="L88" t="n">
-        <v>228.5</v>
+        <v>161.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.56</v>
+        <v>-6.38</v>
       </c>
       <c r="K14" t="n">
-        <v>55.05</v>
+        <v>53.59</v>
       </c>
       <c r="L14" t="n">
-        <v>55.44</v>
+        <v>53.97</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>48.54</v>
+        <v>46.95</v>
       </c>
       <c r="K15" t="n">
-        <v>27.71</v>
+        <v>26.81</v>
       </c>
       <c r="L15" t="n">
-        <v>55.89</v>
+        <v>54.07</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>26.19</v>
+        <v>27.48</v>
       </c>
       <c r="K16" t="n">
-        <v>17.11</v>
+        <v>17.96</v>
       </c>
       <c r="L16" t="n">
-        <v>31.28</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>42.57</v>
+        <v>44.81</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.3</v>
+        <v>-3.47</v>
       </c>
       <c r="L17" t="n">
-        <v>42.7</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-32.36</v>
+        <v>-34.5</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.96</v>
+        <v>-24.48</v>
       </c>
       <c r="L18" t="n">
-        <v>39.68</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>20.62</v>
+        <v>19.88</v>
       </c>
       <c r="K19" t="n">
-        <v>85.22</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>87.68000000000001</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-75.7</v>
+        <v>-73.28</v>
       </c>
       <c r="K20" t="n">
-        <v>96.70999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="L20" t="n">
-        <v>122.81</v>
+        <v>118.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-47.15</v>
+        <v>-46.43</v>
       </c>
       <c r="K21" t="n">
-        <v>-99.33</v>
+        <v>-97.81999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>109.95</v>
+        <v>108.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-29.84</v>
+        <v>-28.89</v>
       </c>
       <c r="K22" t="n">
-        <v>112.49</v>
+        <v>108.91</v>
       </c>
       <c r="L22" t="n">
-        <v>116.38</v>
+        <v>112.67</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>59.94</v>
+        <v>61.23</v>
       </c>
       <c r="K23" t="n">
-        <v>74.72</v>
+        <v>76.34</v>
       </c>
       <c r="L23" t="n">
-        <v>95.79000000000001</v>
+        <v>97.86</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-77.5</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>16.7</v>
+        <v>17.78</v>
       </c>
       <c r="L24" t="n">
-        <v>79.28</v>
+        <v>84.39</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-17.52</v>
+        <v>-17.84</v>
       </c>
       <c r="K25" t="n">
-        <v>-107.5</v>
+        <v>-109.45</v>
       </c>
       <c r="L25" t="n">
-        <v>108.91</v>
+        <v>110.89</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-66.73</v>
+        <v>-66.39</v>
       </c>
       <c r="K26" t="n">
-        <v>-195.41</v>
+        <v>-194.4</v>
       </c>
       <c r="L26" t="n">
-        <v>206.49</v>
+        <v>205.42</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-69.73999999999999</v>
+        <v>-68.69</v>
       </c>
       <c r="K27" t="n">
-        <v>182.71</v>
+        <v>179.96</v>
       </c>
       <c r="L27" t="n">
-        <v>195.56</v>
+        <v>192.63</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>121.18</v>
+        <v>126.95</v>
       </c>
       <c r="K28" t="n">
-        <v>-45</v>
+        <v>-47.14</v>
       </c>
       <c r="L28" t="n">
-        <v>129.26</v>
+        <v>135.42</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.63</v>
+        <v>-27.55</v>
       </c>
       <c r="K29" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="L29" t="n">
-        <v>25.66</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>51.8</v>
+        <v>51.06</v>
       </c>
       <c r="K30" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="L30" t="n">
-        <v>51.89</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>45.84</v>
+        <v>46.07</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.64</v>
+        <v>-7.68</v>
       </c>
       <c r="L31" t="n">
-        <v>46.47</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>5.18</v>
+        <v>5.07</v>
       </c>
       <c r="K32" t="n">
-        <v>-80.56</v>
+        <v>-78.91</v>
       </c>
       <c r="L32" t="n">
-        <v>80.72</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.66</v>
+        <v>-2.7</v>
       </c>
       <c r="K33" t="n">
-        <v>58.27</v>
+        <v>59.15</v>
       </c>
       <c r="L33" t="n">
-        <v>58.33</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="K34" t="n">
-        <v>-61.37</v>
+        <v>-61.6</v>
       </c>
       <c r="L34" t="n">
-        <v>61.53</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>54.1</v>
+        <v>54.15</v>
       </c>
       <c r="K35" t="n">
-        <v>-72.98999999999999</v>
+        <v>-73.05</v>
       </c>
       <c r="L35" t="n">
-        <v>90.84999999999999</v>
+        <v>90.93000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>115.86</v>
+        <v>110.33</v>
       </c>
       <c r="K36" t="n">
-        <v>-86.88</v>
+        <v>-82.73</v>
       </c>
       <c r="L36" t="n">
-        <v>144.81</v>
+        <v>137.91</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-16.4</v>
+        <v>-16.55</v>
       </c>
       <c r="K37" t="n">
-        <v>78.3</v>
+        <v>79.02</v>
       </c>
       <c r="L37" t="n">
-        <v>80</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-120.81</v>
+        <v>-118.41</v>
       </c>
       <c r="K38" t="n">
-        <v>73.14</v>
+        <v>71.69</v>
       </c>
       <c r="L38" t="n">
-        <v>141.23</v>
+        <v>138.42</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-15.76</v>
+        <v>-16.28</v>
       </c>
       <c r="K39" t="n">
-        <v>-94.44</v>
+        <v>-97.56</v>
       </c>
       <c r="L39" t="n">
-        <v>95.73999999999999</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>62.36</v>
+        <v>61.3</v>
       </c>
       <c r="K40" t="n">
-        <v>121.08</v>
+        <v>119.02</v>
       </c>
       <c r="L40" t="n">
-        <v>136.19</v>
+        <v>133.88</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-66.94</v>
+        <v>-69.06</v>
       </c>
       <c r="K41" t="n">
-        <v>126.11</v>
+        <v>130.1</v>
       </c>
       <c r="L41" t="n">
-        <v>142.77</v>
+        <v>147.29</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>184.69</v>
+        <v>182.53</v>
       </c>
       <c r="K42" t="n">
-        <v>48.69</v>
+        <v>48.12</v>
       </c>
       <c r="L42" t="n">
-        <v>191</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-46.26</v>
+        <v>-45.54</v>
       </c>
       <c r="K43" t="n">
-        <v>211.08</v>
+        <v>207.8</v>
       </c>
       <c r="L43" t="n">
-        <v>216.09</v>
+        <v>212.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-24.18</v>
+        <v>-25.15</v>
       </c>
       <c r="K44" t="n">
-        <v>-18.79</v>
+        <v>-19.54</v>
       </c>
       <c r="L44" t="n">
-        <v>30.62</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-26.71</v>
+        <v>-27.99</v>
       </c>
       <c r="K45" t="n">
-        <v>17.42</v>
+        <v>18.26</v>
       </c>
       <c r="L45" t="n">
-        <v>31.89</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="K46" t="n">
-        <v>28.53</v>
+        <v>30.4</v>
       </c>
       <c r="L46" t="n">
-        <v>28.84</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-66.95999999999999</v>
+        <v>-65.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.41</v>
+        <v>-13.17</v>
       </c>
       <c r="L47" t="n">
-        <v>68.29000000000001</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-30.57</v>
+        <v>-30.01</v>
       </c>
       <c r="K48" t="n">
-        <v>67.93000000000001</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>74.48999999999999</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-69.64</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="L49" t="n">
-        <v>69.7</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>116.77</v>
+        <v>114.55</v>
       </c>
       <c r="K50" t="n">
-        <v>8.73</v>
+        <v>8.57</v>
       </c>
       <c r="L50" t="n">
-        <v>117.1</v>
+        <v>114.87</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="K51" t="n">
-        <v>81.62</v>
+        <v>81.92</v>
       </c>
       <c r="L51" t="n">
-        <v>81.92</v>
+        <v>82.22</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>18.5</v>
+        <v>18.72</v>
       </c>
       <c r="K52" t="n">
-        <v>73.92</v>
+        <v>74.8</v>
       </c>
       <c r="L52" t="n">
-        <v>76.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-48.14</v>
+        <v>-47.19</v>
       </c>
       <c r="K53" t="n">
-        <v>125.03</v>
+        <v>122.56</v>
       </c>
       <c r="L53" t="n">
-        <v>133.97</v>
+        <v>131.33</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>41.58</v>
+        <v>42.02</v>
       </c>
       <c r="K54" t="n">
-        <v>101.27</v>
+        <v>102.33</v>
       </c>
       <c r="L54" t="n">
-        <v>109.47</v>
+        <v>110.62</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>88.18000000000001</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-169.25</v>
+        <v>-161.67</v>
       </c>
       <c r="L55" t="n">
-        <v>190.84</v>
+        <v>182.3</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-29.51</v>
+        <v>-30.03</v>
       </c>
       <c r="K56" t="n">
-        <v>158.69</v>
+        <v>161.46</v>
       </c>
       <c r="L56" t="n">
-        <v>161.41</v>
+        <v>164.23</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>143.52</v>
+        <v>147.25</v>
       </c>
       <c r="K57" t="n">
-        <v>-79.5</v>
+        <v>-81.56999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>164.07</v>
+        <v>168.34</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>156.81</v>
+        <v>153.41</v>
       </c>
       <c r="K58" t="n">
-        <v>-164.01</v>
+        <v>-160.46</v>
       </c>
       <c r="L58" t="n">
-        <v>226.91</v>
+        <v>221.99</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>21.81</v>
+        <v>21.99</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.08</v>
+        <v>-38.39</v>
       </c>
       <c r="L59" t="n">
-        <v>43.89</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.68</v>
+        <v>-48.81</v>
       </c>
       <c r="K60" t="n">
-        <v>-14.69</v>
+        <v>-14.73</v>
       </c>
       <c r="L60" t="n">
-        <v>50.84</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.94</v>
+        <v>-17.36</v>
       </c>
       <c r="K61" t="n">
-        <v>-33.76</v>
+        <v>-34.6</v>
       </c>
       <c r="L61" t="n">
-        <v>37.77</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-14.21</v>
+        <v>-13.56</v>
       </c>
       <c r="K62" t="n">
-        <v>99.29000000000001</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>100.3</v>
+        <v>95.73</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>51.22</v>
+        <v>52.36</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.13</v>
+        <v>-11.38</v>
       </c>
       <c r="L63" t="n">
-        <v>52.42</v>
+        <v>53.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>28.46</v>
+        <v>28.28</v>
       </c>
       <c r="K64" t="n">
-        <v>58.04</v>
+        <v>57.68</v>
       </c>
       <c r="L64" t="n">
-        <v>64.65000000000001</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-21.23</v>
+        <v>-23.27</v>
       </c>
       <c r="K65" t="n">
-        <v>49.93</v>
+        <v>54.75</v>
       </c>
       <c r="L65" t="n">
-        <v>54.26</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-81.69</v>
+        <v>-78.45999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>108.06</v>
+        <v>103.79</v>
       </c>
       <c r="L66" t="n">
-        <v>135.46</v>
+        <v>130.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-13.18</v>
+        <v>-13.76</v>
       </c>
       <c r="K67" t="n">
-        <v>72.22</v>
+        <v>75.39</v>
       </c>
       <c r="L67" t="n">
-        <v>73.42</v>
+        <v>76.64</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>73.5</v>
+        <v>75.88</v>
       </c>
       <c r="K68" t="n">
-        <v>-72.84</v>
+        <v>-75.2</v>
       </c>
       <c r="L68" t="n">
-        <v>103.48</v>
+        <v>106.83</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-66.69</v>
+        <v>-65.81999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>117.61</v>
+        <v>116.09</v>
       </c>
       <c r="L69" t="n">
-        <v>135.2</v>
+        <v>133.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>75.05</v>
+        <v>79.58</v>
       </c>
       <c r="K70" t="n">
-        <v>19.89</v>
+        <v>21.09</v>
       </c>
       <c r="L70" t="n">
-        <v>77.64</v>
+        <v>82.31999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-176.18</v>
+        <v>-176.65</v>
       </c>
       <c r="K71" t="n">
-        <v>37.56</v>
+        <v>37.66</v>
       </c>
       <c r="L71" t="n">
-        <v>180.14</v>
+        <v>180.62</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-148.05</v>
+        <v>-148.67</v>
       </c>
       <c r="K72" t="n">
-        <v>113.65</v>
+        <v>114.13</v>
       </c>
       <c r="L72" t="n">
-        <v>186.64</v>
+        <v>187.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-132.15</v>
+        <v>-131.11</v>
       </c>
       <c r="K73" t="n">
-        <v>134.74</v>
+        <v>133.68</v>
       </c>
       <c r="L73" t="n">
-        <v>188.73</v>
+        <v>187.25</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>57.06</v>
+        <v>55.96</v>
       </c>
       <c r="K74" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="L74" t="n">
-        <v>57.08</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>20.15</v>
+        <v>20.02</v>
       </c>
       <c r="K75" t="n">
-        <v>-56.91</v>
+        <v>-56.54</v>
       </c>
       <c r="L75" t="n">
-        <v>60.37</v>
+        <v>59.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.37</v>
+        <v>-10.15</v>
       </c>
       <c r="K76" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="L76" t="n">
-        <v>14.93</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>62.38</v>
+        <v>62.62</v>
       </c>
       <c r="K77" t="n">
-        <v>-22.43</v>
+        <v>-22.52</v>
       </c>
       <c r="L77" t="n">
-        <v>66.29000000000001</v>
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>36.92</v>
+        <v>37.82</v>
       </c>
       <c r="K78" t="n">
-        <v>46.21</v>
+        <v>47.33</v>
       </c>
       <c r="L78" t="n">
-        <v>59.15</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>56.07</v>
+        <v>55.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-45.29</v>
+        <v>-44.77</v>
       </c>
       <c r="L79" t="n">
-        <v>72.06999999999999</v>
+        <v>71.26000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>101.9</v>
+        <v>100.14</v>
       </c>
       <c r="K80" t="n">
-        <v>-38.6</v>
+        <v>-37.93</v>
       </c>
       <c r="L80" t="n">
-        <v>108.97</v>
+        <v>107.08</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-43.54</v>
+        <v>-47.5</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.43</v>
+        <v>-37.56</v>
       </c>
       <c r="L81" t="n">
-        <v>55.51</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-23.06</v>
+        <v>-22.59</v>
       </c>
       <c r="K82" t="n">
         <v>-0.25</v>
       </c>
       <c r="L82" t="n">
-        <v>23.06</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>179.01</v>
+        <v>176.28</v>
       </c>
       <c r="K83" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="L83" t="n">
-        <v>179.5</v>
+        <v>176.76</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-221.06</v>
+        <v>-209.8</v>
       </c>
       <c r="K84" t="n">
-        <v>-87.76000000000001</v>
+        <v>-83.28</v>
       </c>
       <c r="L84" t="n">
-        <v>237.84</v>
+        <v>225.72</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>134.37</v>
+        <v>135.43</v>
       </c>
       <c r="K85" t="n">
-        <v>17.13</v>
+        <v>17.27</v>
       </c>
       <c r="L85" t="n">
-        <v>135.46</v>
+        <v>136.52</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-175.88</v>
+        <v>-176.94</v>
       </c>
       <c r="K86" t="n">
-        <v>-61.42</v>
+        <v>-61.79</v>
       </c>
       <c r="L86" t="n">
-        <v>186.29</v>
+        <v>187.42</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>182.25</v>
+        <v>182.05</v>
       </c>
       <c r="K87" t="n">
-        <v>-39.85</v>
+        <v>-39.81</v>
       </c>
       <c r="L87" t="n">
-        <v>186.56</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>25.03</v>
+        <v>25.51</v>
       </c>
       <c r="K88" t="n">
-        <v>-159.23</v>
+        <v>-162.28</v>
       </c>
       <c r="L88" t="n">
-        <v>161.18</v>
+        <v>164.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.38</v>
+        <v>-6.19</v>
       </c>
       <c r="K14" t="n">
-        <v>53.59</v>
+        <v>51.93</v>
       </c>
       <c r="L14" t="n">
-        <v>53.97</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>46.95</v>
+        <v>45.15</v>
       </c>
       <c r="K15" t="n">
-        <v>26.81</v>
+        <v>25.77</v>
       </c>
       <c r="L15" t="n">
-        <v>54.07</v>
+        <v>51.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>27.48</v>
+        <v>28.96</v>
       </c>
       <c r="K16" t="n">
-        <v>17.96</v>
+        <v>18.92</v>
       </c>
       <c r="L16" t="n">
-        <v>32.83</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>44.81</v>
+        <v>47.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.47</v>
+        <v>-3.67</v>
       </c>
       <c r="L17" t="n">
-        <v>44.94</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-34.5</v>
+        <v>-36.95</v>
       </c>
       <c r="K18" t="n">
-        <v>-24.48</v>
+        <v>-26.22</v>
       </c>
       <c r="L18" t="n">
-        <v>42.31</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>19.88</v>
+        <v>19.04</v>
       </c>
       <c r="K19" t="n">
-        <v>82.18000000000001</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>84.55</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-73.28</v>
+        <v>-70.51000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>93.62</v>
+        <v>90.08</v>
       </c>
       <c r="L20" t="n">
-        <v>118.89</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-46.43</v>
+        <v>-45.6</v>
       </c>
       <c r="K21" t="n">
-        <v>-97.81999999999999</v>
+        <v>-96.08</v>
       </c>
       <c r="L21" t="n">
-        <v>108.27</v>
+        <v>106.35</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-28.89</v>
+        <v>-27.8</v>
       </c>
       <c r="K22" t="n">
-        <v>108.91</v>
+        <v>104.81</v>
       </c>
       <c r="L22" t="n">
-        <v>112.67</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>61.23</v>
+        <v>62.71</v>
       </c>
       <c r="K23" t="n">
-        <v>76.34</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>97.86</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-82.48999999999999</v>
+        <v>-88.2</v>
       </c>
       <c r="K24" t="n">
-        <v>17.78</v>
+        <v>19.01</v>
       </c>
       <c r="L24" t="n">
-        <v>84.39</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-17.84</v>
+        <v>-18.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-109.45</v>
+        <v>-111.67</v>
       </c>
       <c r="L25" t="n">
-        <v>110.89</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-66.39</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-194.4</v>
+        <v>-193.25</v>
       </c>
       <c r="L26" t="n">
-        <v>205.42</v>
+        <v>204.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-68.69</v>
+        <v>-67.48999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>179.96</v>
+        <v>176.83</v>
       </c>
       <c r="L27" t="n">
-        <v>192.63</v>
+        <v>189.27</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>126.95</v>
+        <v>133.54</v>
       </c>
       <c r="K28" t="n">
-        <v>-47.14</v>
+        <v>-49.59</v>
       </c>
       <c r="L28" t="n">
-        <v>135.42</v>
+        <v>142.45</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.55</v>
+        <v>-29.73</v>
       </c>
       <c r="K29" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="L29" t="n">
-        <v>27.58</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>51.06</v>
+        <v>50.21</v>
       </c>
       <c r="K30" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="L30" t="n">
-        <v>51.14</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>46.07</v>
+        <v>46.33</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.68</v>
+        <v>-7.72</v>
       </c>
       <c r="L31" t="n">
-        <v>46.7</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
       <c r="K32" t="n">
-        <v>-78.91</v>
+        <v>-77.03</v>
       </c>
       <c r="L32" t="n">
-        <v>79.06999999999999</v>
+        <v>77.19</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.7</v>
+        <v>-2.75</v>
       </c>
       <c r="K33" t="n">
-        <v>59.15</v>
+        <v>60.15</v>
       </c>
       <c r="L33" t="n">
-        <v>59.21</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="K34" t="n">
-        <v>-61.6</v>
+        <v>-61.85</v>
       </c>
       <c r="L34" t="n">
-        <v>61.75</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>54.15</v>
+        <v>54.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-73.05</v>
+        <v>-73.12</v>
       </c>
       <c r="L35" t="n">
-        <v>90.93000000000001</v>
+        <v>91.02</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>110.33</v>
+        <v>104.02</v>
       </c>
       <c r="K36" t="n">
-        <v>-82.73</v>
+        <v>-78</v>
       </c>
       <c r="L36" t="n">
-        <v>137.91</v>
+        <v>130.01</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-16.55</v>
+        <v>-16.73</v>
       </c>
       <c r="K37" t="n">
-        <v>79.02</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>80.73999999999999</v>
+        <v>81.58</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-118.41</v>
+        <v>-115.67</v>
       </c>
       <c r="K38" t="n">
-        <v>71.69</v>
+        <v>70.03</v>
       </c>
       <c r="L38" t="n">
-        <v>138.42</v>
+        <v>135.21</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.28</v>
+        <v>-16.87</v>
       </c>
       <c r="K39" t="n">
-        <v>-97.56</v>
+        <v>-101.13</v>
       </c>
       <c r="L39" t="n">
-        <v>98.91</v>
+        <v>102.53</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>61.3</v>
+        <v>60.1</v>
       </c>
       <c r="K40" t="n">
-        <v>119.02</v>
+        <v>116.68</v>
       </c>
       <c r="L40" t="n">
-        <v>133.88</v>
+        <v>131.24</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-69.06</v>
+        <v>-71.48</v>
       </c>
       <c r="K41" t="n">
-        <v>130.1</v>
+        <v>134.66</v>
       </c>
       <c r="L41" t="n">
-        <v>147.29</v>
+        <v>152.45</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>182.53</v>
+        <v>180.06</v>
       </c>
       <c r="K42" t="n">
-        <v>48.12</v>
+        <v>47.47</v>
       </c>
       <c r="L42" t="n">
-        <v>188.76</v>
+        <v>186.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-45.54</v>
+        <v>-44.72</v>
       </c>
       <c r="K43" t="n">
-        <v>207.8</v>
+        <v>204.06</v>
       </c>
       <c r="L43" t="n">
-        <v>212.74</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-25.15</v>
+        <v>-26.26</v>
       </c>
       <c r="K44" t="n">
-        <v>-19.54</v>
+        <v>-20.4</v>
       </c>
       <c r="L44" t="n">
-        <v>31.85</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-27.99</v>
+        <v>-29.45</v>
       </c>
       <c r="K45" t="n">
-        <v>18.26</v>
+        <v>19.21</v>
       </c>
       <c r="L45" t="n">
-        <v>33.42</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="K46" t="n">
-        <v>30.4</v>
+        <v>32.54</v>
       </c>
       <c r="L46" t="n">
-        <v>30.73</v>
+        <v>32.89</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-65.78</v>
+        <v>-64.43000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.17</v>
+        <v>-12.9</v>
       </c>
       <c r="L47" t="n">
-        <v>67.09</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-30.01</v>
+        <v>-29.37</v>
       </c>
       <c r="K48" t="n">
-        <v>66.68000000000001</v>
+        <v>65.25</v>
       </c>
       <c r="L48" t="n">
-        <v>73.12</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-68.73999999999999</v>
+        <v>-67.72</v>
       </c>
       <c r="K49" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="L49" t="n">
-        <v>68.8</v>
+        <v>67.78</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>114.55</v>
+        <v>112</v>
       </c>
       <c r="K50" t="n">
-        <v>8.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>114.87</v>
+        <v>112.32</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>7.02</v>
+        <v>7.05</v>
       </c>
       <c r="K51" t="n">
-        <v>81.92</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>82.22</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>18.72</v>
+        <v>18.97</v>
       </c>
       <c r="K52" t="n">
-        <v>74.8</v>
+        <v>75.8</v>
       </c>
       <c r="L52" t="n">
-        <v>77.09999999999999</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-47.19</v>
+        <v>-46.11</v>
       </c>
       <c r="K53" t="n">
-        <v>122.56</v>
+        <v>119.74</v>
       </c>
       <c r="L53" t="n">
-        <v>131.33</v>
+        <v>128.31</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>42.02</v>
+        <v>42.52</v>
       </c>
       <c r="K54" t="n">
-        <v>102.33</v>
+        <v>103.55</v>
       </c>
       <c r="L54" t="n">
-        <v>110.62</v>
+        <v>111.94</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>84.23999999999999</v>
+        <v>79.73</v>
       </c>
       <c r="K55" t="n">
-        <v>-161.67</v>
+        <v>-153.01</v>
       </c>
       <c r="L55" t="n">
-        <v>182.3</v>
+        <v>172.54</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-30.03</v>
+        <v>-30.61</v>
       </c>
       <c r="K56" t="n">
-        <v>161.46</v>
+        <v>164.63</v>
       </c>
       <c r="L56" t="n">
-        <v>164.23</v>
+        <v>167.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>147.25</v>
+        <v>151.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-81.56999999999999</v>
+        <v>-83.93000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>168.34</v>
+        <v>173.22</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>153.41</v>
+        <v>149.53</v>
       </c>
       <c r="K58" t="n">
-        <v>-160.46</v>
+        <v>-156.4</v>
       </c>
       <c r="L58" t="n">
-        <v>221.99</v>
+        <v>216.38</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>21.99</v>
+        <v>22.19</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.39</v>
+        <v>-38.75</v>
       </c>
       <c r="L59" t="n">
-        <v>44.24</v>
+        <v>44.65</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.81</v>
+        <v>-48.96</v>
       </c>
       <c r="K60" t="n">
-        <v>-14.73</v>
+        <v>-14.78</v>
       </c>
       <c r="L60" t="n">
-        <v>50.98</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.36</v>
+        <v>-17.84</v>
       </c>
       <c r="K61" t="n">
-        <v>-34.6</v>
+        <v>-35.55</v>
       </c>
       <c r="L61" t="n">
-        <v>38.71</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-13.56</v>
+        <v>-12.82</v>
       </c>
       <c r="K62" t="n">
-        <v>94.76000000000001</v>
+        <v>89.59</v>
       </c>
       <c r="L62" t="n">
-        <v>95.73</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>52.36</v>
+        <v>53.67</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.38</v>
+        <v>-11.67</v>
       </c>
       <c r="L63" t="n">
-        <v>53.59</v>
+        <v>54.92</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>28.28</v>
+        <v>28.08</v>
       </c>
       <c r="K64" t="n">
-        <v>57.68</v>
+        <v>57.27</v>
       </c>
       <c r="L64" t="n">
-        <v>64.25</v>
+        <v>63.79</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-23.27</v>
+        <v>-25.61</v>
       </c>
       <c r="K65" t="n">
-        <v>54.75</v>
+        <v>60.25</v>
       </c>
       <c r="L65" t="n">
-        <v>59.49</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-78.45999999999999</v>
+        <v>-74.77</v>
       </c>
       <c r="K66" t="n">
-        <v>103.79</v>
+        <v>98.91</v>
       </c>
       <c r="L66" t="n">
-        <v>130.11</v>
+        <v>123.99</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-13.76</v>
+        <v>-14.42</v>
       </c>
       <c r="K67" t="n">
-        <v>75.39</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>76.64</v>
+        <v>80.31999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>75.88</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-75.2</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>106.83</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-65.81999999999999</v>
+        <v>-64.84</v>
       </c>
       <c r="K69" t="n">
-        <v>116.09</v>
+        <v>114.35</v>
       </c>
       <c r="L69" t="n">
-        <v>133.45</v>
+        <v>131.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>79.58</v>
+        <v>84.75</v>
       </c>
       <c r="K70" t="n">
-        <v>21.09</v>
+        <v>22.46</v>
       </c>
       <c r="L70" t="n">
-        <v>82.31999999999999</v>
+        <v>87.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-176.65</v>
+        <v>-177.19</v>
       </c>
       <c r="K71" t="n">
-        <v>37.66</v>
+        <v>37.78</v>
       </c>
       <c r="L71" t="n">
-        <v>180.62</v>
+        <v>181.17</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-148.67</v>
+        <v>-149.38</v>
       </c>
       <c r="K72" t="n">
-        <v>114.13</v>
+        <v>114.68</v>
       </c>
       <c r="L72" t="n">
-        <v>187.43</v>
+        <v>188.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-131.11</v>
+        <v>-129.93</v>
       </c>
       <c r="K73" t="n">
-        <v>133.68</v>
+        <v>132.48</v>
       </c>
       <c r="L73" t="n">
-        <v>187.25</v>
+        <v>185.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>55.96</v>
+        <v>54.71</v>
       </c>
       <c r="K74" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="L74" t="n">
-        <v>55.99</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>20.02</v>
+        <v>19.87</v>
       </c>
       <c r="K75" t="n">
-        <v>-56.54</v>
+        <v>-56.12</v>
       </c>
       <c r="L75" t="n">
-        <v>59.98</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.15</v>
+        <v>-11.02</v>
       </c>
       <c r="K76" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="L76" t="n">
-        <v>14.61</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>62.62</v>
+        <v>62.89</v>
       </c>
       <c r="K77" t="n">
-        <v>-22.52</v>
+        <v>-22.61</v>
       </c>
       <c r="L77" t="n">
-        <v>66.54000000000001</v>
+        <v>66.83</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>37.82</v>
+        <v>38.85</v>
       </c>
       <c r="K78" t="n">
-        <v>47.33</v>
+        <v>48.61</v>
       </c>
       <c r="L78" t="n">
-        <v>60.59</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>55.43</v>
+        <v>54.71</v>
       </c>
       <c r="K79" t="n">
-        <v>-44.77</v>
+        <v>-44.19</v>
       </c>
       <c r="L79" t="n">
-        <v>71.26000000000001</v>
+        <v>70.33</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>100.14</v>
+        <v>98.13</v>
       </c>
       <c r="K80" t="n">
-        <v>-37.93</v>
+        <v>-37.17</v>
       </c>
       <c r="L80" t="n">
-        <v>107.08</v>
+        <v>104.93</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-47.5</v>
+        <v>-52.03</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.56</v>
+        <v>-41.15</v>
       </c>
       <c r="L81" t="n">
-        <v>60.56</v>
+        <v>66.34</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-22.59</v>
+        <v>-24.43</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="L82" t="n">
-        <v>22.6</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>176.28</v>
+        <v>173.15</v>
       </c>
       <c r="K83" t="n">
-        <v>13</v>
+        <v>12.77</v>
       </c>
       <c r="L83" t="n">
-        <v>176.76</v>
+        <v>173.62</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-209.8</v>
+        <v>-196.93</v>
       </c>
       <c r="K84" t="n">
-        <v>-83.28</v>
+        <v>-78.18000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>225.72</v>
+        <v>211.88</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>135.43</v>
+        <v>136.63</v>
       </c>
       <c r="K85" t="n">
-        <v>17.27</v>
+        <v>17.42</v>
       </c>
       <c r="L85" t="n">
-        <v>136.52</v>
+        <v>137.74</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-176.94</v>
+        <v>-178.16</v>
       </c>
       <c r="K86" t="n">
-        <v>-61.79</v>
+        <v>-62.22</v>
       </c>
       <c r="L86" t="n">
-        <v>187.42</v>
+        <v>188.71</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>182.05</v>
+        <v>181.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-39.81</v>
+        <v>-39.76</v>
       </c>
       <c r="L87" t="n">
-        <v>186.35</v>
+        <v>186.11</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>25.51</v>
+        <v>26.06</v>
       </c>
       <c r="K88" t="n">
-        <v>-162.28</v>
+        <v>-165.78</v>
       </c>
       <c r="L88" t="n">
-        <v>164.27</v>
+        <v>167.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -628,25 +628,25 @@
         <v>1.89</v>
       </c>
       <c r="F14" t="n">
-        <v>5.37</v>
+        <v>3.07</v>
       </c>
       <c r="G14" t="n">
-        <v>334.3</v>
+        <v>312.1</v>
       </c>
       <c r="H14" t="n">
-        <v>91</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.19</v>
+        <v>-6.53</v>
       </c>
       <c r="K14" t="n">
-        <v>51.93</v>
+        <v>52.05</v>
       </c>
       <c r="L14" t="n">
-        <v>52.3</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>1.32</v>
       </c>
       <c r="F15" t="n">
-        <v>6.54</v>
+        <v>3.92</v>
       </c>
       <c r="G15" t="n">
-        <v>319.6</v>
+        <v>335.4</v>
       </c>
       <c r="H15" t="n">
-        <v>95.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>45.15</v>
+        <v>50.14</v>
       </c>
       <c r="K15" t="n">
-        <v>25.77</v>
+        <v>28.86</v>
       </c>
       <c r="L15" t="n">
-        <v>51.98</v>
+        <v>57.86</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>1.55</v>
       </c>
       <c r="F16" t="n">
-        <v>5.99</v>
+        <v>2.08</v>
       </c>
       <c r="G16" t="n">
-        <v>342.4</v>
+        <v>324.4</v>
       </c>
       <c r="H16" t="n">
-        <v>91.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>28.96</v>
+        <v>29.32</v>
       </c>
       <c r="K16" t="n">
-        <v>18.92</v>
+        <v>19.76</v>
       </c>
       <c r="L16" t="n">
-        <v>34.59</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>1.61</v>
       </c>
       <c r="F17" t="n">
-        <v>6.24</v>
+        <v>5.01</v>
       </c>
       <c r="G17" t="n">
-        <v>336.2</v>
+        <v>329.4</v>
       </c>
       <c r="H17" t="n">
-        <v>95.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>47.37</v>
+        <v>60.42</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.67</v>
+        <v>-3.06</v>
       </c>
       <c r="L17" t="n">
-        <v>47.51</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>1.77</v>
       </c>
       <c r="F18" t="n">
-        <v>6.92</v>
+        <v>3.11</v>
       </c>
       <c r="G18" t="n">
-        <v>344.5</v>
+        <v>343</v>
       </c>
       <c r="H18" t="n">
-        <v>91.8</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-36.95</v>
+        <v>-41.04</v>
       </c>
       <c r="K18" t="n">
-        <v>-26.22</v>
+        <v>-26.43</v>
       </c>
       <c r="L18" t="n">
-        <v>45.31</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>1.96</v>
       </c>
       <c r="F19" t="n">
-        <v>7.01</v>
+        <v>4.88</v>
       </c>
       <c r="G19" t="n">
-        <v>330.2</v>
+        <v>344.7</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>19.04</v>
+        <v>20.94</v>
       </c>
       <c r="K19" t="n">
-        <v>78.70999999999999</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>80.98</v>
+        <v>90.26000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>1.7</v>
       </c>
       <c r="F20" t="n">
-        <v>5.99</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>339.3</v>
+        <v>324.4</v>
       </c>
       <c r="H20" t="n">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-70.51000000000001</v>
+        <v>-77.11</v>
       </c>
       <c r="K20" t="n">
-        <v>90.08</v>
+        <v>97.73</v>
       </c>
       <c r="L20" t="n">
-        <v>114.4</v>
+        <v>124.49</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>1.93</v>
       </c>
       <c r="F21" t="n">
-        <v>5.86</v>
+        <v>3.76</v>
       </c>
       <c r="G21" t="n">
-        <v>327.7</v>
+        <v>321.8</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-45.6</v>
+        <v>-52.6</v>
       </c>
       <c r="K21" t="n">
-        <v>-96.08</v>
+        <v>-99.52</v>
       </c>
       <c r="L21" t="n">
-        <v>106.35</v>
+        <v>112.57</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>1.57</v>
       </c>
       <c r="F22" t="n">
-        <v>6.01</v>
+        <v>4.2</v>
       </c>
       <c r="G22" t="n">
-        <v>333.4</v>
+        <v>324.8</v>
       </c>
       <c r="H22" t="n">
-        <v>95.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-27.8</v>
+        <v>-33.57</v>
       </c>
       <c r="K22" t="n">
-        <v>104.81</v>
+        <v>120.5</v>
       </c>
       <c r="L22" t="n">
-        <v>108.44</v>
+        <v>125.09</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>1.63</v>
       </c>
       <c r="F23" t="n">
-        <v>6.72</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>326.8</v>
+        <v>339</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>94.7</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>62.71</v>
+        <v>59.53</v>
       </c>
       <c r="K23" t="n">
-        <v>78.18000000000001</v>
+        <v>89.69</v>
       </c>
       <c r="L23" t="n">
-        <v>100.22</v>
+        <v>107.65</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>1.61</v>
       </c>
       <c r="F24" t="n">
-        <v>6.14</v>
+        <v>3.57</v>
       </c>
       <c r="G24" t="n">
-        <v>336.8</v>
+        <v>327.5</v>
       </c>
       <c r="H24" t="n">
-        <v>93.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-88.2</v>
+        <v>-100.92</v>
       </c>
       <c r="K24" t="n">
-        <v>19.01</v>
+        <v>35.01</v>
       </c>
       <c r="L24" t="n">
-        <v>90.23</v>
+        <v>106.82</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>1.49</v>
       </c>
       <c r="F25" t="n">
-        <v>6.35</v>
+        <v>4.82</v>
       </c>
       <c r="G25" t="n">
-        <v>330.2</v>
+        <v>331.7</v>
       </c>
       <c r="H25" t="n">
-        <v>94.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-18.2</v>
+        <v>-28.15</v>
       </c>
       <c r="K25" t="n">
-        <v>-111.67</v>
+        <v>-120.85</v>
       </c>
       <c r="L25" t="n">
-        <v>113.15</v>
+        <v>124.08</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.19</v>
       </c>
       <c r="F26" t="n">
-        <v>5.51</v>
+        <v>7.24</v>
       </c>
       <c r="G26" t="n">
-        <v>340</v>
+        <v>314.8</v>
       </c>
       <c r="H26" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-65.98999999999999</v>
+        <v>-115.46</v>
       </c>
       <c r="K26" t="n">
-        <v>-193.25</v>
+        <v>-208.22</v>
       </c>
       <c r="L26" t="n">
-        <v>204.21</v>
+        <v>238.09</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>1.67</v>
       </c>
       <c r="F27" t="n">
-        <v>6.31</v>
+        <v>7.19</v>
       </c>
       <c r="G27" t="n">
-        <v>333.8</v>
+        <v>330.7</v>
       </c>
       <c r="H27" t="n">
-        <v>92</v>
+        <v>98.2</v>
       </c>
       <c r="I27" t="n">
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-67.48999999999999</v>
+        <v>-94.11</v>
       </c>
       <c r="K27" t="n">
-        <v>176.83</v>
+        <v>234.51</v>
       </c>
       <c r="L27" t="n">
-        <v>189.27</v>
+        <v>252.68</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>1.7</v>
       </c>
       <c r="F28" t="n">
-        <v>6.28</v>
+        <v>3.83</v>
       </c>
       <c r="G28" t="n">
-        <v>336.5</v>
+        <v>330.1</v>
       </c>
       <c r="H28" t="n">
-        <v>93.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>133.54</v>
+        <v>144.19</v>
       </c>
       <c r="K28" t="n">
-        <v>-49.59</v>
+        <v>-21.71</v>
       </c>
       <c r="L28" t="n">
-        <v>142.45</v>
+        <v>145.82</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>1.21</v>
       </c>
       <c r="F29" t="n">
-        <v>6.29</v>
+        <v>6.46</v>
       </c>
       <c r="G29" t="n">
-        <v>345.7</v>
+        <v>330.5</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.73</v>
+        <v>-42.23</v>
       </c>
       <c r="K29" t="n">
-        <v>1.42</v>
+        <v>2.47</v>
       </c>
       <c r="L29" t="n">
-        <v>29.77</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>1.54</v>
       </c>
       <c r="F30" t="n">
-        <v>6.3</v>
+        <v>7.24</v>
       </c>
       <c r="G30" t="n">
-        <v>334.4</v>
+        <v>330.5</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>50.21</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>50.29</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>1.69</v>
       </c>
       <c r="F31" t="n">
-        <v>6.73</v>
+        <v>4.26</v>
       </c>
       <c r="G31" t="n">
         <v>319.1</v>
       </c>
       <c r="H31" t="n">
-        <v>97.2</v>
+        <v>99.2</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>46.33</v>
+        <v>-5.06</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.72</v>
+        <v>50.13</v>
       </c>
       <c r="L31" t="n">
-        <v>46.97</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="32">
@@ -1381,10 +1381,10 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="F32" t="n">
-        <v>6.11</v>
+        <v>3.07</v>
       </c>
       <c r="G32" t="n">
         <v>323.6</v>
@@ -1393,16 +1393,16 @@
         <v>99.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>4.95</v>
+        <v>-3.32</v>
       </c>
       <c r="K32" t="n">
-        <v>-77.03</v>
+        <v>21.23</v>
       </c>
       <c r="L32" t="n">
-        <v>77.19</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="33">
@@ -1423,10 +1423,10 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="F33" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="G33" t="n">
         <v>331.9</v>
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.75</v>
+        <v>-75.31</v>
       </c>
       <c r="K33" t="n">
-        <v>60.15</v>
+        <v>-0.38</v>
       </c>
       <c r="L33" t="n">
-        <v>60.21</v>
+        <v>75.31</v>
       </c>
     </row>
     <row r="34">
@@ -1465,10 +1465,10 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="F34" t="n">
-        <v>6.26</v>
+        <v>5.58</v>
       </c>
       <c r="G34" t="n">
         <v>338.1</v>
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>4.44</v>
+        <v>-67.39</v>
       </c>
       <c r="K34" t="n">
-        <v>-61.85</v>
+        <v>10.69</v>
       </c>
       <c r="L34" t="n">
-        <v>62.01</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="35">
@@ -1507,10 +1507,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="F35" t="n">
-        <v>6.49</v>
+        <v>2.02</v>
       </c>
       <c r="G35" t="n">
         <v>324.7</v>
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>54.2</v>
+        <v>-65.81</v>
       </c>
       <c r="K35" t="n">
-        <v>-73.12</v>
+        <v>61.8</v>
       </c>
       <c r="L35" t="n">
-        <v>91.02</v>
+        <v>90.28</v>
       </c>
     </row>
     <row r="36">
@@ -1549,10 +1549,10 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="F36" t="n">
-        <v>6.06</v>
+        <v>5.18</v>
       </c>
       <c r="G36" t="n">
         <v>335.6</v>
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>104.02</v>
+        <v>37.25</v>
       </c>
       <c r="K36" t="n">
-        <v>-78</v>
+        <v>128.45</v>
       </c>
       <c r="L36" t="n">
-        <v>130.01</v>
+        <v>133.74</v>
       </c>
     </row>
     <row r="37">
@@ -1591,10 +1591,10 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="F37" t="n">
-        <v>6.86</v>
+        <v>4.24</v>
       </c>
       <c r="G37" t="n">
         <v>320.2</v>
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-16.73</v>
+        <v>-102.56</v>
       </c>
       <c r="K37" t="n">
-        <v>79.84999999999999</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>81.58</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="38">
@@ -1633,10 +1633,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>4.51</v>
       </c>
       <c r="G38" t="n">
         <v>328.8</v>
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-115.67</v>
+        <v>10.37</v>
       </c>
       <c r="K38" t="n">
-        <v>70.03</v>
+        <v>-129.81</v>
       </c>
       <c r="L38" t="n">
-        <v>135.21</v>
+        <v>130.23</v>
       </c>
     </row>
     <row r="39">
@@ -1675,10 +1675,10 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="F39" t="n">
-        <v>6.08</v>
+        <v>6.75</v>
       </c>
       <c r="G39" t="n">
         <v>324.8</v>
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.87</v>
+        <v>-104.37</v>
       </c>
       <c r="K39" t="n">
-        <v>-101.13</v>
+        <v>25.32</v>
       </c>
       <c r="L39" t="n">
-        <v>102.53</v>
+        <v>107.39</v>
       </c>
     </row>
     <row r="40">
@@ -1717,10 +1717,10 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="F40" t="n">
-        <v>6.78</v>
+        <v>4.16</v>
       </c>
       <c r="G40" t="n">
         <v>331.7</v>
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>60.1</v>
+        <v>147.16</v>
       </c>
       <c r="K40" t="n">
-        <v>116.68</v>
+        <v>71.25</v>
       </c>
       <c r="L40" t="n">
-        <v>131.24</v>
+        <v>163.51</v>
       </c>
     </row>
     <row r="41">
@@ -1759,10 +1759,10 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="F41" t="n">
-        <v>6.22</v>
+        <v>7.24</v>
       </c>
       <c r="G41" t="n">
         <v>336.3</v>
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-71.48</v>
+        <v>-74.38</v>
       </c>
       <c r="K41" t="n">
-        <v>134.66</v>
+        <v>-22.5</v>
       </c>
       <c r="L41" t="n">
-        <v>152.45</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1801,10 +1801,10 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="F42" t="n">
-        <v>6.21</v>
+        <v>5.91</v>
       </c>
       <c r="G42" t="n">
         <v>344.4</v>
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>180.06</v>
+        <v>49.99</v>
       </c>
       <c r="K42" t="n">
-        <v>47.47</v>
+        <v>230.24</v>
       </c>
       <c r="L42" t="n">
-        <v>186.21</v>
+        <v>235.61</v>
       </c>
     </row>
     <row r="43">
@@ -1843,10 +1843,10 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="F43" t="n">
-        <v>6.87</v>
+        <v>3.6</v>
       </c>
       <c r="G43" t="n">
         <v>332.3</v>
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-44.72</v>
+        <v>-196.36</v>
       </c>
       <c r="K43" t="n">
-        <v>204.06</v>
+        <v>-5.9</v>
       </c>
       <c r="L43" t="n">
-        <v>208.9</v>
+        <v>196.45</v>
       </c>
     </row>
     <row r="44">
@@ -1885,10 +1885,10 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.44</v>
+        <v>2.11</v>
       </c>
       <c r="F44" t="n">
-        <v>5.67</v>
+        <v>7.24</v>
       </c>
       <c r="G44" t="n">
         <v>346.4</v>
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-26.26</v>
+        <v>59.47</v>
       </c>
       <c r="K44" t="n">
-        <v>-20.4</v>
+        <v>-19.77</v>
       </c>
       <c r="L44" t="n">
-        <v>33.25</v>
+        <v>62.67</v>
       </c>
     </row>
     <row r="45">
@@ -1927,10 +1927,10 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="F45" t="n">
-        <v>6.03</v>
+        <v>3.53</v>
       </c>
       <c r="G45" t="n">
         <v>336.5</v>
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.45</v>
+        <v>-45.01</v>
       </c>
       <c r="K45" t="n">
-        <v>19.21</v>
+        <v>-18.69</v>
       </c>
       <c r="L45" t="n">
-        <v>35.17</v>
+        <v>48.73</v>
       </c>
     </row>
     <row r="46">
@@ -1969,28 +1969,28 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.77</v>
+        <v>2.72</v>
       </c>
       <c r="F46" t="n">
-        <v>6.18</v>
+        <v>7.24</v>
       </c>
       <c r="G46" t="n">
-        <v>339.3</v>
+        <v>328.1</v>
       </c>
       <c r="H46" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I46" t="n">
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>4.82</v>
+        <v>5.7</v>
       </c>
       <c r="K46" t="n">
-        <v>32.54</v>
+        <v>49.54</v>
       </c>
       <c r="L46" t="n">
-        <v>32.89</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>1.54</v>
       </c>
       <c r="F47" t="n">
-        <v>6.58</v>
+        <v>3.66</v>
       </c>
       <c r="G47" t="n">
-        <v>324.5</v>
+        <v>336.3</v>
       </c>
       <c r="H47" t="n">
-        <v>95.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-64.43000000000001</v>
+        <v>-70.52</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.9</v>
+        <v>-13.2</v>
       </c>
       <c r="L47" t="n">
-        <v>65.70999999999999</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>1.8</v>
       </c>
       <c r="F48" t="n">
-        <v>6.14</v>
+        <v>4.76</v>
       </c>
       <c r="G48" t="n">
-        <v>327.4</v>
+        <v>327.5</v>
       </c>
       <c r="H48" t="n">
-        <v>94.2</v>
+        <v>95</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-29.37</v>
+        <v>-33.27</v>
       </c>
       <c r="K48" t="n">
-        <v>65.25</v>
+        <v>73.55</v>
       </c>
       <c r="L48" t="n">
-        <v>71.55</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>1.94</v>
       </c>
       <c r="F49" t="n">
-        <v>6.06</v>
+        <v>6.65</v>
       </c>
       <c r="G49" t="n">
-        <v>340.3</v>
+        <v>325.8</v>
       </c>
       <c r="H49" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-67.72</v>
+        <v>-83.94</v>
       </c>
       <c r="K49" t="n">
-        <v>2.89</v>
+        <v>4.5</v>
       </c>
       <c r="L49" t="n">
-        <v>67.78</v>
+        <v>84.06</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>2.15</v>
       </c>
       <c r="F50" t="n">
-        <v>6.5</v>
+        <v>7.24</v>
       </c>
       <c r="G50" t="n">
-        <v>328.5</v>
+        <v>334.7</v>
       </c>
       <c r="H50" t="n">
-        <v>97.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>112</v>
+        <v>115.01</v>
       </c>
       <c r="K50" t="n">
-        <v>8.380000000000001</v>
+        <v>14.03</v>
       </c>
       <c r="L50" t="n">
-        <v>112.32</v>
+        <v>115.87</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>1.77</v>
       </c>
       <c r="F51" t="n">
-        <v>6.74</v>
+        <v>3.47</v>
       </c>
       <c r="G51" t="n">
-        <v>324</v>
+        <v>339.4</v>
       </c>
       <c r="H51" t="n">
-        <v>98.8</v>
+        <v>93.3</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>7.05</v>
+        <v>6.6</v>
       </c>
       <c r="K51" t="n">
-        <v>82.26000000000001</v>
+        <v>92.91</v>
       </c>
       <c r="L51" t="n">
-        <v>82.56</v>
+        <v>93.14</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>1.42</v>
       </c>
       <c r="F52" t="n">
-        <v>6.53</v>
+        <v>3.89</v>
       </c>
       <c r="G52" t="n">
-        <v>331.7</v>
+        <v>335.2</v>
       </c>
       <c r="H52" t="n">
-        <v>94.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>18.97</v>
+        <v>18.98</v>
       </c>
       <c r="K52" t="n">
-        <v>75.8</v>
+        <v>86.13</v>
       </c>
       <c r="L52" t="n">
-        <v>78.14</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>1.96</v>
       </c>
       <c r="F53" t="n">
-        <v>5.58</v>
+        <v>7.24</v>
       </c>
       <c r="G53" t="n">
-        <v>337.8</v>
+        <v>316.2</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-46.11</v>
+        <v>-71.41</v>
       </c>
       <c r="K53" t="n">
-        <v>119.74</v>
+        <v>163.91</v>
       </c>
       <c r="L53" t="n">
-        <v>128.31</v>
+        <v>178.79</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>1.87</v>
       </c>
       <c r="F54" t="n">
-        <v>6.2</v>
+        <v>4.89</v>
       </c>
       <c r="G54" t="n">
-        <v>335.6</v>
+        <v>328.6</v>
       </c>
       <c r="H54" t="n">
-        <v>93.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>42.52</v>
+        <v>38.47</v>
       </c>
       <c r="K54" t="n">
-        <v>103.55</v>
+        <v>125.81</v>
       </c>
       <c r="L54" t="n">
-        <v>111.94</v>
+        <v>131.56</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>1.43</v>
       </c>
       <c r="F55" t="n">
-        <v>6.15</v>
+        <v>5.64</v>
       </c>
       <c r="G55" t="n">
-        <v>338.3</v>
+        <v>327.7</v>
       </c>
       <c r="H55" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>79.73</v>
+        <v>84.12</v>
       </c>
       <c r="K55" t="n">
-        <v>-153.01</v>
+        <v>-164.39</v>
       </c>
       <c r="L55" t="n">
-        <v>172.54</v>
+        <v>184.66</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>1.99</v>
       </c>
       <c r="F56" t="n">
-        <v>6.79</v>
+        <v>4.87</v>
       </c>
       <c r="G56" t="n">
-        <v>333.3</v>
+        <v>340.4</v>
       </c>
       <c r="H56" t="n">
-        <v>93</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-30.61</v>
+        <v>-36.71</v>
       </c>
       <c r="K56" t="n">
-        <v>164.63</v>
+        <v>180.22</v>
       </c>
       <c r="L56" t="n">
-        <v>167.45</v>
+        <v>183.92</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>2.94</v>
       </c>
       <c r="F57" t="n">
-        <v>5.88</v>
+        <v>7.24</v>
       </c>
       <c r="G57" t="n">
-        <v>330.3</v>
+        <v>322.2</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>151.52</v>
+        <v>149.22</v>
       </c>
       <c r="K57" t="n">
-        <v>-83.93000000000001</v>
+        <v>-58.68</v>
       </c>
       <c r="L57" t="n">
-        <v>173.22</v>
+        <v>160.34</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>1.95</v>
       </c>
       <c r="F58" t="n">
-        <v>6.23</v>
+        <v>3.95</v>
       </c>
       <c r="G58" t="n">
-        <v>330.2</v>
+        <v>329.2</v>
       </c>
       <c r="H58" t="n">
-        <v>91.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>149.53</v>
+        <v>146.66</v>
       </c>
       <c r="K58" t="n">
-        <v>-156.4</v>
+        <v>-145.01</v>
       </c>
       <c r="L58" t="n">
-        <v>216.38</v>
+        <v>206.25</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>2.01</v>
       </c>
       <c r="F59" t="n">
-        <v>6.44</v>
+        <v>6.45</v>
       </c>
       <c r="G59" t="n">
-        <v>333.9</v>
+        <v>333.4</v>
       </c>
       <c r="H59" t="n">
-        <v>96.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="I59" t="n">
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>22.19</v>
+        <v>26.14</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.75</v>
+        <v>-45.6</v>
       </c>
       <c r="L59" t="n">
-        <v>44.65</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>2.09</v>
       </c>
       <c r="F60" t="n">
-        <v>6.25</v>
+        <v>7.24</v>
       </c>
       <c r="G60" t="n">
-        <v>318.6</v>
+        <v>329.7</v>
       </c>
       <c r="H60" t="n">
-        <v>97.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.96</v>
+        <v>-59.44</v>
       </c>
       <c r="K60" t="n">
-        <v>-14.78</v>
+        <v>-17.29</v>
       </c>
       <c r="L60" t="n">
-        <v>51.14</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>1.61</v>
       </c>
       <c r="F61" t="n">
-        <v>6.28</v>
+        <v>5.81</v>
       </c>
       <c r="G61" t="n">
-        <v>333.4</v>
+        <v>330.1</v>
       </c>
       <c r="H61" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.84</v>
+        <v>-22.99</v>
       </c>
       <c r="K61" t="n">
-        <v>-35.55</v>
+        <v>-44.82</v>
       </c>
       <c r="L61" t="n">
-        <v>39.78</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>1.75</v>
       </c>
       <c r="F62" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>331.8</v>
+        <v>329.1</v>
       </c>
       <c r="H62" t="n">
-        <v>96.7</v>
+        <v>97.2</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-12.82</v>
+        <v>-15.5</v>
       </c>
       <c r="K62" t="n">
-        <v>89.59</v>
+        <v>105.53</v>
       </c>
       <c r="L62" t="n">
-        <v>90.5</v>
+        <v>106.66</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>1.75</v>
       </c>
       <c r="F63" t="n">
-        <v>6.64</v>
+        <v>7.24</v>
       </c>
       <c r="G63" t="n">
-        <v>319.6</v>
+        <v>337.3</v>
       </c>
       <c r="H63" t="n">
-        <v>98.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>53.67</v>
+        <v>75.36</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.67</v>
+        <v>-14.41</v>
       </c>
       <c r="L63" t="n">
-        <v>54.92</v>
+        <v>76.72</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>1.82</v>
       </c>
       <c r="F64" t="n">
-        <v>6.47</v>
+        <v>7.24</v>
       </c>
       <c r="G64" t="n">
-        <v>338.4</v>
+        <v>334.1</v>
       </c>
       <c r="H64" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>28.08</v>
+        <v>34.06</v>
       </c>
       <c r="K64" t="n">
-        <v>57.27</v>
+        <v>72</v>
       </c>
       <c r="L64" t="n">
-        <v>63.79</v>
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>1.94</v>
       </c>
       <c r="F65" t="n">
-        <v>6.35</v>
+        <v>7.24</v>
       </c>
       <c r="G65" t="n">
-        <v>332.6</v>
+        <v>331.7</v>
       </c>
       <c r="H65" t="n">
-        <v>97.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-25.61</v>
+        <v>-35.05</v>
       </c>
       <c r="K65" t="n">
-        <v>60.25</v>
+        <v>77.97</v>
       </c>
       <c r="L65" t="n">
-        <v>65.47</v>
+        <v>85.48999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>1.83</v>
       </c>
       <c r="F66" t="n">
-        <v>6.57</v>
+        <v>6.31</v>
       </c>
       <c r="G66" t="n">
-        <v>336.8</v>
+        <v>335.9</v>
       </c>
       <c r="H66" t="n">
-        <v>96.7</v>
+        <v>99.7</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-74.77</v>
+        <v>-91</v>
       </c>
       <c r="K66" t="n">
-        <v>98.91</v>
+        <v>121.93</v>
       </c>
       <c r="L66" t="n">
-        <v>123.99</v>
+        <v>152.14</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>1.89</v>
       </c>
       <c r="F67" t="n">
-        <v>6.85</v>
+        <v>5.79</v>
       </c>
       <c r="G67" t="n">
-        <v>343</v>
+        <v>341.7</v>
       </c>
       <c r="H67" t="n">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-14.42</v>
+        <v>-17.68</v>
       </c>
       <c r="K67" t="n">
-        <v>79.01000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="L67" t="n">
-        <v>80.31999999999999</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>1.94</v>
       </c>
       <c r="F68" t="n">
-        <v>6.4</v>
+        <v>7.24</v>
       </c>
       <c r="G68" t="n">
-        <v>327.1</v>
+        <v>332.6</v>
       </c>
       <c r="H68" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>78.59999999999999</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-77.90000000000001</v>
+        <v>-84.62</v>
       </c>
       <c r="L68" t="n">
-        <v>110.67</v>
+        <v>129.59</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>2.07</v>
       </c>
       <c r="F69" t="n">
-        <v>6.71</v>
+        <v>5.96</v>
       </c>
       <c r="G69" t="n">
-        <v>322</v>
+        <v>338.7</v>
       </c>
       <c r="H69" t="n">
-        <v>94.5</v>
+        <v>92.3</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-64.84</v>
+        <v>-75.14</v>
       </c>
       <c r="K69" t="n">
-        <v>114.35</v>
+        <v>140.8</v>
       </c>
       <c r="L69" t="n">
-        <v>131.45</v>
+        <v>159.6</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>1.82</v>
       </c>
       <c r="F70" t="n">
-        <v>6.64</v>
+        <v>4.22</v>
       </c>
       <c r="G70" t="n">
-        <v>337.3</v>
+        <v>337.4</v>
       </c>
       <c r="H70" t="n">
-        <v>92.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>84.75</v>
+        <v>85.78</v>
       </c>
       <c r="K70" t="n">
-        <v>22.46</v>
+        <v>45.93</v>
       </c>
       <c r="L70" t="n">
-        <v>87.67</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>1.83</v>
       </c>
       <c r="F71" t="n">
-        <v>6.32</v>
+        <v>7.24</v>
       </c>
       <c r="G71" t="n">
-        <v>325.1</v>
+        <v>330.9</v>
       </c>
       <c r="H71" t="n">
-        <v>99.7</v>
+        <v>93.8</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-177.19</v>
+        <v>-229.52</v>
       </c>
       <c r="K71" t="n">
-        <v>37.78</v>
+        <v>76.31</v>
       </c>
       <c r="L71" t="n">
-        <v>181.17</v>
+        <v>241.87</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>1.86</v>
       </c>
       <c r="F72" t="n">
-        <v>6.15</v>
+        <v>3.44</v>
       </c>
       <c r="G72" t="n">
-        <v>318.1</v>
+        <v>327.6</v>
       </c>
       <c r="H72" t="n">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-149.38</v>
+        <v>-141.19</v>
       </c>
       <c r="K72" t="n">
-        <v>114.68</v>
+        <v>122.25</v>
       </c>
       <c r="L72" t="n">
-        <v>188.32</v>
+        <v>186.76</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>1.93</v>
       </c>
       <c r="F73" t="n">
-        <v>5.79</v>
+        <v>6.31</v>
       </c>
       <c r="G73" t="n">
-        <v>331.5</v>
+        <v>320.5</v>
       </c>
       <c r="H73" t="n">
-        <v>93.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-129.93</v>
+        <v>-174.68</v>
       </c>
       <c r="K73" t="n">
-        <v>132.48</v>
+        <v>177.91</v>
       </c>
       <c r="L73" t="n">
-        <v>185.56</v>
+        <v>249.33</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>1.89</v>
       </c>
       <c r="F74" t="n">
-        <v>6.45</v>
+        <v>4.3</v>
       </c>
       <c r="G74" t="n">
-        <v>325.2</v>
+        <v>333.6</v>
       </c>
       <c r="H74" t="n">
-        <v>92.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I74" t="n">
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>54.71</v>
+        <v>58.2</v>
       </c>
       <c r="K74" t="n">
-        <v>1.74</v>
+        <v>2.22</v>
       </c>
       <c r="L74" t="n">
-        <v>54.74</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>2.33</v>
       </c>
       <c r="F75" t="n">
-        <v>5.36</v>
+        <v>7.24</v>
       </c>
       <c r="G75" t="n">
-        <v>334</v>
+        <v>311.9</v>
       </c>
       <c r="H75" t="n">
-        <v>92.8</v>
+        <v>98.3</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>19.87</v>
+        <v>21.62</v>
       </c>
       <c r="K75" t="n">
-        <v>-56.12</v>
+        <v>-62.88</v>
       </c>
       <c r="L75" t="n">
-        <v>59.54</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>2.05</v>
       </c>
       <c r="F76" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="G76" t="n">
-        <v>322.8</v>
+        <v>326.8</v>
       </c>
       <c r="H76" t="n">
-        <v>94.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.02</v>
+        <v>-14.09</v>
       </c>
       <c r="K76" t="n">
-        <v>11.4</v>
+        <v>15.13</v>
       </c>
       <c r="L76" t="n">
-        <v>15.86</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>1.91</v>
       </c>
       <c r="F77" t="n">
-        <v>6.33</v>
+        <v>5.2</v>
       </c>
       <c r="G77" t="n">
-        <v>322.3</v>
+        <v>331.2</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>62.89</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-22.61</v>
+        <v>-25.35</v>
       </c>
       <c r="L77" t="n">
-        <v>66.83</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>2.08</v>
       </c>
       <c r="F78" t="n">
-        <v>7.04</v>
+        <v>6.16</v>
       </c>
       <c r="G78" t="n">
-        <v>335.5</v>
+        <v>345.5</v>
       </c>
       <c r="H78" t="n">
-        <v>94.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>38.85</v>
+        <v>45.5</v>
       </c>
       <c r="K78" t="n">
-        <v>48.61</v>
+        <v>59.41</v>
       </c>
       <c r="L78" t="n">
-        <v>62.23</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>1.68</v>
       </c>
       <c r="F79" t="n">
-        <v>6.2</v>
+        <v>3.81</v>
       </c>
       <c r="G79" t="n">
-        <v>347.9</v>
+        <v>328.6</v>
       </c>
       <c r="H79" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>54.71</v>
+        <v>57.37</v>
       </c>
       <c r="K79" t="n">
-        <v>-44.19</v>
+        <v>-46.27</v>
       </c>
       <c r="L79" t="n">
-        <v>70.33</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>1.89</v>
       </c>
       <c r="F80" t="n">
-        <v>6.52</v>
+        <v>6.7</v>
       </c>
       <c r="G80" t="n">
-        <v>318.1</v>
+        <v>335</v>
       </c>
       <c r="H80" t="n">
-        <v>96.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I80" t="n">
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>98.13</v>
+        <v>116</v>
       </c>
       <c r="K80" t="n">
-        <v>-37.17</v>
+        <v>-38.97</v>
       </c>
       <c r="L80" t="n">
-        <v>104.93</v>
+        <v>122.37</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>2.19</v>
       </c>
       <c r="F81" t="n">
-        <v>5.96</v>
+        <v>5.94</v>
       </c>
       <c r="G81" t="n">
-        <v>333.7</v>
+        <v>323.7</v>
       </c>
       <c r="H81" t="n">
-        <v>95.8</v>
+        <v>98.2</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-52.03</v>
+        <v>-76.72</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.15</v>
+        <v>-34.35</v>
       </c>
       <c r="L81" t="n">
-        <v>66.34</v>
+        <v>84.06</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>1.99</v>
       </c>
       <c r="F82" t="n">
-        <v>6.06</v>
+        <v>5.72</v>
       </c>
       <c r="G82" t="n">
-        <v>331.9</v>
+        <v>325.8</v>
       </c>
       <c r="H82" t="n">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-24.43</v>
+        <v>-46.44</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.27</v>
+        <v>14.01</v>
       </c>
       <c r="L82" t="n">
-        <v>24.44</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>3.19</v>
       </c>
       <c r="F83" t="n">
-        <v>6.19</v>
+        <v>7.24</v>
       </c>
       <c r="G83" t="n">
-        <v>324.8</v>
+        <v>343.6</v>
       </c>
       <c r="H83" t="n">
-        <v>97.2</v>
+        <v>93.2</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>173.15</v>
+        <v>31.01</v>
       </c>
       <c r="K83" t="n">
-        <v>12.77</v>
+        <v>-61.44</v>
       </c>
       <c r="L83" t="n">
-        <v>173.62</v>
+        <v>68.81999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.85</v>
+        <v>1.99</v>
       </c>
       <c r="F84" t="n">
-        <v>5.93</v>
+        <v>6.64</v>
       </c>
       <c r="G84" t="n">
-        <v>329.2</v>
+        <v>328.4</v>
       </c>
       <c r="H84" t="n">
-        <v>91.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-196.93</v>
+        <v>-106.02</v>
       </c>
       <c r="K84" t="n">
-        <v>-78.18000000000001</v>
+        <v>140.65</v>
       </c>
       <c r="L84" t="n">
-        <v>211.88</v>
+        <v>176.13</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="F85" t="n">
-        <v>6.12</v>
+        <v>7.24</v>
       </c>
       <c r="G85" t="n">
-        <v>336</v>
+        <v>322.3</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>136.63</v>
+        <v>-5.96</v>
       </c>
       <c r="K85" t="n">
-        <v>17.42</v>
+        <v>217.81</v>
       </c>
       <c r="L85" t="n">
-        <v>137.74</v>
+        <v>217.89</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="F86" t="n">
-        <v>6.83</v>
+        <v>6.44</v>
       </c>
       <c r="G86" t="n">
-        <v>329.3</v>
+        <v>344.2</v>
       </c>
       <c r="H86" t="n">
         <v>100</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-178.16</v>
+        <v>-123.48</v>
       </c>
       <c r="K86" t="n">
-        <v>-62.22</v>
+        <v>-164.81</v>
       </c>
       <c r="L86" t="n">
-        <v>188.71</v>
+        <v>205.94</v>
       </c>
     </row>
     <row r="87">
@@ -3691,28 +3691,28 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="F87" t="n">
-        <v>6.52</v>
+        <v>5.77</v>
       </c>
       <c r="G87" t="n">
-        <v>331</v>
+        <v>315.7</v>
       </c>
       <c r="H87" t="n">
-        <v>95.8</v>
+        <v>98.8</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>181.82</v>
+        <v>-113.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-39.76</v>
+        <v>153.97</v>
       </c>
       <c r="L87" t="n">
-        <v>186.11</v>
+        <v>191.53</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="F88" t="n">
-        <v>5.45</v>
+        <v>7.24</v>
       </c>
       <c r="G88" t="n">
-        <v>329.8</v>
+        <v>331.1</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>26.06</v>
+        <v>-219.13</v>
       </c>
       <c r="K88" t="n">
-        <v>-165.78</v>
+        <v>78.98</v>
       </c>
       <c r="L88" t="n">
-        <v>167.81</v>
+        <v>232.93</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.53</v>
+        <v>-6.25</v>
       </c>
       <c r="K14" t="n">
-        <v>52.05</v>
+        <v>49.88</v>
       </c>
       <c r="L14" t="n">
-        <v>52.46</v>
+        <v>50.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>50.14</v>
+        <v>49.12</v>
       </c>
       <c r="K15" t="n">
-        <v>28.86</v>
+        <v>28.27</v>
       </c>
       <c r="L15" t="n">
-        <v>57.86</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="16">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>60.42</v>
+        <v>63.84</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.06</v>
+        <v>-3.23</v>
       </c>
       <c r="L17" t="n">
-        <v>60.5</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-41.04</v>
+        <v>-40.21</v>
       </c>
       <c r="K18" t="n">
-        <v>-26.43</v>
+        <v>-25.89</v>
       </c>
       <c r="L18" t="n">
-        <v>48.81</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="19">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-77.11</v>
+        <v>-82.81999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>97.73</v>
+        <v>104.97</v>
       </c>
       <c r="L20" t="n">
-        <v>124.49</v>
+        <v>133.71</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-52.6</v>
+        <v>-56.49</v>
       </c>
       <c r="K21" t="n">
-        <v>-99.52</v>
+        <v>-106.9</v>
       </c>
       <c r="L21" t="n">
-        <v>112.57</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-33.57</v>
+        <v>-34.22</v>
       </c>
       <c r="K22" t="n">
-        <v>120.5</v>
+        <v>122.86</v>
       </c>
       <c r="L22" t="n">
-        <v>125.09</v>
+        <v>127.54</v>
       </c>
     </row>
     <row r="23">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-100.92</v>
+        <v>-106.63</v>
       </c>
       <c r="K24" t="n">
-        <v>35.01</v>
+        <v>36.99</v>
       </c>
       <c r="L24" t="n">
-        <v>106.82</v>
+        <v>112.87</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-28.15</v>
+        <v>-28.71</v>
       </c>
       <c r="K25" t="n">
-        <v>-120.85</v>
+        <v>-123.22</v>
       </c>
       <c r="L25" t="n">
-        <v>124.08</v>
+        <v>126.52</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-115.46</v>
+        <v>-124.01</v>
       </c>
       <c r="K26" t="n">
-        <v>-208.22</v>
+        <v>-223.65</v>
       </c>
       <c r="L26" t="n">
-        <v>238.09</v>
+        <v>255.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-94.11</v>
+        <v>-92.19</v>
       </c>
       <c r="K27" t="n">
-        <v>234.51</v>
+        <v>229.72</v>
       </c>
       <c r="L27" t="n">
-        <v>252.68</v>
+        <v>247.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>144.19</v>
+        <v>141.25</v>
       </c>
       <c r="K28" t="n">
-        <v>-21.71</v>
+        <v>-21.27</v>
       </c>
       <c r="L28" t="n">
-        <v>145.82</v>
+        <v>142.84</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-42.23</v>
+        <v>-40.47</v>
       </c>
       <c r="K29" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="L29" t="n">
-        <v>42.3</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>64.09999999999999</v>
+        <v>65.36</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="L30" t="n">
-        <v>64.22</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.06</v>
+        <v>-5.26</v>
       </c>
       <c r="K31" t="n">
-        <v>50.13</v>
+        <v>52.05</v>
       </c>
       <c r="L31" t="n">
-        <v>50.38</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.32</v>
+        <v>-3.56</v>
       </c>
       <c r="K32" t="n">
-        <v>21.23</v>
+        <v>22.8</v>
       </c>
       <c r="L32" t="n">
-        <v>21.49</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-75.31</v>
+        <v>-78.2</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="L33" t="n">
-        <v>75.31</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-67.39</v>
+        <v>-69.98</v>
       </c>
       <c r="K34" t="n">
-        <v>10.69</v>
+        <v>11.1</v>
       </c>
       <c r="L34" t="n">
-        <v>68.23</v>
+        <v>70.86</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-65.81</v>
+        <v>-67.09999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>61.8</v>
+        <v>63.01</v>
       </c>
       <c r="L35" t="n">
-        <v>90.28</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>37.25</v>
+        <v>35.7</v>
       </c>
       <c r="K36" t="n">
-        <v>128.45</v>
+        <v>123.1</v>
       </c>
       <c r="L36" t="n">
-        <v>133.74</v>
+        <v>128.17</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-102.56</v>
+        <v>-98.29000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.130000000000001</v>
+        <v>-8.75</v>
       </c>
       <c r="L37" t="n">
-        <v>102.97</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-104.37</v>
+        <v>-106.41</v>
       </c>
       <c r="K39" t="n">
-        <v>25.32</v>
+        <v>25.82</v>
       </c>
       <c r="L39" t="n">
-        <v>107.39</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="40">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-74.38</v>
+        <v>-72.86</v>
       </c>
       <c r="K41" t="n">
-        <v>-22.5</v>
+        <v>-22.04</v>
       </c>
       <c r="L41" t="n">
-        <v>77.70999999999999</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>49.99</v>
+        <v>48.97</v>
       </c>
       <c r="K42" t="n">
-        <v>230.24</v>
+        <v>225.54</v>
       </c>
       <c r="L42" t="n">
-        <v>235.61</v>
+        <v>230.8</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-196.36</v>
+        <v>-200.22</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.9</v>
+        <v>-6.02</v>
       </c>
       <c r="L43" t="n">
-        <v>196.45</v>
+        <v>200.31</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>59.47</v>
+        <v>58.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-19.77</v>
+        <v>-19.37</v>
       </c>
       <c r="L44" t="n">
-        <v>62.67</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-45.01</v>
+        <v>-47.55</v>
       </c>
       <c r="K45" t="n">
-        <v>-18.69</v>
+        <v>-19.75</v>
       </c>
       <c r="L45" t="n">
-        <v>48.73</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>5.7</v>
+        <v>5.81</v>
       </c>
       <c r="K46" t="n">
-        <v>49.54</v>
+        <v>50.51</v>
       </c>
       <c r="L46" t="n">
-        <v>49.86</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-70.52</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.2</v>
+        <v>-13.46</v>
       </c>
       <c r="L47" t="n">
-        <v>71.75</v>
+        <v>73.15000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-33.27</v>
+        <v>-35.16</v>
       </c>
       <c r="K48" t="n">
-        <v>73.55</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>80.73</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-83.94</v>
+        <v>-87.17</v>
       </c>
       <c r="K49" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="L49" t="n">
-        <v>84.06</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>115.01</v>
+        <v>110.22</v>
       </c>
       <c r="K50" t="n">
-        <v>14.03</v>
+        <v>13.45</v>
       </c>
       <c r="L50" t="n">
-        <v>115.87</v>
+        <v>111.04</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>6.6</v>
+        <v>6.73</v>
       </c>
       <c r="K51" t="n">
-        <v>92.91</v>
+        <v>94.73</v>
       </c>
       <c r="L51" t="n">
-        <v>93.14</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>18.98</v>
+        <v>18.59</v>
       </c>
       <c r="K52" t="n">
-        <v>86.13</v>
+        <v>84.37</v>
       </c>
       <c r="L52" t="n">
-        <v>88.2</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-71.41</v>
+        <v>-76.69</v>
       </c>
       <c r="K53" t="n">
-        <v>163.91</v>
+        <v>176.05</v>
       </c>
       <c r="L53" t="n">
-        <v>178.79</v>
+        <v>192.03</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>38.47</v>
+        <v>40.65</v>
       </c>
       <c r="K54" t="n">
-        <v>125.81</v>
+        <v>132.93</v>
       </c>
       <c r="L54" t="n">
-        <v>131.56</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>84.12</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-164.39</v>
+        <v>-161.03</v>
       </c>
       <c r="L55" t="n">
-        <v>184.66</v>
+        <v>180.89</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-36.71</v>
+        <v>-35.96</v>
       </c>
       <c r="K56" t="n">
-        <v>180.22</v>
+        <v>176.54</v>
       </c>
       <c r="L56" t="n">
-        <v>183.92</v>
+        <v>180.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>149.22</v>
+        <v>143</v>
       </c>
       <c r="K57" t="n">
-        <v>-58.68</v>
+        <v>-56.24</v>
       </c>
       <c r="L57" t="n">
-        <v>160.34</v>
+        <v>153.66</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>146.66</v>
+        <v>152.3</v>
       </c>
       <c r="K58" t="n">
-        <v>-145.01</v>
+        <v>-150.59</v>
       </c>
       <c r="L58" t="n">
-        <v>206.25</v>
+        <v>214.18</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>26.14</v>
+        <v>25.61</v>
       </c>
       <c r="K59" t="n">
-        <v>-45.6</v>
+        <v>-44.67</v>
       </c>
       <c r="L59" t="n">
-        <v>52.56</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-59.44</v>
+        <v>-63.84</v>
       </c>
       <c r="K60" t="n">
-        <v>-17.29</v>
+        <v>-18.57</v>
       </c>
       <c r="L60" t="n">
-        <v>61.9</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-22.99</v>
+        <v>-24.29</v>
       </c>
       <c r="K61" t="n">
-        <v>-44.82</v>
+        <v>-47.35</v>
       </c>
       <c r="L61" t="n">
-        <v>50.37</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-15.5</v>
+        <v>-15.81</v>
       </c>
       <c r="K62" t="n">
-        <v>105.53</v>
+        <v>107.6</v>
       </c>
       <c r="L62" t="n">
-        <v>106.66</v>
+        <v>108.75</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>75.36</v>
+        <v>80.94</v>
       </c>
       <c r="K63" t="n">
-        <v>-14.41</v>
+        <v>-15.48</v>
       </c>
       <c r="L63" t="n">
-        <v>76.72</v>
+        <v>82.41</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>34.06</v>
+        <v>32.64</v>
       </c>
       <c r="K64" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L64" t="n">
-        <v>79.65000000000001</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-35.05</v>
+        <v>-35.74</v>
       </c>
       <c r="K65" t="n">
-        <v>77.97</v>
+        <v>79.5</v>
       </c>
       <c r="L65" t="n">
-        <v>85.48999999999999</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-91</v>
+        <v>-94.5</v>
       </c>
       <c r="K66" t="n">
-        <v>121.93</v>
+        <v>126.62</v>
       </c>
       <c r="L66" t="n">
-        <v>152.14</v>
+        <v>157.99</v>
       </c>
     </row>
     <row r="67">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>98.15000000000001</v>
+        <v>103.7</v>
       </c>
       <c r="K68" t="n">
-        <v>-84.62</v>
+        <v>-89.41</v>
       </c>
       <c r="L68" t="n">
-        <v>129.59</v>
+        <v>136.92</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-75.14</v>
+        <v>-76.62</v>
       </c>
       <c r="K69" t="n">
-        <v>140.8</v>
+        <v>143.56</v>
       </c>
       <c r="L69" t="n">
-        <v>159.6</v>
+        <v>162.73</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>85.78</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>45.93</v>
+        <v>44.01</v>
       </c>
       <c r="L70" t="n">
-        <v>97.3</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-229.52</v>
+        <v>-242.51</v>
       </c>
       <c r="K71" t="n">
-        <v>76.31</v>
+        <v>80.63</v>
       </c>
       <c r="L71" t="n">
-        <v>241.87</v>
+        <v>255.57</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-141.19</v>
+        <v>-138.3</v>
       </c>
       <c r="K72" t="n">
-        <v>122.25</v>
+        <v>119.76</v>
       </c>
       <c r="L72" t="n">
-        <v>186.76</v>
+        <v>182.95</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-174.68</v>
+        <v>-184.57</v>
       </c>
       <c r="K73" t="n">
-        <v>177.91</v>
+        <v>187.98</v>
       </c>
       <c r="L73" t="n">
-        <v>249.33</v>
+        <v>263.44</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>58.2</v>
+        <v>59.34</v>
       </c>
       <c r="K74" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="L74" t="n">
-        <v>58.24</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>21.62</v>
+        <v>22.04</v>
       </c>
       <c r="K75" t="n">
-        <v>-62.88</v>
+        <v>-64.11</v>
       </c>
       <c r="L75" t="n">
-        <v>66.48999999999999</v>
+        <v>67.79000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.09</v>
+        <v>-14.89</v>
       </c>
       <c r="K76" t="n">
-        <v>15.13</v>
+        <v>15.98</v>
       </c>
       <c r="L76" t="n">
-        <v>20.67</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>74.26000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-25.35</v>
+        <v>-27.23</v>
       </c>
       <c r="L77" t="n">
-        <v>78.45999999999999</v>
+        <v>84.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>45.5</v>
+        <v>48.08</v>
       </c>
       <c r="K78" t="n">
-        <v>59.41</v>
+        <v>62.78</v>
       </c>
       <c r="L78" t="n">
-        <v>74.84</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>116</v>
+        <v>113.63</v>
       </c>
       <c r="K80" t="n">
-        <v>-38.97</v>
+        <v>-38.17</v>
       </c>
       <c r="L80" t="n">
-        <v>122.37</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-76.72</v>
+        <v>-79.67</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.35</v>
+        <v>-35.68</v>
       </c>
       <c r="L81" t="n">
-        <v>84.06</v>
+        <v>87.29000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-46.44</v>
+        <v>-48.23</v>
       </c>
       <c r="K82" t="n">
-        <v>14.01</v>
+        <v>14.55</v>
       </c>
       <c r="L82" t="n">
-        <v>48.51</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>31.01</v>
+        <v>33.3</v>
       </c>
       <c r="K83" t="n">
-        <v>-61.44</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>68.81999999999999</v>
+        <v>73.92</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-106.02</v>
+        <v>-101.6</v>
       </c>
       <c r="K84" t="n">
-        <v>140.65</v>
+        <v>134.79</v>
       </c>
       <c r="L84" t="n">
-        <v>176.13</v>
+        <v>168.79</v>
       </c>
     </row>
     <row r="85">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-123.48</v>
+        <v>-125.91</v>
       </c>
       <c r="K86" t="n">
-        <v>-164.81</v>
+        <v>-168.04</v>
       </c>
       <c r="L86" t="n">
-        <v>205.94</v>
+        <v>209.98</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-113.91</v>
+        <v>-111.59</v>
       </c>
       <c r="K87" t="n">
-        <v>153.97</v>
+        <v>150.83</v>
       </c>
       <c r="L87" t="n">
-        <v>191.53</v>
+        <v>187.62</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-219.13</v>
+        <v>-227.56</v>
       </c>
       <c r="K88" t="n">
-        <v>78.98</v>
+        <v>82.02</v>
       </c>
       <c r="L88" t="n">
-        <v>232.93</v>
+        <v>241.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.89</v>
+        <v>2.74</v>
       </c>
       <c r="F14" t="n">
-        <v>3.07</v>
+        <v>4.7</v>
       </c>
       <c r="G14" t="n">
-        <v>312.1</v>
+        <v>330.6</v>
       </c>
       <c r="H14" t="n">
-        <v>98.40000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.25</v>
+        <v>-37.15</v>
       </c>
       <c r="K14" t="n">
-        <v>49.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>50.27</v>
+        <v>38.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:04:30</t>
+          <t>05:04:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="F15" t="n">
-        <v>3.92</v>
+        <v>6.07</v>
       </c>
       <c r="G15" t="n">
-        <v>335.4</v>
+        <v>335</v>
       </c>
       <c r="H15" t="n">
-        <v>91.09999999999999</v>
+        <v>57.8</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>49.12</v>
+        <v>32.82</v>
       </c>
       <c r="K15" t="n">
-        <v>28.27</v>
+        <v>9.17</v>
       </c>
       <c r="L15" t="n">
-        <v>56.68</v>
+        <v>34.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:06:26</t>
+          <t>05:06:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="F16" t="n">
-        <v>2.08</v>
+        <v>7.24</v>
       </c>
       <c r="G16" t="n">
-        <v>324.4</v>
+        <v>337.4</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>67.7</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>29.32</v>
+        <v>34.58</v>
       </c>
       <c r="K16" t="n">
-        <v>19.76</v>
+        <v>-3.28</v>
       </c>
       <c r="L16" t="n">
-        <v>35.35</v>
+        <v>34.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:09:58</t>
+          <t>05:11:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="F17" t="n">
-        <v>5.01</v>
+        <v>7.24</v>
       </c>
       <c r="G17" t="n">
-        <v>329.4</v>
+        <v>328.2</v>
       </c>
       <c r="H17" t="n">
-        <v>99.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>63.84</v>
+        <v>-42.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.23</v>
+        <v>16.58</v>
       </c>
       <c r="L17" t="n">
-        <v>63.92</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:11:13</t>
+          <t>05:12:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="F18" t="n">
-        <v>3.11</v>
+        <v>7.19</v>
       </c>
       <c r="G18" t="n">
-        <v>343</v>
+        <v>332.3</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>52.7</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-40.21</v>
+        <v>-20.37</v>
       </c>
       <c r="K18" t="n">
-        <v>-25.89</v>
+        <v>-39.87</v>
       </c>
       <c r="L18" t="n">
-        <v>47.82</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:13:12</t>
+          <t>05:13:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="F19" t="n">
-        <v>4.88</v>
+        <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>344.7</v>
+        <v>334</v>
       </c>
       <c r="H19" t="n">
-        <v>96.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>20.94</v>
+        <v>7.31</v>
       </c>
       <c r="K19" t="n">
-        <v>87.79000000000001</v>
+        <v>52.46</v>
       </c>
       <c r="L19" t="n">
-        <v>90.26000000000001</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:18:50</t>
+          <t>05:18:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>4.47</v>
       </c>
       <c r="G20" t="n">
-        <v>324.4</v>
+        <v>335.4</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="I20" t="n">
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-82.81999999999999</v>
+        <v>-43.44</v>
       </c>
       <c r="K20" t="n">
-        <v>104.97</v>
+        <v>-6.15</v>
       </c>
       <c r="L20" t="n">
-        <v>133.71</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:20:18</t>
+          <t>05:20:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="F21" t="n">
-        <v>3.76</v>
+        <v>4.86</v>
       </c>
       <c r="G21" t="n">
-        <v>321.8</v>
+        <v>331.8</v>
       </c>
       <c r="H21" t="n">
-        <v>95.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-56.49</v>
+        <v>39.16</v>
       </c>
       <c r="K21" t="n">
-        <v>-106.9</v>
+        <v>-18.43</v>
       </c>
       <c r="L21" t="n">
-        <v>120.9</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:21:47</t>
+          <t>05:22:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="F22" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="G22" t="n">
-        <v>324.8</v>
+        <v>319.9</v>
       </c>
       <c r="H22" t="n">
-        <v>98</v>
+        <v>97.7</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-34.22</v>
+        <v>93.08</v>
       </c>
       <c r="K22" t="n">
-        <v>122.86</v>
+        <v>-4.96</v>
       </c>
       <c r="L22" t="n">
-        <v>127.54</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:25:40</t>
+          <t>05:28:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>5.22</v>
       </c>
       <c r="G23" t="n">
-        <v>339</v>
+        <v>330.7</v>
       </c>
       <c r="H23" t="n">
-        <v>94.7</v>
+        <v>62.8</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>59.53</v>
+        <v>69.3</v>
       </c>
       <c r="K23" t="n">
-        <v>89.69</v>
+        <v>-80.23</v>
       </c>
       <c r="L23" t="n">
-        <v>107.65</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:26:30</t>
+          <t>05:30:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="F24" t="n">
-        <v>3.57</v>
+        <v>4.68</v>
       </c>
       <c r="G24" t="n">
-        <v>327.5</v>
+        <v>332</v>
       </c>
       <c r="H24" t="n">
-        <v>99.7</v>
+        <v>89.7</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-106.63</v>
+        <v>-98.81999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>36.99</v>
+        <v>72.56</v>
       </c>
       <c r="L24" t="n">
-        <v>112.87</v>
+        <v>122.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:28:44</t>
+          <t>05:31:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="F25" t="n">
-        <v>4.82</v>
+        <v>4.35</v>
       </c>
       <c r="G25" t="n">
-        <v>331.7</v>
+        <v>325.9</v>
       </c>
       <c r="H25" t="n">
-        <v>96.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-28.71</v>
+        <v>-28.11</v>
       </c>
       <c r="K25" t="n">
-        <v>-123.22</v>
+        <v>102.23</v>
       </c>
       <c r="L25" t="n">
-        <v>126.52</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:34:08</t>
+          <t>05:35:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="F26" t="n">
         <v>7.24</v>
       </c>
       <c r="G26" t="n">
-        <v>314.8</v>
+        <v>320.7</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>62.3</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-124.01</v>
+        <v>-89.3</v>
       </c>
       <c r="K26" t="n">
-        <v>-223.65</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>255.73</v>
+        <v>121.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:35:55</t>
+          <t>05:36:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="F27" t="n">
-        <v>7.19</v>
+        <v>5.65</v>
       </c>
       <c r="G27" t="n">
-        <v>330.7</v>
+        <v>309.8</v>
       </c>
       <c r="H27" t="n">
-        <v>98.2</v>
+        <v>73.7</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-92.19</v>
+        <v>-70.41</v>
       </c>
       <c r="K27" t="n">
-        <v>229.72</v>
+        <v>23.11</v>
       </c>
       <c r="L27" t="n">
-        <v>247.53</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:38:20</t>
+          <t>05:39:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="F28" t="n">
-        <v>3.83</v>
+        <v>3.38</v>
       </c>
       <c r="G28" t="n">
-        <v>330.1</v>
+        <v>339.6</v>
       </c>
       <c r="H28" t="n">
-        <v>99.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="I28" t="n">
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>141.25</v>
+        <v>-357.82</v>
       </c>
       <c r="K28" t="n">
-        <v>-21.27</v>
+        <v>-6.72</v>
       </c>
       <c r="L28" t="n">
-        <v>142.84</v>
+        <v>357.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:48:55</t>
+          <t>05:51:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="F29" t="n">
-        <v>6.46</v>
+        <v>5.04</v>
       </c>
       <c r="G29" t="n">
-        <v>330.5</v>
+        <v>330.4</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-40.47</v>
+        <v>-21.84</v>
       </c>
       <c r="K29" t="n">
-        <v>2.37</v>
+        <v>10.32</v>
       </c>
       <c r="L29" t="n">
-        <v>40.54</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:50:05</t>
+          <t>05:53:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="F30" t="n">
-        <v>7.24</v>
+        <v>4.71</v>
       </c>
       <c r="G30" t="n">
-        <v>330.5</v>
+        <v>337.1</v>
       </c>
       <c r="H30" t="n">
-        <v>98.5</v>
+        <v>52.7</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>65.36</v>
+        <v>-9.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.98</v>
+        <v>-27.57</v>
       </c>
       <c r="L30" t="n">
-        <v>65.48</v>
+        <v>29.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:50:57</t>
+          <t>05:55:10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="F31" t="n">
-        <v>4.26</v>
+        <v>7.24</v>
       </c>
       <c r="G31" t="n">
-        <v>319.1</v>
+        <v>328.9</v>
       </c>
       <c r="H31" t="n">
-        <v>99.2</v>
+        <v>52.1</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.26</v>
+        <v>27.69</v>
       </c>
       <c r="K31" t="n">
-        <v>52.05</v>
+        <v>-1.71</v>
       </c>
       <c r="L31" t="n">
-        <v>52.32</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:55:23</t>
+          <t>06:00:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="F32" t="n">
-        <v>3.07</v>
+        <v>7.24</v>
       </c>
       <c r="G32" t="n">
-        <v>323.6</v>
+        <v>342</v>
       </c>
       <c r="H32" t="n">
-        <v>99.59999999999999</v>
+        <v>49.9</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.56</v>
+        <v>-35.91</v>
       </c>
       <c r="K32" t="n">
-        <v>22.8</v>
+        <v>-15.47</v>
       </c>
       <c r="L32" t="n">
-        <v>23.08</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:57:04</t>
+          <t>06:01:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="F33" t="n">
-        <v>6.17</v>
+        <v>7.24</v>
       </c>
       <c r="G33" t="n">
-        <v>331.9</v>
+        <v>321.1</v>
       </c>
       <c r="H33" t="n">
-        <v>95.7</v>
+        <v>68</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-78.2</v>
+        <v>-30.38</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.39</v>
+        <v>53.58</v>
       </c>
       <c r="L33" t="n">
-        <v>78.2</v>
+        <v>61.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:57:43</t>
+          <t>06:02:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="F34" t="n">
-        <v>5.58</v>
+        <v>7.24</v>
       </c>
       <c r="G34" t="n">
-        <v>338.1</v>
+        <v>335</v>
       </c>
       <c r="H34" t="n">
-        <v>91.09999999999999</v>
+        <v>50.5</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-69.98</v>
+        <v>11.22</v>
       </c>
       <c r="K34" t="n">
-        <v>11.1</v>
+        <v>-34.3</v>
       </c>
       <c r="L34" t="n">
-        <v>70.86</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:03:45</t>
+          <t>06:07:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="F35" t="n">
-        <v>2.02</v>
+        <v>6.64</v>
       </c>
       <c r="G35" t="n">
-        <v>324.7</v>
+        <v>330.6</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>25.2</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>-67.09999999999999</v>
+        <v>-74.31</v>
       </c>
       <c r="K35" t="n">
-        <v>63.01</v>
+        <v>58.09</v>
       </c>
       <c r="L35" t="n">
-        <v>92.05</v>
+        <v>94.31999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:04:54</t>
+          <t>06:08:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="F36" t="n">
-        <v>5.18</v>
+        <v>7.24</v>
       </c>
       <c r="G36" t="n">
-        <v>335.6</v>
+        <v>339.3</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>62.6</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>35.7</v>
+        <v>-21.92</v>
       </c>
       <c r="K36" t="n">
-        <v>123.1</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>128.17</v>
+        <v>78.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:07:01</t>
+          <t>06:11:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="F37" t="n">
-        <v>4.24</v>
+        <v>7.24</v>
       </c>
       <c r="G37" t="n">
-        <v>320.2</v>
+        <v>317.2</v>
       </c>
       <c r="H37" t="n">
-        <v>95.3</v>
+        <v>31.7</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-98.29000000000001</v>
+        <v>-39.46</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.75</v>
+        <v>49.82</v>
       </c>
       <c r="L37" t="n">
-        <v>98.68000000000001</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:10:26</t>
+          <t>06:15:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="F38" t="n">
-        <v>4.51</v>
+        <v>2.18</v>
       </c>
       <c r="G38" t="n">
-        <v>328.8</v>
+        <v>334</v>
       </c>
       <c r="H38" t="n">
-        <v>91.2</v>
+        <v>55.2</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>10.37</v>
+        <v>-76.09999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-129.81</v>
+        <v>-56.69</v>
       </c>
       <c r="L38" t="n">
-        <v>130.23</v>
+        <v>94.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:12:49</t>
+          <t>06:16:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="F39" t="n">
-        <v>6.75</v>
+        <v>7.24</v>
       </c>
       <c r="G39" t="n">
-        <v>324.8</v>
+        <v>334.3</v>
       </c>
       <c r="H39" t="n">
-        <v>94.8</v>
+        <v>84.8</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-106.41</v>
+        <v>115.97</v>
       </c>
       <c r="K39" t="n">
-        <v>25.82</v>
+        <v>-87.26000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>109.5</v>
+        <v>145.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:14:10</t>
+          <t>06:18:03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.62</v>
+        <v>2.13</v>
       </c>
       <c r="F40" t="n">
-        <v>4.16</v>
+        <v>6.45</v>
       </c>
       <c r="G40" t="n">
-        <v>331.7</v>
+        <v>334.5</v>
       </c>
       <c r="H40" t="n">
-        <v>98</v>
+        <v>68.7</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>147.16</v>
+        <v>93.61</v>
       </c>
       <c r="K40" t="n">
-        <v>71.25</v>
+        <v>94.73</v>
       </c>
       <c r="L40" t="n">
-        <v>163.51</v>
+        <v>133.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:19:26</t>
+          <t>06:21:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="F41" t="n">
-        <v>7.24</v>
+        <v>5.5</v>
       </c>
       <c r="G41" t="n">
-        <v>336.3</v>
+        <v>334</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-72.86</v>
+        <v>46.1</v>
       </c>
       <c r="K41" t="n">
-        <v>-22.04</v>
+        <v>170.27</v>
       </c>
       <c r="L41" t="n">
-        <v>76.12</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:20:41</t>
+          <t>06:23:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="F42" t="n">
-        <v>5.91</v>
+        <v>1.74</v>
       </c>
       <c r="G42" t="n">
-        <v>344.4</v>
+        <v>321.3</v>
       </c>
       <c r="H42" t="n">
-        <v>87.2</v>
+        <v>59.3</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>48.97</v>
+        <v>1.04</v>
       </c>
       <c r="K42" t="n">
-        <v>225.54</v>
+        <v>113.09</v>
       </c>
       <c r="L42" t="n">
-        <v>230.8</v>
+        <v>113.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:22:32</t>
+          <t>06:25:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="F43" t="n">
-        <v>3.6</v>
+        <v>4.19</v>
       </c>
       <c r="G43" t="n">
-        <v>332.3</v>
+        <v>341</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>77.7</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-200.22</v>
+        <v>-25.74</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.02</v>
+        <v>99.77</v>
       </c>
       <c r="L43" t="n">
-        <v>200.31</v>
+        <v>103.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:33:08</t>
+          <t>06:33:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="F44" t="n">
-        <v>7.24</v>
+        <v>5.26</v>
       </c>
       <c r="G44" t="n">
-        <v>346.4</v>
+        <v>319.3</v>
       </c>
       <c r="H44" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>58.25</v>
+        <v>-31.42</v>
       </c>
       <c r="K44" t="n">
-        <v>-19.37</v>
+        <v>0.01</v>
       </c>
       <c r="L44" t="n">
-        <v>61.39</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:34:51</t>
+          <t>06:35:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,28 +1927,28 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="F45" t="n">
-        <v>3.53</v>
+        <v>7.24</v>
       </c>
       <c r="G45" t="n">
-        <v>336.5</v>
+        <v>337.7</v>
       </c>
       <c r="H45" t="n">
-        <v>92.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.55</v>
+        <v>-37.55</v>
       </c>
       <c r="K45" t="n">
-        <v>-19.75</v>
+        <v>10.26</v>
       </c>
       <c r="L45" t="n">
-        <v>51.49</v>
+        <v>38.93</v>
       </c>
     </row>
     <row r="46">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.72</v>
+        <v>1.8</v>
       </c>
       <c r="F46" t="n">
-        <v>7.24</v>
+        <v>6.49</v>
       </c>
       <c r="G46" t="n">
-        <v>328.1</v>
+        <v>326.9</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>34.7</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>5.81</v>
+        <v>-1.02</v>
       </c>
       <c r="K46" t="n">
-        <v>50.51</v>
+        <v>32.19</v>
       </c>
       <c r="L46" t="n">
-        <v>50.84</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:41:27</t>
+          <t>06:40:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.54</v>
+        <v>2.19</v>
       </c>
       <c r="F47" t="n">
-        <v>3.66</v>
+        <v>6.16</v>
       </c>
       <c r="G47" t="n">
-        <v>336.3</v>
+        <v>329.2</v>
       </c>
       <c r="H47" t="n">
-        <v>93.59999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-71.90000000000001</v>
+        <v>-34.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.46</v>
+        <v>-53.52</v>
       </c>
       <c r="L47" t="n">
-        <v>73.15000000000001</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:43:36</t>
+          <t>06:42:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F48" t="n">
-        <v>4.76</v>
+        <v>5.24</v>
       </c>
       <c r="G48" t="n">
-        <v>327.5</v>
+        <v>318.4</v>
       </c>
       <c r="H48" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-35.16</v>
+        <v>-24.68</v>
       </c>
       <c r="K48" t="n">
-        <v>77.70999999999999</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>85.3</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:45:18</t>
+          <t>06:43:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="F49" t="n">
-        <v>6.65</v>
+        <v>7.24</v>
       </c>
       <c r="G49" t="n">
-        <v>325.8</v>
+        <v>334.7</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>36.1</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-87.17</v>
+        <v>-48.38</v>
       </c>
       <c r="K49" t="n">
-        <v>4.67</v>
+        <v>21.9</v>
       </c>
       <c r="L49" t="n">
-        <v>87.3</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:50:55</t>
+          <t>06:48:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="F50" t="n">
         <v>7.24</v>
       </c>
       <c r="G50" t="n">
-        <v>334.7</v>
+        <v>321.3</v>
       </c>
       <c r="H50" t="n">
-        <v>95.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>110.22</v>
+        <v>-24.01</v>
       </c>
       <c r="K50" t="n">
-        <v>13.45</v>
+        <v>70.42</v>
       </c>
       <c r="L50" t="n">
-        <v>111.04</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:52:28</t>
+          <t>06:49:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="F51" t="n">
-        <v>3.47</v>
+        <v>4.54</v>
       </c>
       <c r="G51" t="n">
-        <v>339.4</v>
+        <v>317.5</v>
       </c>
       <c r="H51" t="n">
-        <v>93.3</v>
+        <v>82.7</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>6.73</v>
+        <v>9.49</v>
       </c>
       <c r="K51" t="n">
-        <v>94.73</v>
+        <v>57.53</v>
       </c>
       <c r="L51" t="n">
-        <v>94.97</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:54:14</t>
+          <t>06:51:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.42</v>
+        <v>2.17</v>
       </c>
       <c r="F52" t="n">
-        <v>3.89</v>
+        <v>7.24</v>
       </c>
       <c r="G52" t="n">
-        <v>335.2</v>
+        <v>327.7</v>
       </c>
       <c r="H52" t="n">
-        <v>97.2</v>
+        <v>17.1</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>18.59</v>
+        <v>-67.88</v>
       </c>
       <c r="K52" t="n">
-        <v>84.37</v>
+        <v>-75.79000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>86.40000000000001</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:59:19</t>
+          <t>06:56:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2266,31 +2266,31 @@
         <v>1.96</v>
       </c>
       <c r="F53" t="n">
-        <v>7.24</v>
+        <v>2.39</v>
       </c>
       <c r="G53" t="n">
-        <v>316.2</v>
+        <v>320.3</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-76.69</v>
+        <v>74.66</v>
       </c>
       <c r="K53" t="n">
-        <v>176.05</v>
+        <v>-91.83</v>
       </c>
       <c r="L53" t="n">
-        <v>192.03</v>
+        <v>118.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:01:03</t>
+          <t>06:57:16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.87</v>
+        <v>2.54</v>
       </c>
       <c r="F54" t="n">
-        <v>4.89</v>
+        <v>6.23</v>
       </c>
       <c r="G54" t="n">
-        <v>328.6</v>
+        <v>320</v>
       </c>
       <c r="H54" t="n">
-        <v>99.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>40.65</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>132.93</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>139</v>
+        <v>111.12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:02:49</t>
+          <t>06:59:40</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="F55" t="n">
-        <v>5.64</v>
+        <v>5.83</v>
       </c>
       <c r="G55" t="n">
-        <v>327.7</v>
+        <v>332.3</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>18.6</v>
       </c>
       <c r="I55" t="n">
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>82.40000000000001</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-161.03</v>
+        <v>63.49</v>
       </c>
       <c r="L55" t="n">
-        <v>180.89</v>
+        <v>98.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:07:21</t>
+          <t>07:05:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="F56" t="n">
-        <v>4.87</v>
+        <v>5.9</v>
       </c>
       <c r="G56" t="n">
-        <v>340.4</v>
+        <v>330.7</v>
       </c>
       <c r="H56" t="n">
-        <v>97.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>-35.96</v>
+        <v>34.54</v>
       </c>
       <c r="K56" t="n">
-        <v>176.54</v>
+        <v>-119.18</v>
       </c>
       <c r="L56" t="n">
-        <v>180.16</v>
+        <v>124.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:09:17</t>
+          <t>07:05:55</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="F57" t="n">
         <v>7.24</v>
       </c>
       <c r="G57" t="n">
-        <v>322.2</v>
+        <v>325.5</v>
       </c>
       <c r="H57" t="n">
-        <v>96.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J57" t="n">
-        <v>143</v>
+        <v>214.21</v>
       </c>
       <c r="K57" t="n">
-        <v>-56.24</v>
+        <v>80.48</v>
       </c>
       <c r="L57" t="n">
-        <v>153.66</v>
+        <v>228.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:11:39</t>
+          <t>07:06:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="F58" t="n">
-        <v>3.95</v>
+        <v>6.5</v>
       </c>
       <c r="G58" t="n">
-        <v>329.2</v>
+        <v>325.6</v>
       </c>
       <c r="H58" t="n">
-        <v>96.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>152.3</v>
+        <v>-131.44</v>
       </c>
       <c r="K58" t="n">
-        <v>-150.59</v>
+        <v>111.3</v>
       </c>
       <c r="L58" t="n">
-        <v>214.18</v>
+        <v>172.24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:20:46</t>
+          <t>07:16:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="F59" t="n">
-        <v>6.45</v>
+        <v>4.2</v>
       </c>
       <c r="G59" t="n">
-        <v>333.4</v>
+        <v>331</v>
       </c>
       <c r="H59" t="n">
-        <v>98.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>25.61</v>
+        <v>14.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.67</v>
+        <v>32.39</v>
       </c>
       <c r="L59" t="n">
-        <v>51.49</v>
+        <v>35.59</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:21:51</t>
+          <t>07:18:18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="F60" t="n">
-        <v>7.24</v>
+        <v>6.22</v>
       </c>
       <c r="G60" t="n">
-        <v>329.7</v>
+        <v>340.5</v>
       </c>
       <c r="H60" t="n">
-        <v>90.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-63.84</v>
+        <v>20.36</v>
       </c>
       <c r="K60" t="n">
-        <v>-18.57</v>
+        <v>28.85</v>
       </c>
       <c r="L60" t="n">
-        <v>66.48999999999999</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:23:04</t>
+          <t>07:18:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="F61" t="n">
-        <v>5.81</v>
+        <v>4.06</v>
       </c>
       <c r="G61" t="n">
-        <v>330.1</v>
+        <v>334.3</v>
       </c>
       <c r="H61" t="n">
-        <v>98</v>
+        <v>42.8</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-24.29</v>
+        <v>-12.51</v>
       </c>
       <c r="K61" t="n">
-        <v>-47.35</v>
+        <v>40.93</v>
       </c>
       <c r="L61" t="n">
-        <v>53.22</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:26:38</t>
+          <t>07:23:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>7.24</v>
       </c>
       <c r="G62" t="n">
-        <v>329.1</v>
+        <v>325.3</v>
       </c>
       <c r="H62" t="n">
-        <v>97.2</v>
+        <v>82.7</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-15.81</v>
+        <v>35.57</v>
       </c>
       <c r="K62" t="n">
-        <v>107.6</v>
+        <v>-55.34</v>
       </c>
       <c r="L62" t="n">
-        <v>108.75</v>
+        <v>65.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:28:33</t>
+          <t>07:24:21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="F63" t="n">
-        <v>7.24</v>
+        <v>6.77</v>
       </c>
       <c r="G63" t="n">
-        <v>337.3</v>
+        <v>322</v>
       </c>
       <c r="H63" t="n">
-        <v>91.09999999999999</v>
+        <v>53</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>80.94</v>
+        <v>-29.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.48</v>
+        <v>24.77</v>
       </c>
       <c r="L63" t="n">
-        <v>82.41</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:29:45</t>
+          <t>07:26:11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="F64" t="n">
         <v>7.24</v>
       </c>
       <c r="G64" t="n">
-        <v>334.1</v>
+        <v>325.9</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>50.1</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>32.64</v>
+        <v>-25.1</v>
       </c>
       <c r="K64" t="n">
-        <v>69</v>
+        <v>39.61</v>
       </c>
       <c r="L64" t="n">
-        <v>76.33</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:34:39</t>
+          <t>07:32:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="F65" t="n">
-        <v>7.24</v>
+        <v>5.62</v>
       </c>
       <c r="G65" t="n">
-        <v>331.7</v>
+        <v>330.2</v>
       </c>
       <c r="H65" t="n">
-        <v>97.59999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-35.74</v>
+        <v>54.28</v>
       </c>
       <c r="K65" t="n">
-        <v>79.5</v>
+        <v>-36.44</v>
       </c>
       <c r="L65" t="n">
-        <v>87.16</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:37:13</t>
+          <t>07:33:54</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="F66" t="n">
-        <v>6.31</v>
+        <v>7.24</v>
       </c>
       <c r="G66" t="n">
-        <v>335.9</v>
+        <v>335</v>
       </c>
       <c r="H66" t="n">
-        <v>99.7</v>
+        <v>59.3</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-94.5</v>
+        <v>-22.01</v>
       </c>
       <c r="K66" t="n">
-        <v>126.62</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>157.99</v>
+        <v>75.22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:39:14</t>
+          <t>07:35:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="F67" t="n">
-        <v>5.79</v>
+        <v>2.69</v>
       </c>
       <c r="G67" t="n">
-        <v>341.7</v>
+        <v>325.4</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>22.2</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-17.68</v>
+        <v>-31.81</v>
       </c>
       <c r="K67" t="n">
-        <v>89.55</v>
+        <v>63.55</v>
       </c>
       <c r="L67" t="n">
-        <v>91.28</v>
+        <v>71.06999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:43:51</t>
+          <t>07:39:42</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="F68" t="n">
-        <v>7.24</v>
+        <v>5.59</v>
       </c>
       <c r="G68" t="n">
-        <v>332.6</v>
+        <v>335.7</v>
       </c>
       <c r="H68" t="n">
-        <v>94.8</v>
+        <v>52.5</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>103.7</v>
+        <v>-49.37</v>
       </c>
       <c r="K68" t="n">
-        <v>-89.41</v>
+        <v>18.29</v>
       </c>
       <c r="L68" t="n">
-        <v>136.92</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:44:57</t>
+          <t>07:41:22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="F69" t="n">
-        <v>5.96</v>
+        <v>6.96</v>
       </c>
       <c r="G69" t="n">
-        <v>338.7</v>
+        <v>333.6</v>
       </c>
       <c r="H69" t="n">
-        <v>92.3</v>
+        <v>25.8</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-76.62</v>
+        <v>-47</v>
       </c>
       <c r="K69" t="n">
-        <v>143.56</v>
+        <v>-62.14</v>
       </c>
       <c r="L69" t="n">
-        <v>162.73</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:46:06</t>
+          <t>07:43:17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="F70" t="n">
-        <v>4.22</v>
+        <v>6.86</v>
       </c>
       <c r="G70" t="n">
-        <v>337.4</v>
+        <v>321.9</v>
       </c>
       <c r="H70" t="n">
-        <v>99.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>82.20999999999999</v>
+        <v>107.18</v>
       </c>
       <c r="K70" t="n">
-        <v>44.01</v>
+        <v>-51.05</v>
       </c>
       <c r="L70" t="n">
-        <v>93.25</v>
+        <v>118.72</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:52:24</t>
+          <t>07:48:26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="F71" t="n">
         <v>7.24</v>
       </c>
       <c r="G71" t="n">
-        <v>330.9</v>
+        <v>343.9</v>
       </c>
       <c r="H71" t="n">
-        <v>93.8</v>
+        <v>55.8</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-242.51</v>
+        <v>-153</v>
       </c>
       <c r="K71" t="n">
-        <v>80.63</v>
+        <v>8.51</v>
       </c>
       <c r="L71" t="n">
-        <v>255.57</v>
+        <v>153.23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:54:54</t>
+          <t>07:50:21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="F72" t="n">
-        <v>3.44</v>
+        <v>5.56</v>
       </c>
       <c r="G72" t="n">
-        <v>327.6</v>
+        <v>332.5</v>
       </c>
       <c r="H72" t="n">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-138.3</v>
+        <v>4.36</v>
       </c>
       <c r="K72" t="n">
-        <v>119.76</v>
+        <v>146.15</v>
       </c>
       <c r="L72" t="n">
-        <v>182.95</v>
+        <v>146.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:56:14</t>
+          <t>07:51:02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="F73" t="n">
-        <v>6.31</v>
+        <v>5.86</v>
       </c>
       <c r="G73" t="n">
-        <v>320.5</v>
+        <v>325.6</v>
       </c>
       <c r="H73" t="n">
-        <v>97.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J73" t="n">
-        <v>-184.57</v>
+        <v>-118.4</v>
       </c>
       <c r="K73" t="n">
-        <v>187.98</v>
+        <v>-88.94</v>
       </c>
       <c r="L73" t="n">
-        <v>263.44</v>
+        <v>148.09</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:04:44</t>
+          <t>07:59:59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="F74" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="G74" t="n">
-        <v>333.6</v>
+        <v>347.9</v>
       </c>
       <c r="H74" t="n">
-        <v>93.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>59.34</v>
+        <v>18.96</v>
       </c>
       <c r="K74" t="n">
-        <v>2.26</v>
+        <v>17.06</v>
       </c>
       <c r="L74" t="n">
-        <v>59.39</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:07:33</t>
+          <t>08:02:05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="F75" t="n">
         <v>7.24</v>
       </c>
       <c r="G75" t="n">
-        <v>311.9</v>
+        <v>304.5</v>
       </c>
       <c r="H75" t="n">
-        <v>98.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>22.04</v>
+        <v>-10.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-64.11</v>
+        <v>-32.09</v>
       </c>
       <c r="L75" t="n">
-        <v>67.79000000000001</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:08:51</t>
+          <t>08:04:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="F76" t="n">
-        <v>6.12</v>
+        <v>7.24</v>
       </c>
       <c r="G76" t="n">
-        <v>326.8</v>
+        <v>326.6</v>
       </c>
       <c r="H76" t="n">
-        <v>92.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.89</v>
+        <v>-7.03</v>
       </c>
       <c r="K76" t="n">
-        <v>15.98</v>
+        <v>38.5</v>
       </c>
       <c r="L76" t="n">
-        <v>21.84</v>
+        <v>39.13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:12:28</t>
+          <t>08:08:33</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="F77" t="n">
-        <v>5.2</v>
+        <v>3.66</v>
       </c>
       <c r="G77" t="n">
-        <v>331.2</v>
+        <v>331.6</v>
       </c>
       <c r="H77" t="n">
-        <v>92.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>79.76000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="K77" t="n">
-        <v>-27.23</v>
+        <v>51.63</v>
       </c>
       <c r="L77" t="n">
-        <v>84.28</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:13:41</t>
+          <t>08:10:33</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="F78" t="n">
-        <v>6.16</v>
+        <v>5.22</v>
       </c>
       <c r="G78" t="n">
-        <v>345.5</v>
+        <v>315.6</v>
       </c>
       <c r="H78" t="n">
-        <v>99.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>48.08</v>
+        <v>-5.29</v>
       </c>
       <c r="K78" t="n">
-        <v>62.78</v>
+        <v>48.46</v>
       </c>
       <c r="L78" t="n">
-        <v>79.06999999999999</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:14:46</t>
+          <t>08:11:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="F79" t="n">
-        <v>3.81</v>
+        <v>7.24</v>
       </c>
       <c r="G79" t="n">
-        <v>328.6</v>
+        <v>323.2</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>57.37</v>
+        <v>29.7</v>
       </c>
       <c r="K79" t="n">
-        <v>-46.27</v>
+        <v>-67.62</v>
       </c>
       <c r="L79" t="n">
-        <v>73.70999999999999</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:19:45</t>
+          <t>08:15:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="F80" t="n">
-        <v>6.7</v>
+        <v>6.47</v>
       </c>
       <c r="G80" t="n">
-        <v>335</v>
+        <v>319.3</v>
       </c>
       <c r="H80" t="n">
-        <v>90.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>113.63</v>
+        <v>-33.7</v>
       </c>
       <c r="K80" t="n">
-        <v>-38.17</v>
+        <v>-41.61</v>
       </c>
       <c r="L80" t="n">
-        <v>119.88</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:21:21</t>
+          <t>08:16:38</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="F81" t="n">
-        <v>5.94</v>
+        <v>5.14</v>
       </c>
       <c r="G81" t="n">
-        <v>323.7</v>
+        <v>339.4</v>
       </c>
       <c r="H81" t="n">
-        <v>98.2</v>
+        <v>55.3</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-79.67</v>
+        <v>-40.42</v>
       </c>
       <c r="K81" t="n">
-        <v>-35.68</v>
+        <v>44.03</v>
       </c>
       <c r="L81" t="n">
-        <v>87.29000000000001</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:22:46</t>
+          <t>08:17:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="F82" t="n">
-        <v>5.72</v>
+        <v>7.24</v>
       </c>
       <c r="G82" t="n">
-        <v>325.8</v>
+        <v>330.2</v>
       </c>
       <c r="H82" t="n">
-        <v>97.3</v>
+        <v>64.8</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-48.23</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>14.55</v>
+        <v>46.66</v>
       </c>
       <c r="L82" t="n">
-        <v>50.37</v>
+        <v>82.81999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:27:00</t>
+          <t>08:22:32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.19</v>
+        <v>1.65</v>
       </c>
       <c r="F83" t="n">
-        <v>7.24</v>
+        <v>6.48</v>
       </c>
       <c r="G83" t="n">
-        <v>343.6</v>
+        <v>323.2</v>
       </c>
       <c r="H83" t="n">
-        <v>93.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>33.3</v>
+        <v>12.61</v>
       </c>
       <c r="K83" t="n">
-        <v>-65.98999999999999</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>73.92</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:28:58</t>
+          <t>08:23:59</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.99</v>
+        <v>2.83</v>
       </c>
       <c r="F84" t="n">
-        <v>6.64</v>
+        <v>7.24</v>
       </c>
       <c r="G84" t="n">
-        <v>328.4</v>
+        <v>331.2</v>
       </c>
       <c r="H84" t="n">
-        <v>92.90000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-101.6</v>
+        <v>101.3</v>
       </c>
       <c r="K84" t="n">
-        <v>134.79</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>168.79</v>
+        <v>140.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:30:25</t>
+          <t>08:25:03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="F85" t="n">
-        <v>7.24</v>
+        <v>2.17</v>
       </c>
       <c r="G85" t="n">
-        <v>322.3</v>
+        <v>319.3</v>
       </c>
       <c r="H85" t="n">
-        <v>94.8</v>
+        <v>24.2</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.96</v>
+        <v>59.84</v>
       </c>
       <c r="K85" t="n">
-        <v>217.81</v>
+        <v>134.29</v>
       </c>
       <c r="L85" t="n">
-        <v>217.89</v>
+        <v>147.02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:34:28</t>
+          <t>08:29:15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="F86" t="n">
-        <v>6.44</v>
+        <v>5.44</v>
       </c>
       <c r="G86" t="n">
-        <v>344.2</v>
+        <v>326.8</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>-125.91</v>
+        <v>-120.72</v>
       </c>
       <c r="K86" t="n">
-        <v>-168.04</v>
+        <v>112.22</v>
       </c>
       <c r="L86" t="n">
-        <v>209.98</v>
+        <v>164.82</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:36:11</t>
+          <t>08:30:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="F87" t="n">
-        <v>5.77</v>
+        <v>5.79</v>
       </c>
       <c r="G87" t="n">
-        <v>315.7</v>
+        <v>329.4</v>
       </c>
       <c r="H87" t="n">
-        <v>98.8</v>
+        <v>52.2</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>-111.59</v>
+        <v>122.02</v>
       </c>
       <c r="K87" t="n">
-        <v>150.83</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>187.62</v>
+        <v>149.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:36:53</t>
+          <t>08:31:47</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="F88" t="n">
-        <v>7.24</v>
+        <v>4.67</v>
       </c>
       <c r="G88" t="n">
-        <v>331.1</v>
+        <v>328</v>
       </c>
       <c r="H88" t="n">
-        <v>88.09999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-227.56</v>
+        <v>-84.62</v>
       </c>
       <c r="K88" t="n">
-        <v>82.02</v>
+        <v>-13.41</v>
       </c>
       <c r="L88" t="n">
-        <v>241.89</v>
+        <v>85.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.74</v>
+        <v>1.82</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7</v>
+        <v>4.11</v>
       </c>
       <c r="G14" t="n">
-        <v>330.6</v>
+        <v>335.8</v>
       </c>
       <c r="H14" t="n">
-        <v>21.9</v>
+        <v>43.4</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-37.15</v>
+        <v>-35.01</v>
       </c>
       <c r="K14" t="n">
-        <v>9.199999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="L14" t="n">
-        <v>38.27</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:04:36</t>
+          <t>05:03:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="F15" t="n">
-        <v>6.07</v>
+        <v>7.24</v>
       </c>
       <c r="G15" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="H15" t="n">
-        <v>57.8</v>
+        <v>72.3</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>32.82</v>
+        <v>9.69</v>
       </c>
       <c r="K15" t="n">
-        <v>9.17</v>
+        <v>39.07</v>
       </c>
       <c r="L15" t="n">
-        <v>34.08</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:06:19</t>
+          <t>05:06:10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="F16" t="n">
-        <v>7.24</v>
+        <v>6.81</v>
       </c>
       <c r="G16" t="n">
-        <v>337.4</v>
+        <v>321.7</v>
       </c>
       <c r="H16" t="n">
-        <v>67.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>34.58</v>
+        <v>1.24</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.28</v>
+        <v>29.14</v>
       </c>
       <c r="L16" t="n">
-        <v>34.73</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:11:10</t>
+          <t>05:11:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="F17" t="n">
         <v>7.24</v>
       </c>
       <c r="G17" t="n">
-        <v>328.2</v>
+        <v>346.7</v>
       </c>
       <c r="H17" t="n">
-        <v>66.59999999999999</v>
+        <v>35.1</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>-42.2</v>
+        <v>-46.93</v>
       </c>
       <c r="K17" t="n">
-        <v>16.58</v>
+        <v>5.08</v>
       </c>
       <c r="L17" t="n">
-        <v>45.34</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:12:28</t>
+          <t>05:14:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="F18" t="n">
-        <v>7.19</v>
+        <v>3.49</v>
       </c>
       <c r="G18" t="n">
-        <v>332.3</v>
+        <v>326.3</v>
       </c>
       <c r="H18" t="n">
-        <v>52.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-20.37</v>
+        <v>-21.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-39.87</v>
+        <v>50.51</v>
       </c>
       <c r="L18" t="n">
-        <v>44.77</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:13:23</t>
+          <t>05:15:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>5.69</v>
       </c>
       <c r="G19" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H19" t="n">
-        <v>24.4</v>
+        <v>51.4</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>7.31</v>
+        <v>-10.73</v>
       </c>
       <c r="K19" t="n">
-        <v>52.46</v>
+        <v>-36.09</v>
       </c>
       <c r="L19" t="n">
-        <v>52.97</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:18:37</t>
+          <t>05:19:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="F20" t="n">
-        <v>4.47</v>
+        <v>5.55</v>
       </c>
       <c r="G20" t="n">
-        <v>335.4</v>
+        <v>339.7</v>
       </c>
       <c r="H20" t="n">
-        <v>86.2</v>
+        <v>65.5</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-43.44</v>
+        <v>-34.96</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.15</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>43.87</v>
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:20:43</t>
+          <t>05:21:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="F21" t="n">
-        <v>4.86</v>
+        <v>6.45</v>
       </c>
       <c r="G21" t="n">
-        <v>331.8</v>
+        <v>328.6</v>
       </c>
       <c r="H21" t="n">
-        <v>72.5</v>
+        <v>53.4</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>39.16</v>
+        <v>-100.45</v>
       </c>
       <c r="K21" t="n">
-        <v>-18.43</v>
+        <v>-19.82</v>
       </c>
       <c r="L21" t="n">
-        <v>43.28</v>
+        <v>102.39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:22:51</t>
+          <t>05:22:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="F22" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="G22" t="n">
-        <v>319.9</v>
+        <v>328.3</v>
       </c>
       <c r="H22" t="n">
-        <v>97.7</v>
+        <v>62.6</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>93.08</v>
+        <v>-23.24</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.96</v>
+        <v>-68.84</v>
       </c>
       <c r="L22" t="n">
-        <v>93.20999999999999</v>
+        <v>72.65000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:28:04</t>
+          <t>05:27:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="F23" t="n">
-        <v>5.22</v>
+        <v>3.92</v>
       </c>
       <c r="G23" t="n">
-        <v>330.7</v>
+        <v>314.7</v>
       </c>
       <c r="H23" t="n">
-        <v>62.8</v>
+        <v>23.6</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>69.3</v>
+        <v>90.81</v>
       </c>
       <c r="K23" t="n">
-        <v>-80.23</v>
+        <v>-96.17</v>
       </c>
       <c r="L23" t="n">
-        <v>106.02</v>
+        <v>132.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:30:04</t>
+          <t>05:28:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="F24" t="n">
-        <v>4.68</v>
+        <v>4.48</v>
       </c>
       <c r="G24" t="n">
-        <v>332</v>
+        <v>350.4</v>
       </c>
       <c r="H24" t="n">
-        <v>89.7</v>
+        <v>60.6</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-98.81999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="K24" t="n">
-        <v>72.56</v>
+        <v>94.27</v>
       </c>
       <c r="L24" t="n">
-        <v>122.59</v>
+        <v>135.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:31:06</t>
+          <t>05:30:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="F25" t="n">
-        <v>4.35</v>
+        <v>6.16</v>
       </c>
       <c r="G25" t="n">
-        <v>325.9</v>
+        <v>333</v>
       </c>
       <c r="H25" t="n">
-        <v>96.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-28.11</v>
+        <v>-107.43</v>
       </c>
       <c r="K25" t="n">
-        <v>102.23</v>
+        <v>-59.9</v>
       </c>
       <c r="L25" t="n">
-        <v>106.02</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:35:51</t>
+          <t>05:35:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="F26" t="n">
-        <v>7.24</v>
+        <v>5.36</v>
       </c>
       <c r="G26" t="n">
-        <v>320.7</v>
+        <v>332.3</v>
       </c>
       <c r="H26" t="n">
-        <v>62.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-89.3</v>
+        <v>-148.56</v>
       </c>
       <c r="K26" t="n">
-        <v>-82.40000000000001</v>
+        <v>-122.05</v>
       </c>
       <c r="L26" t="n">
-        <v>121.51</v>
+        <v>192.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:36:53</t>
+          <t>05:37:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="F27" t="n">
-        <v>5.65</v>
+        <v>5.1</v>
       </c>
       <c r="G27" t="n">
-        <v>309.8</v>
+        <v>327</v>
       </c>
       <c r="H27" t="n">
-        <v>73.7</v>
+        <v>83.7</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-70.41</v>
+        <v>158.61</v>
       </c>
       <c r="K27" t="n">
-        <v>23.11</v>
+        <v>18.21</v>
       </c>
       <c r="L27" t="n">
-        <v>74.11</v>
+        <v>159.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:39:10</t>
+          <t>05:40:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="F28" t="n">
-        <v>3.38</v>
+        <v>5.97</v>
       </c>
       <c r="G28" t="n">
-        <v>339.6</v>
+        <v>322.5</v>
       </c>
       <c r="H28" t="n">
-        <v>91.8</v>
+        <v>22.3</v>
       </c>
       <c r="I28" t="n">
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-357.82</v>
+        <v>-118.15</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.72</v>
+        <v>22.78</v>
       </c>
       <c r="L28" t="n">
-        <v>357.89</v>
+        <v>120.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:51:03</t>
+          <t>05:52:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="F29" t="n">
-        <v>5.04</v>
+        <v>2.45</v>
       </c>
       <c r="G29" t="n">
-        <v>330.4</v>
+        <v>340.4</v>
       </c>
       <c r="H29" t="n">
-        <v>89.59999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-21.84</v>
+        <v>34.79</v>
       </c>
       <c r="K29" t="n">
-        <v>10.32</v>
+        <v>4.65</v>
       </c>
       <c r="L29" t="n">
-        <v>24.15</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:53:13</t>
+          <t>05:53:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="F30" t="n">
-        <v>4.71</v>
+        <v>5.42</v>
       </c>
       <c r="G30" t="n">
-        <v>337.1</v>
+        <v>330.8</v>
       </c>
       <c r="H30" t="n">
-        <v>52.7</v>
+        <v>58.2</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.35</v>
+        <v>-14.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-27.57</v>
+        <v>29.8</v>
       </c>
       <c r="L30" t="n">
-        <v>29.11</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:55:10</t>
+          <t>05:55:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="F31" t="n">
-        <v>7.24</v>
+        <v>3.39</v>
       </c>
       <c r="G31" t="n">
-        <v>328.9</v>
+        <v>327.8</v>
       </c>
       <c r="H31" t="n">
-        <v>52.1</v>
+        <v>34.9</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>27.69</v>
+        <v>-6.78</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.71</v>
+        <v>-31.21</v>
       </c>
       <c r="L31" t="n">
-        <v>27.74</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:00:08</t>
+          <t>06:00:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="F32" t="n">
-        <v>7.24</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>342</v>
+        <v>330.7</v>
       </c>
       <c r="H32" t="n">
-        <v>49.9</v>
+        <v>62.8</v>
       </c>
       <c r="I32" t="n">
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.91</v>
+        <v>31.93</v>
       </c>
       <c r="K32" t="n">
-        <v>-15.47</v>
+        <v>-39.14</v>
       </c>
       <c r="L32" t="n">
-        <v>39.1</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:01:23</t>
+          <t>06:01:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="F33" t="n">
-        <v>7.24</v>
+        <v>4.97</v>
       </c>
       <c r="G33" t="n">
-        <v>321.1</v>
+        <v>342.6</v>
       </c>
       <c r="H33" t="n">
-        <v>68</v>
+        <v>65.3</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-30.38</v>
+        <v>4.06</v>
       </c>
       <c r="K33" t="n">
-        <v>53.58</v>
+        <v>46.23</v>
       </c>
       <c r="L33" t="n">
-        <v>61.59</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:02:57</t>
+          <t>06:02:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="F34" t="n">
         <v>7.24</v>
       </c>
       <c r="G34" t="n">
-        <v>335</v>
+        <v>325.9</v>
       </c>
       <c r="H34" t="n">
-        <v>50.5</v>
+        <v>96.3</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>11.22</v>
+        <v>-11.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-34.3</v>
+        <v>51.69</v>
       </c>
       <c r="L34" t="n">
-        <v>36.09</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:07:05</t>
+          <t>06:06:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="F35" t="n">
-        <v>6.64</v>
+        <v>7.24</v>
       </c>
       <c r="G35" t="n">
-        <v>330.6</v>
+        <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>25.2</v>
+        <v>36.9</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-74.31</v>
+        <v>-46.5</v>
       </c>
       <c r="K35" t="n">
-        <v>58.09</v>
+        <v>39.08</v>
       </c>
       <c r="L35" t="n">
-        <v>94.31999999999999</v>
+        <v>60.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:08:37</t>
+          <t>06:07:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="F36" t="n">
-        <v>7.24</v>
+        <v>7.17</v>
       </c>
       <c r="G36" t="n">
-        <v>339.3</v>
+        <v>309.8</v>
       </c>
       <c r="H36" t="n">
-        <v>62.6</v>
+        <v>73.7</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.92</v>
+        <v>-33.32</v>
       </c>
       <c r="K36" t="n">
-        <v>75.09999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="L36" t="n">
-        <v>78.23</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:11:03</t>
+          <t>06:09:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="F37" t="n">
-        <v>7.24</v>
+        <v>3.67</v>
       </c>
       <c r="G37" t="n">
-        <v>317.2</v>
+        <v>329.7</v>
       </c>
       <c r="H37" t="n">
-        <v>31.7</v>
+        <v>84.2</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-39.46</v>
+        <v>-36.86</v>
       </c>
       <c r="K37" t="n">
-        <v>49.82</v>
+        <v>88.34</v>
       </c>
       <c r="L37" t="n">
-        <v>63.55</v>
+        <v>95.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:15:03</t>
+          <t>06:15:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="F38" t="n">
-        <v>2.18</v>
+        <v>7.24</v>
       </c>
       <c r="G38" t="n">
-        <v>334</v>
+        <v>348.8</v>
       </c>
       <c r="H38" t="n">
-        <v>55.2</v>
+        <v>61.1</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-76.09999999999999</v>
+        <v>-101.96</v>
       </c>
       <c r="K38" t="n">
-        <v>-56.69</v>
+        <v>57.24</v>
       </c>
       <c r="L38" t="n">
-        <v>94.89</v>
+        <v>116.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:16:58</t>
+          <t>06:16:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="F39" t="n">
-        <v>7.24</v>
+        <v>4.76</v>
       </c>
       <c r="G39" t="n">
-        <v>334.3</v>
+        <v>339.9</v>
       </c>
       <c r="H39" t="n">
-        <v>84.8</v>
+        <v>74.5</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>115.97</v>
+        <v>31.03</v>
       </c>
       <c r="K39" t="n">
-        <v>-87.26000000000001</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>145.13</v>
+        <v>99.23999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:18:03</t>
+          <t>06:18:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="F40" t="n">
-        <v>6.45</v>
+        <v>5.72</v>
       </c>
       <c r="G40" t="n">
-        <v>334.5</v>
+        <v>335.2</v>
       </c>
       <c r="H40" t="n">
-        <v>68.7</v>
+        <v>57.3</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>93.61</v>
+        <v>-109.62</v>
       </c>
       <c r="K40" t="n">
-        <v>94.73</v>
+        <v>-3.72</v>
       </c>
       <c r="L40" t="n">
-        <v>133.18</v>
+        <v>109.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:21:45</t>
+          <t>06:23:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="F41" t="n">
-        <v>5.5</v>
+        <v>4.24</v>
       </c>
       <c r="G41" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H41" t="n">
-        <v>76.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>46.1</v>
+        <v>-18.41</v>
       </c>
       <c r="K41" t="n">
-        <v>170.27</v>
+        <v>177.3</v>
       </c>
       <c r="L41" t="n">
-        <v>176.4</v>
+        <v>178.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:23:37</t>
+          <t>06:25:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.44</v>
+        <v>2.07</v>
       </c>
       <c r="F42" t="n">
-        <v>1.74</v>
+        <v>7.24</v>
       </c>
       <c r="G42" t="n">
-        <v>321.3</v>
+        <v>335.9</v>
       </c>
       <c r="H42" t="n">
-        <v>59.3</v>
+        <v>37.9</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>1.04</v>
+        <v>178.95</v>
       </c>
       <c r="K42" t="n">
-        <v>113.09</v>
+        <v>-59.93</v>
       </c>
       <c r="L42" t="n">
-        <v>113.1</v>
+        <v>188.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:25:03</t>
+          <t>06:26:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="F43" t="n">
-        <v>4.19</v>
+        <v>5.36</v>
       </c>
       <c r="G43" t="n">
-        <v>341</v>
+        <v>330.7</v>
       </c>
       <c r="H43" t="n">
-        <v>77.7</v>
+        <v>70.3</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-25.74</v>
+        <v>83.09</v>
       </c>
       <c r="K43" t="n">
-        <v>99.77</v>
+        <v>135.52</v>
       </c>
       <c r="L43" t="n">
-        <v>103.04</v>
+        <v>158.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:33:54</t>
+          <t>06:33:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="F44" t="n">
-        <v>5.26</v>
+        <v>2.3</v>
       </c>
       <c r="G44" t="n">
-        <v>319.3</v>
+        <v>346.4</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>61.6</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-31.42</v>
+        <v>29.14</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01</v>
+        <v>10</v>
       </c>
       <c r="L44" t="n">
-        <v>31.42</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:35:33</t>
+          <t>06:35:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="F45" t="n">
-        <v>7.24</v>
+        <v>5.65</v>
       </c>
       <c r="G45" t="n">
-        <v>337.7</v>
+        <v>341.9</v>
       </c>
       <c r="H45" t="n">
-        <v>89.59999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>-37.55</v>
+        <v>2.97</v>
       </c>
       <c r="K45" t="n">
-        <v>10.26</v>
+        <v>-12.13</v>
       </c>
       <c r="L45" t="n">
-        <v>38.93</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:36:55</t>
+          <t>06:36:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="F46" t="n">
-        <v>6.49</v>
+        <v>7.24</v>
       </c>
       <c r="G46" t="n">
-        <v>326.9</v>
+        <v>318.6</v>
       </c>
       <c r="H46" t="n">
-        <v>34.7</v>
+        <v>57.6</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.02</v>
+        <v>21.29</v>
       </c>
       <c r="K46" t="n">
-        <v>32.19</v>
+        <v>-28.54</v>
       </c>
       <c r="L46" t="n">
-        <v>32.2</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:40:13</t>
+          <t>06:41:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="F47" t="n">
-        <v>6.16</v>
+        <v>6.37</v>
       </c>
       <c r="G47" t="n">
-        <v>329.2</v>
+        <v>334</v>
       </c>
       <c r="H47" t="n">
-        <v>50.1</v>
+        <v>55.2</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-34.64</v>
+        <v>-27.97</v>
       </c>
       <c r="K47" t="n">
-        <v>-53.52</v>
+        <v>-28.7</v>
       </c>
       <c r="L47" t="n">
-        <v>63.75</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:42:30</t>
+          <t>06:43:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="F48" t="n">
-        <v>5.24</v>
+        <v>7.24</v>
       </c>
       <c r="G48" t="n">
-        <v>318.4</v>
+        <v>339.9</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-24.68</v>
+        <v>35.21</v>
       </c>
       <c r="K48" t="n">
-        <v>65.01000000000001</v>
+        <v>46.71</v>
       </c>
       <c r="L48" t="n">
-        <v>69.53</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:43:11</t>
+          <t>06:45:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="F49" t="n">
         <v>7.24</v>
       </c>
       <c r="G49" t="n">
-        <v>334.7</v>
+        <v>328.5</v>
       </c>
       <c r="H49" t="n">
-        <v>36.1</v>
+        <v>46.7</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-48.38</v>
+        <v>23.6</v>
       </c>
       <c r="K49" t="n">
-        <v>21.9</v>
+        <v>-40.78</v>
       </c>
       <c r="L49" t="n">
-        <v>53.11</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:48:30</t>
+          <t>06:50:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="F50" t="n">
-        <v>7.24</v>
+        <v>7.17</v>
       </c>
       <c r="G50" t="n">
-        <v>321.3</v>
+        <v>329.2</v>
       </c>
       <c r="H50" t="n">
-        <v>67.90000000000001</v>
+        <v>36.6</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-24.01</v>
+        <v>-90.17</v>
       </c>
       <c r="K50" t="n">
-        <v>70.42</v>
+        <v>-8.49</v>
       </c>
       <c r="L50" t="n">
-        <v>74.40000000000001</v>
+        <v>90.56999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:49:39</t>
+          <t>06:52:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="F51" t="n">
-        <v>4.54</v>
+        <v>6.83</v>
       </c>
       <c r="G51" t="n">
-        <v>317.5</v>
+        <v>317.2</v>
       </c>
       <c r="H51" t="n">
-        <v>82.7</v>
+        <v>75.3</v>
       </c>
       <c r="I51" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>9.49</v>
+        <v>-87.33</v>
       </c>
       <c r="K51" t="n">
-        <v>57.53</v>
+        <v>-5.54</v>
       </c>
       <c r="L51" t="n">
-        <v>58.31</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:51:59</t>
+          <t>06:54:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="F52" t="n">
-        <v>7.24</v>
+        <v>6.99</v>
       </c>
       <c r="G52" t="n">
-        <v>327.7</v>
+        <v>322.3</v>
       </c>
       <c r="H52" t="n">
-        <v>17.1</v>
+        <v>21.8</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-67.88</v>
+        <v>71.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-75.79000000000001</v>
+        <v>-55.85</v>
       </c>
       <c r="L52" t="n">
-        <v>101.74</v>
+        <v>90.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:56:23</t>
+          <t>06:59:20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="F53" t="n">
-        <v>2.39</v>
+        <v>7.24</v>
       </c>
       <c r="G53" t="n">
-        <v>320.3</v>
+        <v>326.4</v>
       </c>
       <c r="H53" t="n">
-        <v>58</v>
+        <v>37.9</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>74.66</v>
+        <v>-73.01000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-91.83</v>
+        <v>-71.34999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>118.34</v>
+        <v>102.08</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:57:16</t>
+          <t>07:00:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="F54" t="n">
-        <v>6.23</v>
+        <v>6.52</v>
       </c>
       <c r="G54" t="n">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="H54" t="n">
-        <v>68.09999999999999</v>
+        <v>38.7</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>84.20999999999999</v>
+        <v>-45.14</v>
       </c>
       <c r="K54" t="n">
-        <v>72.51000000000001</v>
+        <v>140.5</v>
       </c>
       <c r="L54" t="n">
-        <v>111.12</v>
+        <v>147.58</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:59:40</t>
+          <t>07:03:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="F55" t="n">
-        <v>5.83</v>
+        <v>7.24</v>
       </c>
       <c r="G55" t="n">
-        <v>332.3</v>
+        <v>332.7</v>
       </c>
       <c r="H55" t="n">
-        <v>18.6</v>
+        <v>41</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>75.01000000000001</v>
+        <v>-73.90000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>63.49</v>
+        <v>-87.19</v>
       </c>
       <c r="L55" t="n">
-        <v>98.27</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:05:01</t>
+          <t>07:08:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="F56" t="n">
-        <v>5.9</v>
+        <v>6.63</v>
       </c>
       <c r="G56" t="n">
-        <v>330.7</v>
+        <v>329.3</v>
       </c>
       <c r="H56" t="n">
-        <v>90.2</v>
+        <v>97.5</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>34.54</v>
+        <v>121.87</v>
       </c>
       <c r="K56" t="n">
-        <v>-119.18</v>
+        <v>78.87</v>
       </c>
       <c r="L56" t="n">
-        <v>124.08</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:05:55</t>
+          <t>07:10:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="F57" t="n">
         <v>7.24</v>
       </c>
       <c r="G57" t="n">
-        <v>325.5</v>
+        <v>329.7</v>
       </c>
       <c r="H57" t="n">
-        <v>71.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>214.21</v>
+        <v>97.45</v>
       </c>
       <c r="K57" t="n">
-        <v>80.48</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>228.83</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:06:51</t>
+          <t>07:11:38</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="F58" t="n">
-        <v>6.5</v>
+        <v>2.46</v>
       </c>
       <c r="G58" t="n">
-        <v>325.6</v>
+        <v>315.6</v>
       </c>
       <c r="H58" t="n">
-        <v>63.1</v>
+        <v>51.7</v>
       </c>
       <c r="I58" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-131.44</v>
+        <v>37.26</v>
       </c>
       <c r="K58" t="n">
-        <v>111.3</v>
+        <v>-128.5</v>
       </c>
       <c r="L58" t="n">
-        <v>172.24</v>
+        <v>133.79</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:16:31</t>
+          <t>07:20:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="F59" t="n">
-        <v>4.2</v>
+        <v>6.39</v>
       </c>
       <c r="G59" t="n">
-        <v>331</v>
+        <v>335.5</v>
       </c>
       <c r="H59" t="n">
-        <v>75.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>14.73</v>
+        <v>-38.09</v>
       </c>
       <c r="K59" t="n">
-        <v>32.39</v>
+        <v>25.07</v>
       </c>
       <c r="L59" t="n">
-        <v>35.59</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:18:18</t>
+          <t>07:20:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="F60" t="n">
-        <v>6.22</v>
+        <v>5.82</v>
       </c>
       <c r="G60" t="n">
-        <v>340.5</v>
+        <v>337.7</v>
       </c>
       <c r="H60" t="n">
-        <v>72.90000000000001</v>
+        <v>47.8</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>20.36</v>
+        <v>-19.91</v>
       </c>
       <c r="K60" t="n">
-        <v>28.85</v>
+        <v>-29.81</v>
       </c>
       <c r="L60" t="n">
-        <v>35.31</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:18:54</t>
+          <t>07:21:42</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="F61" t="n">
-        <v>4.06</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>334.3</v>
+        <v>339.6</v>
       </c>
       <c r="H61" t="n">
-        <v>42.8</v>
+        <v>60.2</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.51</v>
+        <v>-31</v>
       </c>
       <c r="K61" t="n">
-        <v>40.93</v>
+        <v>40.54</v>
       </c>
       <c r="L61" t="n">
-        <v>42.8</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:23:13</t>
+          <t>07:27:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="F62" t="n">
         <v>7.24</v>
       </c>
       <c r="G62" t="n">
-        <v>325.3</v>
+        <v>337.5</v>
       </c>
       <c r="H62" t="n">
-        <v>82.7</v>
+        <v>34.6</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>35.57</v>
+        <v>19.29</v>
       </c>
       <c r="K62" t="n">
-        <v>-55.34</v>
+        <v>39.17</v>
       </c>
       <c r="L62" t="n">
-        <v>65.78</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:24:21</t>
+          <t>07:29:03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="F63" t="n">
-        <v>6.77</v>
+        <v>6.18</v>
       </c>
       <c r="G63" t="n">
-        <v>322</v>
+        <v>338.6</v>
       </c>
       <c r="H63" t="n">
-        <v>53</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-29.65</v>
+        <v>14.47</v>
       </c>
       <c r="K63" t="n">
-        <v>24.77</v>
+        <v>-46.59</v>
       </c>
       <c r="L63" t="n">
-        <v>38.64</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:26:11</t>
+          <t>07:30:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="F64" t="n">
-        <v>7.24</v>
+        <v>6.59</v>
       </c>
       <c r="G64" t="n">
-        <v>325.9</v>
+        <v>321.7</v>
       </c>
       <c r="H64" t="n">
-        <v>50.1</v>
+        <v>38.3</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.1</v>
+        <v>37.74</v>
       </c>
       <c r="K64" t="n">
-        <v>39.61</v>
+        <v>47.52</v>
       </c>
       <c r="L64" t="n">
-        <v>46.89</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:32:27</t>
+          <t>07:35:54</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="F65" t="n">
-        <v>5.62</v>
+        <v>7.13</v>
       </c>
       <c r="G65" t="n">
-        <v>330.2</v>
+        <v>325.4</v>
       </c>
       <c r="H65" t="n">
-        <v>52.7</v>
+        <v>87.3</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>54.28</v>
+        <v>-71.37</v>
       </c>
       <c r="K65" t="n">
-        <v>-36.44</v>
+        <v>-23.71</v>
       </c>
       <c r="L65" t="n">
-        <v>65.38</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:33:54</t>
+          <t>07:38:06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="F66" t="n">
         <v>7.24</v>
       </c>
       <c r="G66" t="n">
-        <v>335</v>
+        <v>317.8</v>
       </c>
       <c r="H66" t="n">
-        <v>59.3</v>
+        <v>28.8</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.01</v>
+        <v>-40.83</v>
       </c>
       <c r="K66" t="n">
-        <v>71.93000000000001</v>
+        <v>87.66</v>
       </c>
       <c r="L66" t="n">
-        <v>75.22</v>
+        <v>96.70999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:35:11</t>
+          <t>07:39:58</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="F67" t="n">
-        <v>2.69</v>
+        <v>7.24</v>
       </c>
       <c r="G67" t="n">
-        <v>325.4</v>
+        <v>317.1</v>
       </c>
       <c r="H67" t="n">
-        <v>22.2</v>
+        <v>11</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-31.81</v>
+        <v>-4.18</v>
       </c>
       <c r="K67" t="n">
-        <v>63.55</v>
+        <v>-87.84</v>
       </c>
       <c r="L67" t="n">
-        <v>71.06999999999999</v>
+        <v>87.94</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:39:42</t>
+          <t>07:45:29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="F68" t="n">
-        <v>5.59</v>
+        <v>7.03</v>
       </c>
       <c r="G68" t="n">
-        <v>335.7</v>
+        <v>347.7</v>
       </c>
       <c r="H68" t="n">
-        <v>52.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-49.37</v>
+        <v>-56.26</v>
       </c>
       <c r="K68" t="n">
-        <v>18.29</v>
+        <v>-97.56999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>52.65</v>
+        <v>112.62</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:41:22</t>
+          <t>07:47:47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="F69" t="n">
-        <v>6.96</v>
+        <v>7.24</v>
       </c>
       <c r="G69" t="n">
-        <v>333.6</v>
+        <v>336.7</v>
       </c>
       <c r="H69" t="n">
-        <v>25.8</v>
+        <v>85.2</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>-47</v>
+        <v>103.13</v>
       </c>
       <c r="K69" t="n">
-        <v>-62.14</v>
+        <v>173.84</v>
       </c>
       <c r="L69" t="n">
-        <v>77.91</v>
+        <v>202.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:43:17</t>
+          <t>07:49:18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="F70" t="n">
-        <v>6.86</v>
+        <v>6.48</v>
       </c>
       <c r="G70" t="n">
-        <v>321.9</v>
+        <v>329.1</v>
       </c>
       <c r="H70" t="n">
-        <v>58</v>
+        <v>63.6</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>107.18</v>
+        <v>-73.86</v>
       </c>
       <c r="K70" t="n">
-        <v>-51.05</v>
+        <v>-136.64</v>
       </c>
       <c r="L70" t="n">
-        <v>118.72</v>
+        <v>155.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:48:26</t>
+          <t>07:53:08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="F71" t="n">
-        <v>7.24</v>
+        <v>6.96</v>
       </c>
       <c r="G71" t="n">
-        <v>343.9</v>
+        <v>324.7</v>
       </c>
       <c r="H71" t="n">
-        <v>55.8</v>
+        <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-153</v>
+        <v>184.87</v>
       </c>
       <c r="K71" t="n">
-        <v>8.51</v>
+        <v>78.66</v>
       </c>
       <c r="L71" t="n">
-        <v>153.23</v>
+        <v>200.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:50:21</t>
+          <t>07:55:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="F72" t="n">
-        <v>5.56</v>
+        <v>7.24</v>
       </c>
       <c r="G72" t="n">
-        <v>332.5</v>
+        <v>317.3</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>4.36</v>
+        <v>-47.28</v>
       </c>
       <c r="K72" t="n">
-        <v>146.15</v>
+        <v>96.16</v>
       </c>
       <c r="L72" t="n">
-        <v>146.22</v>
+        <v>107.16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:51:02</t>
+          <t>07:57:40</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="F73" t="n">
-        <v>5.86</v>
+        <v>5.38</v>
       </c>
       <c r="G73" t="n">
-        <v>325.6</v>
+        <v>324.7</v>
       </c>
       <c r="H73" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-118.4</v>
+        <v>87.94</v>
       </c>
       <c r="K73" t="n">
-        <v>-88.94</v>
+        <v>-217.51</v>
       </c>
       <c r="L73" t="n">
-        <v>148.09</v>
+        <v>234.61</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:59:59</t>
+          <t>08:10:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="F74" t="n">
-        <v>2.63</v>
+        <v>3.27</v>
       </c>
       <c r="G74" t="n">
-        <v>347.9</v>
+        <v>332.1</v>
       </c>
       <c r="H74" t="n">
-        <v>94.40000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>18.96</v>
+        <v>-31.84</v>
       </c>
       <c r="K74" t="n">
-        <v>17.06</v>
+        <v>3.33</v>
       </c>
       <c r="L74" t="n">
-        <v>25.51</v>
+        <v>32.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:02:05</t>
+          <t>08:12:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="F75" t="n">
         <v>7.24</v>
       </c>
       <c r="G75" t="n">
-        <v>304.5</v>
+        <v>331.9</v>
       </c>
       <c r="H75" t="n">
-        <v>84.59999999999999</v>
+        <v>46.4</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.2</v>
+        <v>-15.2</v>
       </c>
       <c r="K75" t="n">
-        <v>-32.09</v>
+        <v>-34.78</v>
       </c>
       <c r="L75" t="n">
-        <v>33.67</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:04:14</t>
+          <t>08:13:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="F76" t="n">
         <v>7.24</v>
       </c>
       <c r="G76" t="n">
-        <v>326.6</v>
+        <v>338.1</v>
       </c>
       <c r="H76" t="n">
-        <v>64.59999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.03</v>
+        <v>12.65</v>
       </c>
       <c r="K76" t="n">
-        <v>38.5</v>
+        <v>15.26</v>
       </c>
       <c r="L76" t="n">
-        <v>39.13</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:08:33</t>
+          <t>08:17:52</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="F77" t="n">
-        <v>3.66</v>
+        <v>6.47</v>
       </c>
       <c r="G77" t="n">
-        <v>331.6</v>
+        <v>326.1</v>
       </c>
       <c r="H77" t="n">
-        <v>70.3</v>
+        <v>69.8</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>6.64</v>
+        <v>-49.16</v>
       </c>
       <c r="K77" t="n">
-        <v>51.63</v>
+        <v>-63.32</v>
       </c>
       <c r="L77" t="n">
-        <v>52.06</v>
+        <v>80.16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:10:33</t>
+          <t>08:19:17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="F78" t="n">
-        <v>5.22</v>
+        <v>6.98</v>
       </c>
       <c r="G78" t="n">
-        <v>315.6</v>
+        <v>329.8</v>
       </c>
       <c r="H78" t="n">
-        <v>73.90000000000001</v>
+        <v>53.9</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.29</v>
+        <v>21.82</v>
       </c>
       <c r="K78" t="n">
-        <v>48.46</v>
+        <v>60.39</v>
       </c>
       <c r="L78" t="n">
-        <v>48.75</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:11:52</t>
+          <t>08:20:17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="F79" t="n">
-        <v>7.24</v>
+        <v>6.85</v>
       </c>
       <c r="G79" t="n">
-        <v>323.2</v>
+        <v>332.6</v>
       </c>
       <c r="H79" t="n">
-        <v>75.09999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>29.7</v>
+        <v>47.43</v>
       </c>
       <c r="K79" t="n">
-        <v>-67.62</v>
+        <v>-22.29</v>
       </c>
       <c r="L79" t="n">
-        <v>73.86</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:15:13</t>
+          <t>08:23:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>6.47</v>
+        <v>5.75</v>
       </c>
       <c r="G80" t="n">
-        <v>319.3</v>
+        <v>324.7</v>
       </c>
       <c r="H80" t="n">
-        <v>90</v>
+        <v>87.3</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-33.7</v>
+        <v>-83.55</v>
       </c>
       <c r="K80" t="n">
-        <v>-41.61</v>
+        <v>0.26</v>
       </c>
       <c r="L80" t="n">
-        <v>53.55</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:16:38</t>
+          <t>08:25:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="F81" t="n">
-        <v>5.14</v>
+        <v>7.24</v>
       </c>
       <c r="G81" t="n">
-        <v>339.4</v>
+        <v>332.2</v>
       </c>
       <c r="H81" t="n">
-        <v>55.3</v>
+        <v>58.9</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-40.42</v>
+        <v>87.2</v>
       </c>
       <c r="K81" t="n">
-        <v>44.03</v>
+        <v>16.56</v>
       </c>
       <c r="L81" t="n">
-        <v>59.77</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:17:21</t>
+          <t>08:26:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="F82" t="n">
-        <v>7.24</v>
+        <v>6.77</v>
       </c>
       <c r="G82" t="n">
-        <v>330.2</v>
+        <v>343.2</v>
       </c>
       <c r="H82" t="n">
-        <v>64.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>68.43000000000001</v>
+        <v>-77.34</v>
       </c>
       <c r="K82" t="n">
-        <v>46.66</v>
+        <v>-62.92</v>
       </c>
       <c r="L82" t="n">
-        <v>82.81999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:22:32</t>
+          <t>08:32:10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="F83" t="n">
-        <v>6.48</v>
+        <v>3.98</v>
       </c>
       <c r="G83" t="n">
-        <v>323.2</v>
+        <v>328.2</v>
       </c>
       <c r="H83" t="n">
-        <v>82.59999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>12.61</v>
+        <v>107.94</v>
       </c>
       <c r="K83" t="n">
-        <v>95.56999999999999</v>
+        <v>-131</v>
       </c>
       <c r="L83" t="n">
-        <v>96.40000000000001</v>
+        <v>169.74</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:23:59</t>
+          <t>08:34:34</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.83</v>
+        <v>2.05</v>
       </c>
       <c r="F84" t="n">
-        <v>7.24</v>
+        <v>6.59</v>
       </c>
       <c r="G84" t="n">
-        <v>331.2</v>
+        <v>326.9</v>
       </c>
       <c r="H84" t="n">
-        <v>35.6</v>
+        <v>97.7</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>101.3</v>
+        <v>-115.03</v>
       </c>
       <c r="K84" t="n">
-        <v>96.76000000000001</v>
+        <v>-114.96</v>
       </c>
       <c r="L84" t="n">
-        <v>140.09</v>
+        <v>162.63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:25:03</t>
+          <t>08:36:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="F85" t="n">
-        <v>2.17</v>
+        <v>7.24</v>
       </c>
       <c r="G85" t="n">
-        <v>319.3</v>
+        <v>319.2</v>
       </c>
       <c r="H85" t="n">
-        <v>24.2</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>59.84</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>134.29</v>
+        <v>120.88</v>
       </c>
       <c r="L85" t="n">
-        <v>147.02</v>
+        <v>121.28</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:29:15</t>
+          <t>08:40:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="F86" t="n">
-        <v>5.44</v>
+        <v>4.87</v>
       </c>
       <c r="G86" t="n">
-        <v>326.8</v>
+        <v>324.1</v>
       </c>
       <c r="H86" t="n">
-        <v>64.7</v>
+        <v>37.3</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-120.72</v>
+        <v>-150.61</v>
       </c>
       <c r="K86" t="n">
-        <v>112.22</v>
+        <v>-102.85</v>
       </c>
       <c r="L86" t="n">
-        <v>164.82</v>
+        <v>182.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:30:56</t>
+          <t>08:42:34</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="F87" t="n">
-        <v>5.79</v>
+        <v>7.24</v>
       </c>
       <c r="G87" t="n">
-        <v>329.4</v>
+        <v>332</v>
       </c>
       <c r="H87" t="n">
-        <v>52.2</v>
+        <v>58.4</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>122.02</v>
+        <v>50.44</v>
       </c>
       <c r="K87" t="n">
-        <v>86.23999999999999</v>
+        <v>-121.44</v>
       </c>
       <c r="L87" t="n">
-        <v>149.42</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:31:47</t>
+          <t>08:44:14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="F88" t="n">
-        <v>4.67</v>
+        <v>7.24</v>
       </c>
       <c r="G88" t="n">
-        <v>328</v>
+        <v>340.4</v>
       </c>
       <c r="H88" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-84.62</v>
+        <v>-140.08</v>
       </c>
       <c r="K88" t="n">
-        <v>-13.41</v>
+        <v>-136.25</v>
       </c>
       <c r="L88" t="n">
-        <v>85.67</v>
+        <v>195.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-05-14.xlsx
+++ b/output/2024-05-14.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.19</v>
+        <v>-6.39</v>
       </c>
       <c r="K14" t="n">
-        <v>51.93</v>
+        <v>53.62</v>
       </c>
       <c r="L14" t="n">
-        <v>52.3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>45.15</v>
+        <v>46.08</v>
       </c>
       <c r="K15" t="n">
-        <v>25.77</v>
+        <v>26.3</v>
       </c>
       <c r="L15" t="n">
-        <v>51.98</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>28.96</v>
+        <v>33.3</v>
       </c>
       <c r="K16" t="n">
-        <v>18.92</v>
+        <v>21.76</v>
       </c>
       <c r="L16" t="n">
-        <v>34.59</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>47.37</v>
+        <v>55.07</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.67</v>
+        <v>-4.27</v>
       </c>
       <c r="L17" t="n">
-        <v>47.51</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-36.95</v>
+        <v>-43.58</v>
       </c>
       <c r="K18" t="n">
-        <v>-26.22</v>
+        <v>-30.93</v>
       </c>
       <c r="L18" t="n">
-        <v>45.31</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>19.04</v>
+        <v>19.87</v>
       </c>
       <c r="K19" t="n">
-        <v>78.70999999999999</v>
+        <v>82.14</v>
       </c>
       <c r="L19" t="n">
-        <v>80.98</v>
+        <v>84.51000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-70.51000000000001</v>
+        <v>-76.87</v>
       </c>
       <c r="K20" t="n">
-        <v>90.08</v>
+        <v>98.2</v>
       </c>
       <c r="L20" t="n">
-        <v>114.4</v>
+        <v>124.71</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-45.6</v>
+        <v>-51.96</v>
       </c>
       <c r="K21" t="n">
-        <v>-96.08</v>
+        <v>-109.47</v>
       </c>
       <c r="L21" t="n">
-        <v>106.35</v>
+        <v>121.17</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-27.8</v>
+        <v>-30.19</v>
       </c>
       <c r="K22" t="n">
-        <v>104.81</v>
+        <v>113.81</v>
       </c>
       <c r="L22" t="n">
-        <v>108.44</v>
+        <v>117.75</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>62.71</v>
+        <v>77.92</v>
       </c>
       <c r="K23" t="n">
-        <v>78.18000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="L23" t="n">
-        <v>100.22</v>
+        <v>124.53</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-88.2</v>
+        <v>-115.21</v>
       </c>
       <c r="K24" t="n">
-        <v>19.01</v>
+        <v>24.83</v>
       </c>
       <c r="L24" t="n">
-        <v>90.23</v>
+        <v>117.86</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-18.2</v>
+        <v>-22.61</v>
       </c>
       <c r="K25" t="n">
-        <v>-111.67</v>
+        <v>-138.7</v>
       </c>
       <c r="L25" t="n">
-        <v>113.15</v>
+        <v>140.53</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-65.98999999999999</v>
+        <v>-82.55</v>
       </c>
       <c r="K26" t="n">
-        <v>-193.25</v>
+        <v>-241.72</v>
       </c>
       <c r="L26" t="n">
-        <v>204.21</v>
+        <v>255.43</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-67.48999999999999</v>
+        <v>-81.16</v>
       </c>
       <c r="K27" t="n">
-        <v>176.83</v>
+        <v>212.64</v>
       </c>
       <c r="L27" t="n">
-        <v>189.27</v>
+        <v>227.6</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>133.54</v>
+        <v>175.41</v>
       </c>
       <c r="K28" t="n">
-        <v>-49.59</v>
+        <v>-65.14</v>
       </c>
       <c r="L28" t="n">
-        <v>142.45</v>
+        <v>187.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.73</v>
+        <v>-34.93</v>
       </c>
       <c r="K29" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="L29" t="n">
-        <v>29.77</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>50.21</v>
+        <v>53.71</v>
       </c>
       <c r="K30" t="n">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="L30" t="n">
-        <v>50.29</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>46.33</v>
+        <v>51.24</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.72</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>46.97</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="K32" t="n">
-        <v>-77.03</v>
+        <v>-82.48999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>77.19</v>
+        <v>82.67</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.75</v>
+        <v>-3.08</v>
       </c>
       <c r="K33" t="n">
-        <v>60.15</v>
+        <v>67.39</v>
       </c>
       <c r="L33" t="n">
-        <v>60.21</v>
+        <v>67.45999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>4.44</v>
+        <v>4.85</v>
       </c>
       <c r="K34" t="n">
-        <v>-61.85</v>
+        <v>-67.55</v>
       </c>
       <c r="L34" t="n">
-        <v>62.01</v>
+        <v>67.73</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>54.2</v>
+        <v>62.49</v>
       </c>
       <c r="K35" t="n">
-        <v>-73.12</v>
+        <v>-84.31</v>
       </c>
       <c r="L35" t="n">
-        <v>91.02</v>
+        <v>104.94</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>104.02</v>
+        <v>110.63</v>
       </c>
       <c r="K36" t="n">
-        <v>-78</v>
+        <v>-82.95999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>130.01</v>
+        <v>138.28</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-16.73</v>
+        <v>-19.32</v>
       </c>
       <c r="K37" t="n">
-        <v>79.84999999999999</v>
+        <v>92.23</v>
       </c>
       <c r="L37" t="n">
-        <v>81.58</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-115.67</v>
+        <v>-135.06</v>
       </c>
       <c r="K38" t="n">
-        <v>70.03</v>
+        <v>81.77</v>
       </c>
       <c r="L38" t="n">
-        <v>135.21</v>
+        <v>157.89</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-16.87</v>
+        <v>-21.33</v>
       </c>
       <c r="K39" t="n">
-        <v>-101.13</v>
+        <v>-127.86</v>
       </c>
       <c r="L39" t="n">
-        <v>102.53</v>
+        <v>129.62</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>60.1</v>
+        <v>70.63</v>
       </c>
       <c r="K40" t="n">
-        <v>116.68</v>
+        <v>137.13</v>
       </c>
       <c r="L40" t="n">
-        <v>131.24</v>
+        <v>154.25</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-71.48</v>
+        <v>-92.83</v>
       </c>
       <c r="K41" t="n">
-        <v>134.66</v>
+        <v>174.89</v>
       </c>
       <c r="L41" t="n">
-        <v>152.45</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>180.06</v>
+        <v>216.46</v>
       </c>
       <c r="K42" t="n">
-        <v>47.47</v>
+        <v>57.06</v>
       </c>
       <c r="L42" t="n">
-        <v>186.21</v>
+        <v>223.85</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-44.72</v>
+        <v>-54.79</v>
       </c>
       <c r="K43" t="n">
-        <v>204.06</v>
+        <v>250.04</v>
       </c>
       <c r="L43" t="n">
-        <v>208.9</v>
+        <v>255.97</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-26.26</v>
+        <v>-29.91</v>
       </c>
       <c r="K44" t="n">
-        <v>-20.4</v>
+        <v>-23.24</v>
       </c>
       <c r="L44" t="n">
-        <v>33.25</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.45</v>
+        <v>-34</v>
       </c>
       <c r="K45" t="n">
-        <v>19.21</v>
+        <v>22.18</v>
       </c>
       <c r="L45" t="n">
-        <v>35.17</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>4.82</v>
+        <v>5.72</v>
       </c>
       <c r="K46" t="n">
-        <v>32.54</v>
+        <v>38.62</v>
       </c>
       <c r="L46" t="n">
-        <v>32.89</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-64.43000000000001</v>
+        <v>-68.20999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.9</v>
+        <v>-13.65</v>
       </c>
       <c r="L47" t="n">
-        <v>65.70999999999999</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-29.37</v>
+        <v>-31.4</v>
       </c>
       <c r="K48" t="n">
-        <v>65.25</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>71.55</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-67.72</v>
+        <v>-73.40000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>2.89</v>
+        <v>3.13</v>
       </c>
       <c r="L49" t="n">
-        <v>67.78</v>
+        <v>73.47</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>112</v>
+        <v>127.75</v>
       </c>
       <c r="K50" t="n">
-        <v>8.380000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>112.32</v>
+        <v>128.11</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>7.05</v>
+        <v>8.15</v>
       </c>
       <c r="K51" t="n">
-        <v>82.26000000000001</v>
+        <v>95.03</v>
       </c>
       <c r="L51" t="n">
-        <v>82.56</v>
+        <v>95.38</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>18.97</v>
+        <v>21.97</v>
       </c>
       <c r="K52" t="n">
-        <v>75.8</v>
+        <v>87.77</v>
       </c>
       <c r="L52" t="n">
-        <v>78.14</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-46.11</v>
+        <v>-53.42</v>
       </c>
       <c r="K53" t="n">
-        <v>119.74</v>
+        <v>138.72</v>
       </c>
       <c r="L53" t="n">
-        <v>128.31</v>
+        <v>148.65</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>42.52</v>
+        <v>52.18</v>
       </c>
       <c r="K54" t="n">
-        <v>103.55</v>
+        <v>127.08</v>
       </c>
       <c r="L54" t="n">
-        <v>111.94</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>79.73</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-153.01</v>
+        <v>-172.72</v>
       </c>
       <c r="L55" t="n">
-        <v>172.54</v>
+        <v>194.76</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-30.61</v>
+        <v>-39.11</v>
       </c>
       <c r="K56" t="n">
-        <v>164.63</v>
+        <v>210.33</v>
       </c>
       <c r="L56" t="n">
-        <v>167.45</v>
+        <v>213.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>151.52</v>
+        <v>200.32</v>
       </c>
       <c r="K57" t="n">
-        <v>-83.93000000000001</v>
+        <v>-110.96</v>
       </c>
       <c r="L57" t="n">
-        <v>173.22</v>
+        <v>229</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>149.53</v>
+        <v>180.4</v>
       </c>
       <c r="K58" t="n">
-        <v>-156.4</v>
+        <v>-188.68</v>
       </c>
       <c r="L58" t="n">
-        <v>216.38</v>
+        <v>261.04</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>22.19</v>
+        <v>23.86</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.75</v>
+        <v>-41.66</v>
       </c>
       <c r="L59" t="n">
-        <v>44.65</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.96</v>
+        <v>-52.6</v>
       </c>
       <c r="K60" t="n">
-        <v>-14.78</v>
+        <v>-15.88</v>
       </c>
       <c r="L60" t="n">
-        <v>51.14</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.84</v>
+        <v>-19.98</v>
       </c>
       <c r="K61" t="n">
-        <v>-35.55</v>
+        <v>-39.82</v>
       </c>
       <c r="L61" t="n">
-        <v>39.78</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-12.82</v>
+        <v>-13.04</v>
       </c>
       <c r="K62" t="n">
-        <v>89.59</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>90.5</v>
+        <v>92.03</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>53.67</v>
+        <v>60.58</v>
       </c>
       <c r="K63" t="n">
-        <v>-11.67</v>
+        <v>-13.17</v>
       </c>
       <c r="L63" t="n">
-        <v>54.92</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>28.08</v>
+        <v>30.51</v>
       </c>
       <c r="K64" t="n">
-        <v>57.27</v>
+        <v>62.23</v>
       </c>
       <c r="L64" t="n">
-        <v>63.79</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-25.61</v>
+        <v>-33.19</v>
       </c>
       <c r="K65" t="n">
-        <v>60.25</v>
+        <v>78.06</v>
       </c>
       <c r="L65" t="n">
-        <v>65.47</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-74.77</v>
+        <v>-80.92</v>
       </c>
       <c r="K66" t="n">
-        <v>98.91</v>
+        <v>107.04</v>
       </c>
       <c r="L66" t="n">
-        <v>123.99</v>
+        <v>134.19</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-14.42</v>
+        <v>-17.71</v>
       </c>
       <c r="K67" t="n">
-        <v>79.01000000000001</v>
+        <v>97.05</v>
       </c>
       <c r="L67" t="n">
-        <v>80.31999999999999</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>78.59999999999999</v>
+        <v>99.08</v>
       </c>
       <c r="K68" t="n">
-        <v>-77.90000000000001</v>
+        <v>-98.2</v>
       </c>
       <c r="L68" t="n">
-        <v>110.67</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-64.84</v>
+        <v>-74.97</v>
       </c>
       <c r="K69" t="n">
-        <v>114.35</v>
+        <v>132.22</v>
       </c>
       <c r="L69" t="n">
-        <v>131.45</v>
+        <v>151.99</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>84.75</v>
+        <v>109.77</v>
       </c>
       <c r="K70" t="n">
-        <v>22.46</v>
+        <v>29.09</v>
       </c>
       <c r="L70" t="n">
-        <v>87.67</v>
+        <v>113.56</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-177.19</v>
+        <v>-221.98</v>
       </c>
       <c r="K71" t="n">
-        <v>37.78</v>
+        <v>47.33</v>
       </c>
       <c r="L71" t="n">
-        <v>181.17</v>
+        <v>226.97</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-149.38</v>
+        <v>-186.93</v>
       </c>
       <c r="K72" t="n">
-        <v>114.68</v>
+        <v>143.5</v>
       </c>
       <c r="L72" t="n">
-        <v>188.32</v>
+        <v>235.66</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-129.93</v>
+        <v>-158.95</v>
       </c>
       <c r="K73" t="n">
-        <v>132.48</v>
+        <v>162.06</v>
       </c>
       <c r="L73" t="n">
-        <v>185.56</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>54.71</v>
+        <v>57.6</v>
       </c>
       <c r="K74" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="L74" t="n">
-        <v>54.74</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>19.87</v>
+        <v>21.29</v>
       </c>
       <c r="K75" t="n">
-        <v>-56.12</v>
+        <v>-60.15</v>
       </c>
       <c r="L75" t="n">
-        <v>59.54</v>
+        <v>63.81</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.02</v>
+        <v>-12.91</v>
       </c>
       <c r="K76" t="n">
-        <v>11.4</v>
+        <v>13.35</v>
       </c>
       <c r="L76" t="n">
-        <v>15.86</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>62.89</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-22.61</v>
+        <v>-25.21</v>
       </c>
       <c r="L77" t="n">
-        <v>66.83</v>
+        <v>74.48999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>38.85</v>
+        <v>44.63</v>
       </c>
       <c r="K78" t="n">
-        <v>48.61</v>
+        <v>55.86</v>
       </c>
       <c r="L78" t="n">
-        <v>62.23</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>54.71</v>
+        <v>58.8</v>
       </c>
       <c r="K79" t="n">
-        <v>-44.19</v>
+        <v>-47.49</v>
       </c>
       <c r="L79" t="n">
-        <v>70.33</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>98.13</v>
+        <v>110.27</v>
       </c>
       <c r="K80" t="n">
-        <v>-37.17</v>
+        <v>-41.77</v>
       </c>
       <c r="L80" t="n">
-        <v>104.93</v>
+        <v>117.92</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-52.03</v>
+        <v>-67.04000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.15</v>
+        <v>-53.01</v>
       </c>
       <c r="L81" t="n">
-        <v>66.34</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-24.43</v>
+        <v>-30.98</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.27</v>
+        <v>-0.34</v>
       </c>
       <c r="L82" t="n">
-        <v>24.44</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>173.15</v>
+        <v>208.79</v>
       </c>
       <c r="K83" t="n">
-        <v>12.77</v>
+        <v>15.39</v>
       </c>
       <c r="L83" t="n">
-        <v>173.62</v>
+        <v>209.36</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-196.93</v>
+        <v>-218.14</v>
       </c>
       <c r="K84" t="n">
-        <v>-78.18000000000001</v>
+        <v>-86.59</v>
       </c>
       <c r="L84" t="n">
-        <v>211.88</v>
+        <v>234.7</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>136.63</v>
+        <v>166.69</v>
       </c>
       <c r="K85" t="n">
-        <v>17.42</v>
+        <v>21.25</v>
       </c>
       <c r="L85" t="n">
-        <v>137.74</v>
+        <v>168.04</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-178.16</v>
+        <v>-226.5</v>
       </c>
       <c r="K86" t="n">
-        <v>-62.22</v>
+        <v>-79.09999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>188.71</v>
+        <v>239.91</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>181.82</v>
+        <v>225.05</v>
       </c>
       <c r="K87" t="n">
-        <v>-39.76</v>
+        <v>-49.21</v>
       </c>
       <c r="L87" t="n">
-        <v>186.11</v>
+        <v>230.36</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>26.06</v>
+        <v>33.42</v>
       </c>
       <c r="K88" t="n">
-        <v>-165.78</v>
+        <v>-212.6</v>
       </c>
       <c r="L88" t="n">
-        <v>167.81</v>
+        <v>215.21</v>
       </c>
     </row>
   </sheetData>
